--- a/financial_models/BESS_Valuation.xlsx
+++ b/financial_models/BESS_Valuation.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Portfolio project (independent rebuild of Boman deck claims)</t>
+          <t>Portfolio project (independent rebuild of the manager's projections claims)</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Whether the family trust should commit as an LP to an (illustrative) develop-and-flip RTB BESS fund, and at what expected return.</t>
+          <t>Whether the investor should commit as an LP to an (illustrative) develop-and-flip RTB BESS fund, and at what expected return.</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
     <row r="24">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Discount rate &amp; premium • the THREE scenario success rates (vs the independent ~45%) • RTB $/MW by state (need independent comps) • dev cost per project &amp; abandonment • fees/carry/hurdle • cash-flow profile. Boman's figures are CLAIMS to verify — defend your own.</t>
+          <t>Discount rate &amp; premium • the THREE scenario success rates (vs the independent ~45%) • RTB $/MW by state (need independent comps) • dev cost per project &amp; abandonment • fees/carry/hurdle • cash-flow profile. the manager's figures are CLAIMS to verify — defend your own.</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>1. Trace every formula + colour audit; confirm master check = OK; stress the switch in all 3 positions.  2. Replace 🟡 BENCHMARK / Boman-claim inputs with verified independent values (RTB comps, per-state success, dev cost).  3. Stress a downside where RTB prices are 20–30% lower and success ≈ the independent ~45%; confirm capital can be lost.</t>
+          <t>1. Trace every formula + colour audit; confirm master check = OK; stress the switch in all 3 positions.  2. Replace 🟡 BENCHMARK / manager-claim inputs with verified independent values (RTB comps, per-state success, dev cost).  3. Stress a downside where RTB prices are 20–30% lower and success ≈ the independent ~45%; confirm capital can be lost.</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>ILLUSTRATIVE fund built from public benchmark data; an INDEPENDENT rebuild of the Boman deck's CLAIMS (not an endorsement). NOT investment advice. Wholesale-investor context; read the IM. All figures illustrative and must be independently verified. Capital is at risk.</t>
+          <t>ILLUSTRATIVE fund built from public benchmark data; an INDEPENDENT rebuild of the the manager's projections (not an endorsement). NOT investment advice. Wholesale-investor context; read the IM. All figures illustrative and must be independently verified. Capital is at risk.</t>
         </is>
       </c>
     </row>
@@ -2455,7 +2455,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Develop ~5 MW distribution BESS to RTB, sell before construction (NSW/VIC/SA). ILLUSTRATIVE — Boman figures are manager claims to verify. Not investment advice.</t>
+          <t>Develop ~5 MW distribution BESS to RTB, sell before construction (NSW/VIC/SA). ILLUSTRATIVE — the manager figures are manager claims to verify. Not investment advice.</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>A real, policy-backed, capital-light niche with a viable RTB exit — but conditional. Merchant risk passes to the buyer; the fund's risk is the survival curve + the RTB price. The independent success (~45%) sits BELOW Boman's Base (65%), and the Conservative case can lose capital. The single biggest risk is EXIT/BUYER risk (non-binding buyers; RTB stage), then development/approval risk. Pursue only on verified buyer depth, RTB comps, and a survivable downside.</t>
+          <t>A real, policy-backed, capital-light niche with a viable RTB exit — but conditional. Merchant risk passes to the buyer; the fund's risk is the survival curve + the RTB price. The independent success (~45%) sits BELOW the manager's Base (65%), and the Conservative case can lose capital. The single biggest risk is EXIT/BUYER risk (non-binding buyers; RTB stage), then development/approval risk. Pursue only on verified buyer depth, RTB comps, and a survivable downside.</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2713,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Sources (LIVE = fetched; BENCHMARK = documented public benchmark / Boman claim, verify)</t>
+          <t>Sources (LIVE = fetched; BENCHMARK = documented public benchmark / the manager claim, verify)</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>Boman deck (claim ~$500k/project) — verify bottom-up: site+EIA+grid+community+overhead</t>
+          <t>the manager's projections (claim ~$500k/project) — verify bottom-up: site+EIA+grid+community+overhead</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>RTB $/MW by state (Boman claim)</t>
+          <t>RTB $/MW by state (the manager claim)</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -2889,14 +2889,14 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>RTB $/MW by state (Boman claim — independent comps needed)</t>
+          <t>RTB $/MW by state (the manager claim — independent comps needed)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>RTB comps: publicly reported deals only; paid DBs (BNEF, Enerdatics, Mergermarket) out of scope. Boman's prices are claims to verify.</t>
+          <t>RTB comps: publicly reported deals only; paid DBs (BNEF, Enerdatics, Mergermarket) out of scope. the manager's prices are claims to verify.</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>ILLUSTRATIVE develop-and-flip RTB fund. Boman figures are the manager's CLAIMS — verify. Every input traces to a source.</t>
+          <t>ILLUSTRATIVE develop-and-flip RTB fund. the manager figures are the manager's CLAIMS — verify. Every input traces to a source.</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Illustrative / Boman claim (see config)</t>
+          <t>Illustrative / the manager claim (see config)</t>
         </is>
       </c>
       <c r="F6" s="17" t="inlineStr">
@@ -3547,7 +3547,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fund structure &amp; fees (Boman claim — verify in IM)</t>
+          <t>Fund structure &amp; fees (the manager claim — verify in IM)</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Illustrative / Boman claim (see config)</t>
+          <t>Illustrative / the manager claim (see config)</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Illustrative / Boman claim (see config)</t>
+          <t>Illustrative / the manager claim (see config)</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Illustrative / Boman claim (see config)</t>
+          <t>Illustrative / the manager claim (see config)</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Illustrative / Boman claim (see config)</t>
+          <t>Illustrative / the manager claim (see config)</t>
         </is>
       </c>
       <c r="F12" s="17" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Illustrative / Boman claim (see config)</t>
+          <t>Illustrative / the manager claim (see config)</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Illustrative / Boman claim (see config)</t>
+          <t>Illustrative / the manager claim (see config)</t>
         </is>
       </c>
       <c r="F14" s="17" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Illustrative / Boman claim (see config)</t>
+          <t>Illustrative / the manager claim (see config)</t>
         </is>
       </c>
       <c r="F15" s="17" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Boman deck (claim ~$500k/project) — verify bottom-up: site+EIA+grid+community+overhead</t>
+          <t>the manager's projections (claim ~$500k/project) — verify bottom-up: site+EIA+grid+community+overhead</t>
         </is>
       </c>
       <c r="F17" s="17" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Illustrative / Boman claim (see config)</t>
+          <t>Illustrative / the manager claim (see config)</t>
         </is>
       </c>
       <c r="F18" s="17" t="inlineStr">
@@ -3974,7 +3974,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>RTB exit price — $/MW by state (Boman claim — verify)</t>
+          <t>RTB exit price — $/MW by state (the manager claim — verify)</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>RTB $/MW by state (Boman claim — independent comps needed)</t>
+          <t>RTB $/MW by state (the manager claim — independent comps needed)</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>RTB $/MW by state (Boman claim — independent comps needed)</t>
+          <t>RTB $/MW by state (the manager claim — independent comps needed)</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>RTB $/MW by state (Boman claim — independent comps needed)</t>
+          <t>RTB $/MW by state (the manager claim — independent comps needed)</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Illustrative / Boman claim (see config)</t>
+          <t>Illustrative / the manager claim (see config)</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
@@ -4715,7 +4715,7 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>Success rates mirror Boman's deck (40/65/80%) for comparability. The INDEPENDENT survival curve (~45%) sits below Base (65%) — see Calc_Survival. Scenarios are the analyst's to OWN.</t>
+          <t>Success rates mirror the manager's deck (40/65/80%) for comparability. The INDEPENDENT survival curve (~45%) sits below Base (65%) — see Calc_Survival. Scenarios are the analyst's to OWN.</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>Base scenario success (Boman claim)</t>
+          <t>Base scenario success (the manager claim)</t>
         </is>
       </c>
       <c r="C9" s="32">
@@ -4865,7 +4865,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Independent ~45% sits BELOW Boman's Base (65%): treat Base as optimistic; ask for sub-5MW, per-state evidence. The sub-5MW AEMO registration exemption MAY lift small-distribution success above the large-project benchmark — verify.</t>
+          <t>Independent ~45% sits BELOW the manager's Base (65%): treat Base as optimistic; ask for sub-5MW, per-state evidence. The sub-5MW AEMO registration exemption MAY lift small-distribution success above the large-project benchmark — verify.</t>
         </is>
       </c>
     </row>

--- a/financial_models/BESS_Valuation.xlsx
+++ b/financial_models/BESS_Valuation.xlsx
@@ -89,6 +89,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="00008000"/>
       <sz val="10"/>
     </font>
@@ -97,12 +103,6 @@
       <i val="1"/>
       <color rgb="00FF0000"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00008000"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -157,14 +157,14 @@
   <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -216,18 +216,19 @@
     </xf>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -237,12 +238,12 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -259,14 +260,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -718,7 +718,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -979,19 +979,19 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Cumulative success</t>
-        </is>
-      </c>
-      <c r="B5" s="32">
-        <f>'Scenarios'!$B$5</f>
-        <v/>
-      </c>
-      <c r="C5" s="32">
-        <f>'Scenarios'!$C$5</f>
-        <v/>
-      </c>
-      <c r="D5" s="32">
-        <f>'Scenarios'!$D$5</f>
+          <t>Flip success (DA x conn x sale)</t>
+        </is>
+      </c>
+      <c r="B5" s="34">
+        <f>'Scenarios'!$B$5*'Inputs'!$C$23*'Inputs'!$C$24</f>
+        <v/>
+      </c>
+      <c r="C5" s="34">
+        <f>'Scenarios'!$C$5*'Inputs'!$C$23*'Inputs'!$C$24</f>
+        <v/>
+      </c>
+      <c r="D5" s="34">
+        <f>'Scenarios'!$D$5*'Inputs'!$C$23*'Inputs'!$C$24</f>
         <v/>
       </c>
     </row>
@@ -1001,15 +1001,15 @@
           <t>RTB price multiplier</t>
         </is>
       </c>
-      <c r="B6" s="40">
+      <c r="B6" s="41">
         <f>'Scenarios'!$B$6</f>
         <v/>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="41">
         <f>'Scenarios'!$C$6</f>
         <v/>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="41">
         <f>'Scenarios'!$D$6</f>
         <v/>
       </c>
@@ -1020,15 +1020,15 @@
           <t>Dev cost multiplier</t>
         </is>
       </c>
-      <c r="B7" s="40">
+      <c r="B7" s="41">
         <f>'Scenarios'!$B$7</f>
         <v/>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="41">
         <f>'Scenarios'!$C$7</f>
         <v/>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="41">
         <f>'Scenarios'!$D$7</f>
         <v/>
       </c>
@@ -1039,15 +1039,15 @@
           <t>Dev cost per project</t>
         </is>
       </c>
-      <c r="B8" s="41">
+      <c r="B8" s="42">
         <f>'Inputs'!$C$17*B7</f>
         <v/>
       </c>
-      <c r="C8" s="41">
+      <c r="C8" s="42">
         <f>'Inputs'!$C$17*C7</f>
         <v/>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="42">
         <f>'Inputs'!$C$17*D7</f>
         <v/>
       </c>
@@ -1058,15 +1058,15 @@
           <t>Projects started</t>
         </is>
       </c>
-      <c r="B9" s="46">
+      <c r="B9" s="47">
         <f>IFERROR('Inputs'!$C$10/B5,0)</f>
         <v/>
       </c>
-      <c r="C9" s="46">
+      <c r="C9" s="47">
         <f>IFERROR('Inputs'!$C$10/C5,0)</f>
         <v/>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="47">
         <f>IFERROR('Inputs'!$C$10/D5,0)</f>
         <v/>
       </c>
@@ -1077,15 +1077,15 @@
           <t>Projects failed</t>
         </is>
       </c>
-      <c r="B10" s="46">
+      <c r="B10" s="47">
         <f>B9-'Inputs'!$C$10</f>
         <v/>
       </c>
-      <c r="C10" s="46">
+      <c r="C10" s="47">
         <f>C9-'Inputs'!$C$10</f>
         <v/>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="47">
         <f>D9-'Inputs'!$C$10</f>
         <v/>
       </c>
@@ -1096,15 +1096,15 @@
           <t>Total dev cost</t>
         </is>
       </c>
-      <c r="B11" s="47">
+      <c r="B11" s="48">
         <f>'Inputs'!$C$10*B8+B10*'Inputs'!$C$18*B8</f>
         <v/>
       </c>
-      <c r="C11" s="47">
+      <c r="C11" s="48">
         <f>'Inputs'!$C$10*C8+C10*'Inputs'!$C$18*C8</f>
         <v/>
       </c>
-      <c r="D11" s="47">
+      <c r="D11" s="48">
         <f>'Inputs'!$C$10*D8+D10*'Inputs'!$C$18*D8</f>
         <v/>
       </c>
@@ -1115,15 +1115,15 @@
           <t>Gross proceeds</t>
         </is>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="48">
         <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*B6</f>
         <v/>
       </c>
-      <c r="C12" s="47">
+      <c r="C12" s="48">
         <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*C6</f>
         <v/>
       </c>
-      <c r="D12" s="47">
+      <c r="D12" s="48">
         <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*D6</f>
         <v/>
       </c>
@@ -1134,15 +1134,15 @@
           <t>Invested capital</t>
         </is>
       </c>
-      <c r="B13" s="47">
+      <c r="B13" s="48">
         <f>B11+'Calc_Fund'!$C$15+'Calc_Fund'!$C$14</f>
         <v/>
       </c>
-      <c r="C13" s="47">
+      <c r="C13" s="48">
         <f>C11+'Calc_Fund'!$C$15+'Calc_Fund'!$C$14</f>
         <v/>
       </c>
-      <c r="D13" s="47">
+      <c r="D13" s="48">
         <f>D11+'Calc_Fund'!$C$15+'Calc_Fund'!$C$14</f>
         <v/>
       </c>
@@ -1153,15 +1153,15 @@
           <t>Profit before carry</t>
         </is>
       </c>
-      <c r="B14" s="47">
+      <c r="B14" s="48">
         <f>B12-B13</f>
         <v/>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="48">
         <f>C12-C13</f>
         <v/>
       </c>
-      <c r="D14" s="47">
+      <c r="D14" s="48">
         <f>D12-D13</f>
         <v/>
       </c>
@@ -1172,15 +1172,15 @@
           <t>Hurdle amount</t>
         </is>
       </c>
-      <c r="B15" s="47">
+      <c r="B15" s="48">
         <f>B13*'Calc_Fund'!$C$19</f>
         <v/>
       </c>
-      <c r="C15" s="47">
+      <c r="C15" s="48">
         <f>C13*'Calc_Fund'!$C$19</f>
         <v/>
       </c>
-      <c r="D15" s="47">
+      <c r="D15" s="48">
         <f>D13*'Calc_Fund'!$C$19</f>
         <v/>
       </c>
@@ -1191,15 +1191,15 @@
           <t>Carry to GP</t>
         </is>
       </c>
-      <c r="B16" s="47">
+      <c r="B16" s="48">
         <f>'Inputs'!$C$14*MAX(0,B14-B15)</f>
         <v/>
       </c>
-      <c r="C16" s="47">
+      <c r="C16" s="48">
         <f>'Inputs'!$C$14*MAX(0,C14-C15)</f>
         <v/>
       </c>
-      <c r="D16" s="47">
+      <c r="D16" s="48">
         <f>'Inputs'!$C$14*MAX(0,D14-D15)</f>
         <v/>
       </c>
@@ -1210,15 +1210,15 @@
           <t>Distributions to LP</t>
         </is>
       </c>
-      <c r="B17" s="47">
+      <c r="B17" s="48">
         <f>B12-B16</f>
         <v/>
       </c>
-      <c r="C17" s="47">
+      <c r="C17" s="48">
         <f>C12-C16</f>
         <v/>
       </c>
-      <c r="D17" s="47">
+      <c r="D17" s="48">
         <f>D12-D16</f>
         <v/>
       </c>
@@ -1229,15 +1229,15 @@
           <t>MOIC (net)</t>
         </is>
       </c>
-      <c r="B18" s="49">
+      <c r="B18" s="50">
         <f>IFERROR(B17/B13,0)</f>
         <v/>
       </c>
-      <c r="C18" s="49">
+      <c r="C18" s="50">
         <f>IFERROR(C17/C13,0)</f>
         <v/>
       </c>
-      <c r="D18" s="49">
+      <c r="D18" s="50">
         <f>IFERROR(D17/D13,0)</f>
         <v/>
       </c>
@@ -1297,15 +1297,15 @@
           <t>Weight</t>
         </is>
       </c>
-      <c r="B23" s="50">
+      <c r="B23" s="51">
         <f>'Scenarios'!$B$13</f>
         <v/>
       </c>
-      <c r="C23" s="50">
+      <c r="C23" s="51">
         <f>'Scenarios'!$C$13</f>
         <v/>
       </c>
-      <c r="D23" s="50">
+      <c r="D23" s="51">
         <f>'Scenarios'!$D$13</f>
         <v/>
       </c>
@@ -1316,19 +1316,19 @@
           <t>Investor IRR</t>
         </is>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="33">
         <f>'Returns'!$B$19</f>
         <v/>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="33">
         <f>'Returns'!$C$19</f>
         <v/>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="33">
         <f>'Returns'!$D$19</f>
         <v/>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="35">
         <f>SUMPRODUCT('Scenarios'!$B$13:$D$13,B24:D24)</f>
         <v/>
       </c>
@@ -1339,19 +1339,19 @@
           <t>MOIC (net)</t>
         </is>
       </c>
-      <c r="B25" s="51">
+      <c r="B25" s="52">
         <f>'Returns'!$B$18</f>
         <v/>
       </c>
-      <c r="C25" s="51">
+      <c r="C25" s="52">
         <f>'Returns'!$C$18</f>
         <v/>
       </c>
-      <c r="D25" s="51">
+      <c r="D25" s="52">
         <f>'Returns'!$D$18</f>
         <v/>
       </c>
-      <c r="E25" s="49">
+      <c r="E25" s="50">
         <f>SUMPRODUCT('Scenarios'!$B$13:$D$13,B25:D25)</f>
         <v/>
       </c>
@@ -1374,7 +1374,7 @@
           <t>rNPV pipeline (Base)</t>
         </is>
       </c>
-      <c r="C28" s="52">
+      <c r="C28" s="53">
         <f>'Calc_Project_rNPV'!$M$10</f>
         <v/>
       </c>
@@ -1385,7 +1385,7 @@
           <t>$/MW benchmark (dev value)</t>
         </is>
       </c>
-      <c r="C29" s="52">
+      <c r="C29" s="53">
         <f>'Calc_CrossChecks'!$C$9</f>
         <v/>
       </c>
@@ -1396,7 +1396,7 @@
           <t>VC method (today value)</t>
         </is>
       </c>
-      <c r="C30" s="52">
+      <c r="C30" s="53">
         <f>'Calc_CrossChecks'!$C$18</f>
         <v/>
       </c>
@@ -1407,7 +1407,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="C31" s="44">
+      <c r="C31" s="45">
         <f>MIN(C28:C30)</f>
         <v/>
       </c>
@@ -1418,7 +1418,7 @@
           <t>Midpoint</t>
         </is>
       </c>
-      <c r="C32" s="45">
+      <c r="C32" s="46">
         <f>AVERAGE(C28:C30)</f>
         <v/>
       </c>
@@ -1429,7 +1429,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="C33" s="44">
+      <c r="C33" s="45">
         <f>MAX(C28:C30)</f>
         <v/>
       </c>
@@ -1502,7 +1502,7 @@
           <t>Gross RTB asset value $m</t>
         </is>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="48">
         <f>SUMPRODUCT('Calc_Project_rNPV'!$C$4:$C$9,'Calc_Project_rNPV'!$E$4:$E$9)*'Scenarios'!$C$6</f>
         <v/>
       </c>
@@ -1513,7 +1513,7 @@
           <t>Total dev cost $m</t>
         </is>
       </c>
-      <c r="C6" s="47">
+      <c r="C6" s="48">
         <f>'Inputs'!$C$17*'Scenarios'!$C$7*6</f>
         <v/>
       </c>
@@ -1524,7 +1524,7 @@
           <t>Average years to sale</t>
         </is>
       </c>
-      <c r="C7" s="46">
+      <c r="C7" s="47">
         <f>AVERAGE('Calc_Project_rNPV'!$D$4:$D$9)</f>
         <v/>
       </c>
@@ -1532,11 +1532,11 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>Cumulative success (Base)</t>
-        </is>
-      </c>
-      <c r="C8" s="32">
-        <f>'Scenarios'!$C$5</f>
+          <t>Flip success (Base, DA x conn x sale)</t>
+        </is>
+      </c>
+      <c r="C8" s="34">
+        <f>'Scenarios'!$C$5*'Inputs'!$C$23*'Inputs'!$C$24</f>
         <v/>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
           <t>$/MW implied dev value $m</t>
         </is>
       </c>
-      <c r="C9" s="44">
+      <c r="C9" s="45">
         <f>IFERROR((C5-C6)*C8/(1+'Inputs'!$C$7)^C7,0)</f>
         <v/>
       </c>
@@ -1564,7 +1564,7 @@
           <t>Total RTB sale value $m</t>
         </is>
       </c>
-      <c r="C12" s="47">
+      <c r="C12" s="48">
         <f>SUMPRODUCT('Calc_Project_rNPV'!$C$4:$C$9,'Calc_Project_rNPV'!$E$4:$E$9)*'Scenarios'!$C$6</f>
         <v/>
       </c>
@@ -1575,7 +1575,7 @@
           <t>Total dev cost $m</t>
         </is>
       </c>
-      <c r="C13" s="47">
+      <c r="C13" s="48">
         <f>C6</f>
         <v/>
       </c>
@@ -1583,10 +1583,10 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Cumulative success (Base)</t>
-        </is>
-      </c>
-      <c r="C14" s="32">
+          <t>Flip success (Base)</t>
+        </is>
+      </c>
+      <c r="C14" s="33">
         <f>C8</f>
         <v/>
       </c>
@@ -1597,7 +1597,7 @@
           <t>Exit equity value (expected) $m</t>
         </is>
       </c>
-      <c r="C15" s="41">
+      <c r="C15" s="42">
         <f>C14*(C12-C13)</f>
         <v/>
       </c>
@@ -1608,7 +1608,7 @@
           <t>VC target return</t>
         </is>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="33">
         <f>'Inputs'!$C$30</f>
         <v/>
       </c>
@@ -1619,7 +1619,7 @@
           <t>Hold horizon (yrs)</t>
         </is>
       </c>
-      <c r="C17" s="37">
+      <c r="C17" s="38">
         <f>'Inputs'!$C$11</f>
         <v/>
       </c>
@@ -1630,7 +1630,7 @@
           <t>VC today value $m</t>
         </is>
       </c>
-      <c r="C18" s="44">
+      <c r="C18" s="45">
         <f>IFERROR(C15/(1+C16)^C17,0)</f>
         <v/>
       </c>
@@ -1670,15 +1670,15 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="B22" s="53">
+      <c r="B22" s="54">
         <f>'Inputs'!$C$26</f>
         <v/>
       </c>
-      <c r="C22" s="53">
+      <c r="C22" s="54">
         <f>'Inputs'!$C$20</f>
         <v/>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="34">
         <f>IFERROR(B22/C22,0)</f>
         <v/>
       </c>
@@ -1689,15 +1689,15 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="B23" s="53">
+      <c r="B23" s="54">
         <f>'Inputs'!$C$27</f>
         <v/>
       </c>
-      <c r="C23" s="53">
+      <c r="C23" s="54">
         <f>'Inputs'!$C$20</f>
         <v/>
       </c>
-      <c r="D23" s="33">
+      <c r="D23" s="34">
         <f>IFERROR(B23/C23,0)</f>
         <v/>
       </c>
@@ -1708,15 +1708,15 @@
           <t>SA</t>
         </is>
       </c>
-      <c r="B24" s="53">
+      <c r="B24" s="54">
         <f>'Inputs'!$C$28</f>
         <v/>
       </c>
-      <c r="C24" s="53">
+      <c r="C24" s="54">
         <f>'Inputs'!$C$20</f>
         <v/>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="34">
         <f>IFERROR(B24/C24,0)</f>
         <v/>
       </c>
@@ -1743,7 +1743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1762,7 +1762,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SENSITIVITY — investor MOIC (net): success × RTB price</t>
+          <t>SENSITIVITY — investor MOIC (net): development approval × RTB price</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Investor MOIC vs cumulative success (down) × RTB price multiplier (across); all else at Base. IRR ≈ MOIC^(1/eff-hold). Live formula grid (recalculates everywhere). All figures AUD $m / x.</t>
+          <t>Investor MOIC vs DEVELOPMENT-APPROVAL rate (down) × RTB price multiplier (across); all else at Base. Flip success = DA × grid connection × sale, so the funnel widens with the FULL gate chain (not the DA rate alone). IRR ≈ MOIC^(1/eff-hold). Live formula grid. All figures AUD $m / x.</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
           <t>Carry %</t>
         </is>
       </c>
-      <c r="B4" s="32">
+      <c r="B4" s="33">
         <f>'Inputs'!$C$14</f>
         <v/>
       </c>
@@ -1795,7 +1795,7 @@
           <t>Hurdle factor</t>
         </is>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="33">
         <f>'Calc_Fund'!$C$19</f>
         <v/>
       </c>
@@ -1806,13 +1806,24 @@
           <t>Fixed fees (mgmt+entry) $m</t>
         </is>
       </c>
-      <c r="B6" s="47">
+      <c r="B6" s="48">
         <f>'Calc_Fund'!$C$15+'Calc_Fund'!$C$14</f>
         <v/>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Conn × sale (flip adj)</t>
+        </is>
+      </c>
+      <c r="B7" s="34">
+        <f>'Inputs'!$C$23*'Inputs'!$C$24</f>
+        <v/>
+      </c>
+    </row>
     <row r="8">
-      <c r="B8" s="54" t="inlineStr">
+      <c r="B8" s="55" t="inlineStr">
         <is>
           <t>Price mult →</t>
         </is>
@@ -1834,74 +1845,79 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="54" t="inlineStr">
+      <c r="B9" s="55" t="inlineStr">
         <is>
           <t>Gross $m →</t>
         </is>
       </c>
-      <c r="C9" s="55">
+      <c r="C9" s="56">
         <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*C8</f>
         <v/>
       </c>
-      <c r="D9" s="55">
+      <c r="D9" s="56">
         <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*D8</f>
         <v/>
       </c>
-      <c r="E9" s="55">
+      <c r="E9" s="56">
         <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*E8</f>
         <v/>
       </c>
-      <c r="F9" s="55">
+      <c r="F9" s="56">
         <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*F8</f>
         <v/>
       </c>
-      <c r="G9" s="55">
+      <c r="G9" s="56">
         <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*G8</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="56" t="inlineStr">
-        <is>
-          <t>Success ↓</t>
-        </is>
-      </c>
-      <c r="C10" s="56" t="inlineStr">
+      <c r="B10" s="57" t="inlineStr">
+        <is>
+          <t>DA gate ↓</t>
+        </is>
+      </c>
+      <c r="C10" s="57" t="inlineStr">
         <is>
           <t>MOIC</t>
         </is>
       </c>
-      <c r="D10" s="56" t="inlineStr">
+      <c r="D10" s="57" t="inlineStr">
         <is>
           <t>MOIC</t>
         </is>
       </c>
-      <c r="E10" s="56" t="inlineStr">
+      <c r="E10" s="57" t="inlineStr">
         <is>
           <t>MOIC</t>
         </is>
       </c>
-      <c r="F10" s="56" t="inlineStr">
+      <c r="F10" s="57" t="inlineStr">
         <is>
           <t>MOIC</t>
         </is>
       </c>
-      <c r="G10" s="56" t="inlineStr">
+      <c r="G10" s="57" t="inlineStr">
         <is>
           <t>MOIC</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
+          <t>Flip succ</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
           <t>Started</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>Total dev</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>Invested</t>
         </is>
@@ -1909,186 +1925,206 @@
     </row>
     <row r="11">
       <c r="B11" s="24" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C11" s="57">
-        <f>IFERROR((C$9-'Sensitivity'!$B$4*MAX(0,(C$9-$J11)-$J11*'Sensitivity'!$B$5))/$J11,0)</f>
-        <v/>
-      </c>
-      <c r="D11" s="57">
-        <f>IFERROR((D$9-'Sensitivity'!$B$4*MAX(0,(D$9-$J11)-$J11*'Sensitivity'!$B$5))/$J11,0)</f>
-        <v/>
-      </c>
-      <c r="E11" s="57">
-        <f>IFERROR((E$9-'Sensitivity'!$B$4*MAX(0,(E$9-$J11)-$J11*'Sensitivity'!$B$5))/$J11,0)</f>
-        <v/>
-      </c>
-      <c r="F11" s="57">
-        <f>IFERROR((F$9-'Sensitivity'!$B$4*MAX(0,(F$9-$J11)-$J11*'Sensitivity'!$B$5))/$J11,0)</f>
-        <v/>
-      </c>
-      <c r="G11" s="57">
-        <f>IFERROR((G$9-'Sensitivity'!$B$4*MAX(0,(G$9-$J11)-$J11*'Sensitivity'!$B$5))/$J11,0)</f>
-        <v/>
-      </c>
-      <c r="H11" s="46">
-        <f>IFERROR('Inputs'!$C$10/$B11,0)</f>
+        <v>0.4</v>
+      </c>
+      <c r="C11" s="58">
+        <f>IFERROR((C$9-'Sensitivity'!$B$4*MAX(0,(C$9-$K11)-$K11*'Sensitivity'!$B$5))/$K11,0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="58">
+        <f>IFERROR((D$9-'Sensitivity'!$B$4*MAX(0,(D$9-$K11)-$K11*'Sensitivity'!$B$5))/$K11,0)</f>
+        <v/>
+      </c>
+      <c r="E11" s="58">
+        <f>IFERROR((E$9-'Sensitivity'!$B$4*MAX(0,(E$9-$K11)-$K11*'Sensitivity'!$B$5))/$K11,0)</f>
+        <v/>
+      </c>
+      <c r="F11" s="58">
+        <f>IFERROR((F$9-'Sensitivity'!$B$4*MAX(0,(F$9-$K11)-$K11*'Sensitivity'!$B$5))/$K11,0)</f>
+        <v/>
+      </c>
+      <c r="G11" s="58">
+        <f>IFERROR((G$9-'Sensitivity'!$B$4*MAX(0,(G$9-$K11)-$K11*'Sensitivity'!$B$5))/$K11,0)</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>$B11*'Sensitivity'!$B$7</f>
         <v/>
       </c>
       <c r="I11" s="47">
-        <f>'Inputs'!$C$10*'Inputs'!$C$17+(H11-'Inputs'!$C$10)*'Inputs'!$C$18*'Inputs'!$C$17</f>
-        <v/>
-      </c>
-      <c r="J11" s="47">
-        <f>I11+'Sensitivity'!$B$6</f>
+        <f>IFERROR('Inputs'!$C$10/H11,0)</f>
+        <v/>
+      </c>
+      <c r="J11" s="48">
+        <f>'Inputs'!$C$10*'Inputs'!$C$17+(I11-'Inputs'!$C$10)*'Inputs'!$C$18*'Inputs'!$C$17</f>
+        <v/>
+      </c>
+      <c r="K11" s="48">
+        <f>J11+'Sensitivity'!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="24" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="C12" s="57">
-        <f>IFERROR((C$9-'Sensitivity'!$B$4*MAX(0,(C$9-$J12)-$J12*'Sensitivity'!$B$5))/$J12,0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="57">
-        <f>IFERROR((D$9-'Sensitivity'!$B$4*MAX(0,(D$9-$J12)-$J12*'Sensitivity'!$B$5))/$J12,0)</f>
-        <v/>
-      </c>
-      <c r="E12" s="57">
-        <f>IFERROR((E$9-'Sensitivity'!$B$4*MAX(0,(E$9-$J12)-$J12*'Sensitivity'!$B$5))/$J12,0)</f>
-        <v/>
-      </c>
-      <c r="F12" s="57">
-        <f>IFERROR((F$9-'Sensitivity'!$B$4*MAX(0,(F$9-$J12)-$J12*'Sensitivity'!$B$5))/$J12,0)</f>
-        <v/>
-      </c>
-      <c r="G12" s="57">
-        <f>IFERROR((G$9-'Sensitivity'!$B$4*MAX(0,(G$9-$J12)-$J12*'Sensitivity'!$B$5))/$J12,0)</f>
-        <v/>
-      </c>
-      <c r="H12" s="46">
-        <f>IFERROR('Inputs'!$C$10/$B12,0)</f>
+        <v>0.55</v>
+      </c>
+      <c r="C12" s="58">
+        <f>IFERROR((C$9-'Sensitivity'!$B$4*MAX(0,(C$9-$K12)-$K12*'Sensitivity'!$B$5))/$K12,0)</f>
+        <v/>
+      </c>
+      <c r="D12" s="58">
+        <f>IFERROR((D$9-'Sensitivity'!$B$4*MAX(0,(D$9-$K12)-$K12*'Sensitivity'!$B$5))/$K12,0)</f>
+        <v/>
+      </c>
+      <c r="E12" s="58">
+        <f>IFERROR((E$9-'Sensitivity'!$B$4*MAX(0,(E$9-$K12)-$K12*'Sensitivity'!$B$5))/$K12,0)</f>
+        <v/>
+      </c>
+      <c r="F12" s="58">
+        <f>IFERROR((F$9-'Sensitivity'!$B$4*MAX(0,(F$9-$K12)-$K12*'Sensitivity'!$B$5))/$K12,0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="58">
+        <f>IFERROR((G$9-'Sensitivity'!$B$4*MAX(0,(G$9-$K12)-$K12*'Sensitivity'!$B$5))/$K12,0)</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>$B12*'Sensitivity'!$B$7</f>
         <v/>
       </c>
       <c r="I12" s="47">
-        <f>'Inputs'!$C$10*'Inputs'!$C$17+(H12-'Inputs'!$C$10)*'Inputs'!$C$18*'Inputs'!$C$17</f>
-        <v/>
-      </c>
-      <c r="J12" s="47">
-        <f>I12+'Sensitivity'!$B$6</f>
+        <f>IFERROR('Inputs'!$C$10/H12,0)</f>
+        <v/>
+      </c>
+      <c r="J12" s="48">
+        <f>'Inputs'!$C$10*'Inputs'!$C$17+(I12-'Inputs'!$C$10)*'Inputs'!$C$18*'Inputs'!$C$17</f>
+        <v/>
+      </c>
+      <c r="K12" s="48">
+        <f>J12+'Sensitivity'!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="24" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="C13" s="57">
-        <f>IFERROR((C$9-'Sensitivity'!$B$4*MAX(0,(C$9-$J13)-$J13*'Sensitivity'!$B$5))/$J13,0)</f>
-        <v/>
-      </c>
-      <c r="D13" s="57">
-        <f>IFERROR((D$9-'Sensitivity'!$B$4*MAX(0,(D$9-$J13)-$J13*'Sensitivity'!$B$5))/$J13,0)</f>
-        <v/>
-      </c>
-      <c r="E13" s="57">
-        <f>IFERROR((E$9-'Sensitivity'!$B$4*MAX(0,(E$9-$J13)-$J13*'Sensitivity'!$B$5))/$J13,0)</f>
-        <v/>
-      </c>
-      <c r="F13" s="57">
-        <f>IFERROR((F$9-'Sensitivity'!$B$4*MAX(0,(F$9-$J13)-$J13*'Sensitivity'!$B$5))/$J13,0)</f>
-        <v/>
-      </c>
-      <c r="G13" s="57">
-        <f>IFERROR((G$9-'Sensitivity'!$B$4*MAX(0,(G$9-$J13)-$J13*'Sensitivity'!$B$5))/$J13,0)</f>
-        <v/>
-      </c>
-      <c r="H13" s="46">
-        <f>IFERROR('Inputs'!$C$10/$B13,0)</f>
+        <v>0.65</v>
+      </c>
+      <c r="C13" s="58">
+        <f>IFERROR((C$9-'Sensitivity'!$B$4*MAX(0,(C$9-$K13)-$K13*'Sensitivity'!$B$5))/$K13,0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="58">
+        <f>IFERROR((D$9-'Sensitivity'!$B$4*MAX(0,(D$9-$K13)-$K13*'Sensitivity'!$B$5))/$K13,0)</f>
+        <v/>
+      </c>
+      <c r="E13" s="58">
+        <f>IFERROR((E$9-'Sensitivity'!$B$4*MAX(0,(E$9-$K13)-$K13*'Sensitivity'!$B$5))/$K13,0)</f>
+        <v/>
+      </c>
+      <c r="F13" s="58">
+        <f>IFERROR((F$9-'Sensitivity'!$B$4*MAX(0,(F$9-$K13)-$K13*'Sensitivity'!$B$5))/$K13,0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="58">
+        <f>IFERROR((G$9-'Sensitivity'!$B$4*MAX(0,(G$9-$K13)-$K13*'Sensitivity'!$B$5))/$K13,0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>$B13*'Sensitivity'!$B$7</f>
         <v/>
       </c>
       <c r="I13" s="47">
-        <f>'Inputs'!$C$10*'Inputs'!$C$17+(H13-'Inputs'!$C$10)*'Inputs'!$C$18*'Inputs'!$C$17</f>
-        <v/>
-      </c>
-      <c r="J13" s="47">
-        <f>I13+'Sensitivity'!$B$6</f>
+        <f>IFERROR('Inputs'!$C$10/H13,0)</f>
+        <v/>
+      </c>
+      <c r="J13" s="48">
+        <f>'Inputs'!$C$10*'Inputs'!$C$17+(I13-'Inputs'!$C$10)*'Inputs'!$C$18*'Inputs'!$C$17</f>
+        <v/>
+      </c>
+      <c r="K13" s="48">
+        <f>J13+'Sensitivity'!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="24" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="C14" s="57">
-        <f>IFERROR((C$9-'Sensitivity'!$B$4*MAX(0,(C$9-$J14)-$J14*'Sensitivity'!$B$5))/$J14,0)</f>
-        <v/>
-      </c>
-      <c r="D14" s="57">
-        <f>IFERROR((D$9-'Sensitivity'!$B$4*MAX(0,(D$9-$J14)-$J14*'Sensitivity'!$B$5))/$J14,0)</f>
-        <v/>
-      </c>
-      <c r="E14" s="57">
-        <f>IFERROR((E$9-'Sensitivity'!$B$4*MAX(0,(E$9-$J14)-$J14*'Sensitivity'!$B$5))/$J14,0)</f>
-        <v/>
-      </c>
-      <c r="F14" s="57">
-        <f>IFERROR((F$9-'Sensitivity'!$B$4*MAX(0,(F$9-$J14)-$J14*'Sensitivity'!$B$5))/$J14,0)</f>
-        <v/>
-      </c>
-      <c r="G14" s="57">
-        <f>IFERROR((G$9-'Sensitivity'!$B$4*MAX(0,(G$9-$J14)-$J14*'Sensitivity'!$B$5))/$J14,0)</f>
-        <v/>
-      </c>
-      <c r="H14" s="46">
-        <f>IFERROR('Inputs'!$C$10/$B14,0)</f>
+        <v>0.8</v>
+      </c>
+      <c r="C14" s="58">
+        <f>IFERROR((C$9-'Sensitivity'!$B$4*MAX(0,(C$9-$K14)-$K14*'Sensitivity'!$B$5))/$K14,0)</f>
+        <v/>
+      </c>
+      <c r="D14" s="58">
+        <f>IFERROR((D$9-'Sensitivity'!$B$4*MAX(0,(D$9-$K14)-$K14*'Sensitivity'!$B$5))/$K14,0)</f>
+        <v/>
+      </c>
+      <c r="E14" s="58">
+        <f>IFERROR((E$9-'Sensitivity'!$B$4*MAX(0,(E$9-$K14)-$K14*'Sensitivity'!$B$5))/$K14,0)</f>
+        <v/>
+      </c>
+      <c r="F14" s="58">
+        <f>IFERROR((F$9-'Sensitivity'!$B$4*MAX(0,(F$9-$K14)-$K14*'Sensitivity'!$B$5))/$K14,0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="58">
+        <f>IFERROR((G$9-'Sensitivity'!$B$4*MAX(0,(G$9-$K14)-$K14*'Sensitivity'!$B$5))/$K14,0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>$B14*'Sensitivity'!$B$7</f>
         <v/>
       </c>
       <c r="I14" s="47">
-        <f>'Inputs'!$C$10*'Inputs'!$C$17+(H14-'Inputs'!$C$10)*'Inputs'!$C$18*'Inputs'!$C$17</f>
-        <v/>
-      </c>
-      <c r="J14" s="47">
-        <f>I14+'Sensitivity'!$B$6</f>
+        <f>IFERROR('Inputs'!$C$10/H14,0)</f>
+        <v/>
+      </c>
+      <c r="J14" s="48">
+        <f>'Inputs'!$C$10*'Inputs'!$C$17+(I14-'Inputs'!$C$10)*'Inputs'!$C$18*'Inputs'!$C$17</f>
+        <v/>
+      </c>
+      <c r="K14" s="48">
+        <f>J14+'Sensitivity'!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C15" s="57">
-        <f>IFERROR((C$9-'Sensitivity'!$B$4*MAX(0,(C$9-$J15)-$J15*'Sensitivity'!$B$5))/$J15,0)</f>
-        <v/>
-      </c>
-      <c r="D15" s="57">
-        <f>IFERROR((D$9-'Sensitivity'!$B$4*MAX(0,(D$9-$J15)-$J15*'Sensitivity'!$B$5))/$J15,0)</f>
-        <v/>
-      </c>
-      <c r="E15" s="57">
-        <f>IFERROR((E$9-'Sensitivity'!$B$4*MAX(0,(E$9-$J15)-$J15*'Sensitivity'!$B$5))/$J15,0)</f>
-        <v/>
-      </c>
-      <c r="F15" s="57">
-        <f>IFERROR((F$9-'Sensitivity'!$B$4*MAX(0,(F$9-$J15)-$J15*'Sensitivity'!$B$5))/$J15,0)</f>
-        <v/>
-      </c>
-      <c r="G15" s="57">
-        <f>IFERROR((G$9-'Sensitivity'!$B$4*MAX(0,(G$9-$J15)-$J15*'Sensitivity'!$B$5))/$J15,0)</f>
-        <v/>
-      </c>
-      <c r="H15" s="46">
-        <f>IFERROR('Inputs'!$C$10/$B15,0)</f>
+        <v>0.95</v>
+      </c>
+      <c r="C15" s="58">
+        <f>IFERROR((C$9-'Sensitivity'!$B$4*MAX(0,(C$9-$K15)-$K15*'Sensitivity'!$B$5))/$K15,0)</f>
+        <v/>
+      </c>
+      <c r="D15" s="58">
+        <f>IFERROR((D$9-'Sensitivity'!$B$4*MAX(0,(D$9-$K15)-$K15*'Sensitivity'!$B$5))/$K15,0)</f>
+        <v/>
+      </c>
+      <c r="E15" s="58">
+        <f>IFERROR((E$9-'Sensitivity'!$B$4*MAX(0,(E$9-$K15)-$K15*'Sensitivity'!$B$5))/$K15,0)</f>
+        <v/>
+      </c>
+      <c r="F15" s="58">
+        <f>IFERROR((F$9-'Sensitivity'!$B$4*MAX(0,(F$9-$K15)-$K15*'Sensitivity'!$B$5))/$K15,0)</f>
+        <v/>
+      </c>
+      <c r="G15" s="58">
+        <f>IFERROR((G$9-'Sensitivity'!$B$4*MAX(0,(G$9-$K15)-$K15*'Sensitivity'!$B$5))/$K15,0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>$B15*'Sensitivity'!$B$7</f>
         <v/>
       </c>
       <c r="I15" s="47">
-        <f>'Inputs'!$C$10*'Inputs'!$C$17+(H15-'Inputs'!$C$10)*'Inputs'!$C$18*'Inputs'!$C$17</f>
-        <v/>
-      </c>
-      <c r="J15" s="47">
-        <f>I15+'Sensitivity'!$B$6</f>
+        <f>IFERROR('Inputs'!$C$10/H15,0)</f>
+        <v/>
+      </c>
+      <c r="J15" s="48">
+        <f>'Inputs'!$C$10*'Inputs'!$C$17+(I15-'Inputs'!$C$10)*'Inputs'!$C$18*'Inputs'!$C$17</f>
+        <v/>
+      </c>
+      <c r="K15" s="48">
+        <f>J15+'Sensitivity'!$B$6</f>
         <v/>
       </c>
     </row>
@@ -2154,7 +2190,7 @@
           <t>Every gate probability ∈ [0,1]</t>
         </is>
       </c>
-      <c r="B4" s="35">
+      <c r="B4" s="36">
         <f>IF(AND(MIN('Inputs'!$C$22:$C$24)&gt;=0,MAX('Inputs'!$C$22:$C$24)&lt;=1),"OK","ERROR")</f>
         <v/>
       </c>
@@ -2167,10 +2203,10 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Independent cumulative ≤ each gate</t>
-        </is>
-      </c>
-      <c r="B5" s="35">
+          <t>Flip success ≤ each gate</t>
+        </is>
+      </c>
+      <c r="B5" s="36">
         <f>IF('Calc_Survival'!$C$7&lt;=MIN('Calc_Survival'!$B$4:$B$6)+0.000001,"OK","ERROR")</f>
         <v/>
       </c>
@@ -2186,7 +2222,7 @@
           <t>All MW positive</t>
         </is>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="36">
         <f>IF(MIN('Inputs'!$D$36:$D$41)&gt;0,"OK","ERROR")</f>
         <v/>
       </c>
@@ -2202,7 +2238,7 @@
           <t>All RTB sale values positive</t>
         </is>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="36">
         <f>IF(MIN('Calc_Project_rNPV'!$G$4:$G$9)&gt;0,"OK","ERROR")</f>
         <v/>
       </c>
@@ -2218,7 +2254,7 @@
           <t>Dev cost positive</t>
         </is>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="36">
         <f>IF('Inputs'!$C$17&gt;0,"OK","ERROR")</f>
         <v/>
       </c>
@@ -2234,7 +2270,7 @@
           <t>Scenario switch ∈ {1,2,3}</t>
         </is>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="36">
         <f>IF(AND('Scenarios'!$B$2&gt;=1,'Scenarios'!$B$2&lt;=3),"OK","ERROR")</f>
         <v/>
       </c>
@@ -2247,10 +2283,10 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>Scenario success monotonic</t>
-        </is>
-      </c>
-      <c r="B10" s="35">
+          <t>Scenario DA-gate monotonic</t>
+        </is>
+      </c>
+      <c r="B10" s="36">
         <f>IF(AND('Scenarios'!$B$5&lt;='Scenarios'!$C$5,'Scenarios'!$C$5&lt;='Scenarios'!$D$5),"OK","ERROR")</f>
         <v/>
       </c>
@@ -2266,7 +2302,7 @@
           <t>Investor IRR monotonic</t>
         </is>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="36">
         <f>IF(AND('Returns'!$B$19&lt;='Returns'!$C$19,'Returns'!$C$19&lt;='Returns'!$D$19),"OK","ERROR")</f>
         <v/>
       </c>
@@ -2282,7 +2318,7 @@
           <t>Scenario weights sum to 100%</t>
         </is>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="36">
         <f>IF(ABS('Scenarios'!$E$13-1)&lt;0.001,"OK","ERROR")</f>
         <v/>
       </c>
@@ -2298,7 +2334,7 @@
           <t>Capital-call profile sums to 100%</t>
         </is>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="36">
         <f>IF(ABS(SUM('Inputs'!$C$32:$F$32)-1)&lt;0.001,"OK","ERROR")</f>
         <v/>
       </c>
@@ -2314,7 +2350,7 @@
           <t>Distribution profile sums to 100%</t>
         </is>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="36">
         <f>IF(ABS(SUM('Inputs'!$C$33:$F$33)-1)&lt;0.001,"OK","ERROR")</f>
         <v/>
       </c>
@@ -2330,7 +2366,7 @@
           <t>First-Chicago IRR within scenario range</t>
         </is>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="36">
         <f>IF(AND(G15&gt;=E15-0.0001,G15&lt;=F15+0.0001),"OK","ERROR")</f>
         <v/>
       </c>
@@ -2339,15 +2375,15 @@
           <t>Weighting sanity (helpers E:G)</t>
         </is>
       </c>
-      <c r="E15" s="58">
+      <c r="E15" s="59">
         <f>MIN('Returns'!$B$19:$D$19)</f>
         <v/>
       </c>
-      <c r="F15" s="58">
+      <c r="F15" s="59">
         <f>MAX('Returns'!$B$19:$D$19)</f>
         <v/>
       </c>
-      <c r="G15" s="50">
+      <c r="G15" s="51">
         <f>'Returns'!$E$24</f>
         <v/>
       </c>
@@ -2358,7 +2394,7 @@
           <t>Invested capital positive (all scenarios)</t>
         </is>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="36">
         <f>IF(MIN('Returns'!$B$13:$D$13)&gt;0,"OK","ERROR")</f>
         <v/>
       </c>
@@ -2374,7 +2410,7 @@
           <t>No error cells in key outputs</t>
         </is>
       </c>
-      <c r="B17" s="35">
+      <c r="B17" s="36">
         <f>IF(SUM(E17:G17)=0,"OK","ERROR")</f>
         <v/>
       </c>
@@ -2383,15 +2419,15 @@
           <t>#REF!/#DIV0! scan</t>
         </is>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="36">
         <f>SUMPRODUCT(--ISERROR('Calc_Project_rNPV'!$M$4:$M$10))</f>
         <v/>
       </c>
-      <c r="F17" s="35">
+      <c r="F17" s="36">
         <f>SUMPRODUCT(--ISERROR('Returns'!$B$19:$D$19))</f>
         <v/>
       </c>
-      <c r="G17" s="35">
+      <c r="G17" s="36">
         <f>SUMPRODUCT(--ISERROR('Sensitivity'!$C$11:$G$15))</f>
         <v/>
       </c>
@@ -2402,7 +2438,7 @@
           <t>MASTER CHECK</t>
         </is>
       </c>
-      <c r="B19" s="59">
+      <c r="B19" s="60">
         <f>IF(COUNTIF(B4:B17,"ERROR")=0,"OK","ERROR")</f>
         <v/>
       </c>
@@ -2474,7 +2510,7 @@
           <t>Master check</t>
         </is>
       </c>
-      <c r="E4" s="60">
+      <c r="E4" s="61">
         <f>'Checks'!$B$19</f>
         <v/>
       </c>
@@ -2497,7 +2533,7 @@
           <t>Expected IRR (after fees)</t>
         </is>
       </c>
-      <c r="B7" s="61">
+      <c r="B7" s="32">
         <f>'Returns'!$E$24</f>
         <v/>
       </c>
@@ -2506,7 +2542,7 @@
           <t>Investor IRR (live)</t>
         </is>
       </c>
-      <c r="E7" s="61">
+      <c r="E7" s="32">
         <f>'Calc_Fund'!$C$27</f>
         <v/>
       </c>
@@ -2517,7 +2553,7 @@
           <t>Expected MOIC</t>
         </is>
       </c>
-      <c r="B8" s="51">
+      <c r="B8" s="52">
         <f>'Returns'!$E$25</f>
         <v/>
       </c>
@@ -2526,7 +2562,7 @@
           <t>MOIC (live)</t>
         </is>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="52">
         <f>'Calc_Fund'!$C$23</f>
         <v/>
       </c>
@@ -2551,7 +2587,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Flip succ</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2575,20 +2611,20 @@
           <t>Conservative</t>
         </is>
       </c>
-      <c r="B12" s="32">
-        <f>'Scenarios'!$B$5</f>
-        <v/>
-      </c>
-      <c r="C12" s="32">
+      <c r="B12" s="34">
+        <f>'Scenarios'!$B$5*'Inputs'!$C$23*'Inputs'!$C$24</f>
+        <v/>
+      </c>
+      <c r="C12" s="33">
         <f>'Returns'!$B$19</f>
         <v/>
       </c>
-      <c r="D12" s="57" t="inlineStr">
+      <c r="D12" s="58" t="inlineStr">
         <is>
           <t>Projects target</t>
         </is>
       </c>
-      <c r="E12" s="37">
+      <c r="E12" s="38">
         <f>'Inputs'!$C$10</f>
         <v/>
       </c>
@@ -2599,21 +2635,21 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="34">
+        <f>'Scenarios'!$C$5*'Inputs'!$C$23*'Inputs'!$C$24</f>
+        <v/>
+      </c>
+      <c r="C13" s="33">
+        <f>'Returns'!$C$19</f>
+        <v/>
+      </c>
+      <c r="D13" s="58" t="inlineStr">
+        <is>
+          <t>Manager headline DA gate (Base)</t>
+        </is>
+      </c>
+      <c r="E13" s="33">
         <f>'Scenarios'!$C$5</f>
-        <v/>
-      </c>
-      <c r="C13" s="32">
-        <f>'Returns'!$C$19</f>
-        <v/>
-      </c>
-      <c r="D13" s="57" t="inlineStr">
-        <is>
-          <t>Independent cum P(success)</t>
-        </is>
-      </c>
-      <c r="E13" s="32">
-        <f>'Calc_Survival'!$C$7</f>
         <v/>
       </c>
     </row>
@@ -2623,31 +2659,31 @@
           <t>Ideal</t>
         </is>
       </c>
-      <c r="B14" s="32">
-        <f>'Scenarios'!$D$5</f>
-        <v/>
-      </c>
-      <c r="C14" s="32">
+      <c r="B14" s="34">
+        <f>'Scenarios'!$D$5*'Inputs'!$C$23*'Inputs'!$C$24</f>
+        <v/>
+      </c>
+      <c r="C14" s="33">
         <f>'Returns'!$D$19</f>
         <v/>
       </c>
-      <c r="D14" s="57" t="inlineStr">
-        <is>
-          <t>Base scenario success</t>
-        </is>
-      </c>
-      <c r="E14" s="32">
-        <f>'Scenarios'!$C$5</f>
+      <c r="D14" s="58" t="inlineStr">
+        <is>
+          <t>True flip success (Base, DAxconnxsale)</t>
+        </is>
+      </c>
+      <c r="E14" s="33">
+        <f>'Calc_Survival'!$C$13</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>Optimism gap (Base − indep.)</t>
-        </is>
-      </c>
-      <c r="E15" s="32">
+          <t>Independent flip success (benchmark)</t>
+        </is>
+      </c>
+      <c r="E15" s="33">
         <f>'Calc_Survival'!$C$10</f>
         <v/>
       </c>
@@ -2662,7 +2698,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>A real, policy-backed, capital-light niche with a viable RTB exit — but conditional. Merchant risk passes to the buyer; the fund's risk is the survival curve + the RTB price. The independent success (~45%) sits BELOW the manager's Base (65%), and the Conservative case can lose capital. The single biggest risk is EXIT/BUYER risk (non-binding buyers; RTB stage), then development/approval risk. Pursue only on verified buyer depth, RTB comps, and a survivable downside.</t>
+          <t>A real, policy-backed, capital-light niche with a viable RTB exit — but the develop-and-flip economics are THIN once the gates are modelled correctly. The manager's 65% is the development-approval gate ALONE; true flip success = approval x grid connection x sale is ~36% at Base, so the expected investor return is only marginally positive and the Conservative case loses capital. The single biggest risk is EXIT/BUYER risk, then development/approval. On these numbers the flip is the WEAKEST entry — building or holding the asset earns far more (see the stage analysis). Pursue only on verified buyer depth, RTB comps and a survivable downside.</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2844,7 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>Planning approval prob (planning portals)</t>
+          <t>Development-approval prob — public benchmark</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -2884,12 +2920,12 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>RTB $/MW by state (the manager claim — independent comps needed)</t>
+          <t>RTB $/MW by state (manager claim — independent comps needed)</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3172,7 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Scenarios + switch + live case + weights</t>
+          <t>Scenarios + switch (DA gate) + live case + weights</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3187,7 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>PD-style survival curve (independent) + optimism flag</t>
+          <t>Separate gates; flip success = DA × connection × sale + flag</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3262,7 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Investor MOIC grid (success × price)</t>
+          <t>Investor MOIC grid (development approval × price)</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3386,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
@@ -3519,7 +3555,7 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
@@ -3572,7 +3608,7 @@
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
@@ -3602,7 +3638,7 @@
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
@@ -3632,7 +3668,7 @@
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
@@ -3662,7 +3698,7 @@
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
@@ -3692,7 +3728,7 @@
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
@@ -3722,7 +3758,7 @@
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
@@ -3752,7 +3788,7 @@
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
@@ -3819,7 +3855,7 @@
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
@@ -3868,14 +3904,14 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Survival gates (independent — public data)</t>
+          <t>Survival gates — SEPARATE; scenarios move ONLY development approval</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>Gate 1 — Planning approval</t>
+          <t>Development approval — public benchmark</t>
         </is>
       </c>
       <c r="C22" s="16" t="n">
@@ -3908,7 +3944,7 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>Gate 2 — Grid connection</t>
+          <t>Grid connection (separate gate)</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
@@ -3941,7 +3977,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>Gate 3 — Reach sale</t>
+          <t>Reach sale — flip exit (separate gate)</t>
         </is>
       </c>
       <c r="C24" s="16" t="n">
@@ -3994,12 +4030,12 @@
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>RTB $/MW by state (the manager claim — independent comps needed)</t>
+          <t>RTB $/MW by state (manager claim — independent comps needed)</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
@@ -4024,12 +4060,12 @@
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>RTB $/MW by state (the manager claim — independent comps needed)</t>
+          <t>RTB $/MW by state (manager claim — independent comps needed)</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G27" s="17" t="inlineStr">
@@ -4054,12 +4090,12 @@
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>RTB $/MW by state (the manager claim — independent comps needed)</t>
+          <t>RTB $/MW by state (manager claim — independent comps needed)</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr">
@@ -4096,7 +4132,7 @@
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr">
@@ -4574,7 +4610,7 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Cumulative success rate</t>
+          <t>Development-approval rate (DA gate — the 40/65/80%)</t>
         </is>
       </c>
       <c r="B5" s="24" t="n">
@@ -4631,34 +4667,14 @@
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>Discount rate override (0=use base)</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="C8" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="24" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E8" s="18">
-        <f>CHOOSE('Scenarios'!$B$2,B8,C8,D8)</f>
-        <v/>
-      </c>
-    </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Live discount rate</t>
-        </is>
-      </c>
-      <c r="E9" s="18">
-        <f>IF('Scenarios'!$E$8=0,'Inputs'!$C$7,'Scenarios'!$E$8)</f>
+          <t>Live discount rate (= base; scenarios don't move it)</t>
+        </is>
+      </c>
+      <c r="E9" s="32">
+        <f>'Inputs'!$C$7</f>
         <v/>
       </c>
     </row>
@@ -4715,7 +4731,7 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>Success rates mirror the manager's deck (40/65/80%) for comparability. The INDEPENDENT survival curve (~45%) sits below Base (65%) — see Calc_Survival. Scenarios are the analyst's to OWN.</t>
+          <t>The 40/65/80% are the DEVELOPMENT-APPROVAL gate ONLY (the manager's deck). True flip success = development approval x grid connection x sale — far below 65% (see Calc_Survival). The switch moves ONLY the DA gate; connection and sale are fixed public benchmarks. Scenarios are the analyst's to OWN.</t>
         </is>
       </c>
     </row>
@@ -4734,10 +4750,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
@@ -4745,7 +4761,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CALC — PD-STYLE SURVIVAL CURVE (independent, public data)</t>
+          <t>CALC — SURVIVAL GATES (each separate; flip success = their product)</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
@@ -4757,7 +4773,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Cumulative P(success) = product of gate probabilities — structurally a multi-period PD / survival curve (the credit-risk bridge). This is the model's INDEPENDENT estimate; the SCENARIOS set the success rate used in valuation.</t>
+          <t>The manager's 40/65/80% are the DEVELOPMENT-APPROVAL gate ONLY. True develop-and-flip success = development approval x grid connection x sale — a multi-period survival / probability-of-default curve. The DA gate is LIVE from the scenario switch; grid connection and sale are fixed public benchmarks.</t>
         </is>
       </c>
     </row>
@@ -4781,14 +4797,14 @@
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
-          <t>Gate 1 — Planning approval</t>
-        </is>
-      </c>
-      <c r="B4" s="32">
-        <f>'Inputs'!$C$22</f>
-        <v/>
-      </c>
-      <c r="C4" s="33">
+          <t>Development approval (live scenario DA gate)</t>
+        </is>
+      </c>
+      <c r="B4" s="33">
+        <f>'Scenarios'!$E$5</f>
+        <v/>
+      </c>
+      <c r="C4" s="34">
         <f>B4</f>
         <v/>
       </c>
@@ -4796,14 +4812,14 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Gate 2 — Grid connection</t>
-        </is>
-      </c>
-      <c r="B5" s="32">
+          <t>Grid connection</t>
+        </is>
+      </c>
+      <c r="B5" s="33">
         <f>'Inputs'!$C$23</f>
         <v/>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="34">
         <f>C4*B5</f>
         <v/>
       </c>
@@ -4811,14 +4827,14 @@
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>Gate 3 — Reach sale</t>
-        </is>
-      </c>
-      <c r="B6" s="32">
+          <t>Reach sale (flip exit)</t>
+        </is>
+      </c>
+      <c r="B6" s="33">
         <f>'Inputs'!$C$24</f>
         <v/>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="34">
         <f>C5*B6</f>
         <v/>
       </c>
@@ -4826,10 +4842,10 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Independent cumulative P(success)</t>
-        </is>
-      </c>
-      <c r="C7" s="34">
+          <t>LIVE flip success (DA x connection x sale)</t>
+        </is>
+      </c>
+      <c r="C7" s="35">
         <f>C6</f>
         <v/>
       </c>
@@ -4837,35 +4853,57 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>Base scenario success (the manager claim)</t>
-        </is>
-      </c>
-      <c r="C9" s="32">
-        <f>'Scenarios'!$C$5</f>
+          <t>Public-benchmark development approval</t>
+        </is>
+      </c>
+      <c r="C9" s="33">
+        <f>'Inputs'!$C$22</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Optimism gap (Base − independent)</t>
+          <t>Independent flip success (benchmark DA x conn x sale)</t>
         </is>
       </c>
       <c r="C10" s="18">
-        <f>C9-'Calc_Survival'!$C$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" s="35">
-        <f>IF(C10&gt;0.05,"FLAG: Base optimistic","ok")</f>
+        <f>C9*'Inputs'!$C$23*'Inputs'!$C$24</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>Independent ~45% sits BELOW the manager's Base (65%): treat Base as optimistic; ask for sub-5MW, per-state evidence. The sub-5MW AEMO registration exemption MAY lift small-distribution success above the large-project benchmark — verify.</t>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Manager's headline DA rate (Base — the '65%')</t>
+        </is>
+      </c>
+      <c r="C12" s="33">
+        <f>'Scenarios'!$C$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>True flip success at that DA (DA x conn x sale)</t>
+        </is>
+      </c>
+      <c r="C13" s="18">
+        <f>'Scenarios'!$C$5*'Inputs'!$C$23*'Inputs'!$C$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="36">
+        <f>IF(C13&lt;C12,"FLAG: 65% is the DA gate only","ok")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>The 65% headline is the approval gate alone; after grid connection (~70%) and sale (~80%) the true flip success is ~36%. The DA gate is the master return driver — the scenarios move it 40/65/80%. The sub-5MW AEMO registration exemption MAY lift small-distribution success — verify per state.</t>
         </is>
       </c>
     </row>
@@ -4999,55 +5037,55 @@
         <f>'Inputs'!$A$36</f>
         <v/>
       </c>
-      <c r="B4" s="36">
+      <c r="B4" s="37">
         <f>'Inputs'!$B$36</f>
         <v/>
       </c>
-      <c r="C4" s="37">
+      <c r="C4" s="38">
         <f>'Inputs'!$D$36</f>
         <v/>
       </c>
-      <c r="D4" s="38">
+      <c r="D4" s="39">
         <f>'Inputs'!$G$36</f>
         <v/>
       </c>
-      <c r="E4" s="39">
+      <c r="E4" s="40">
         <f>IFERROR(INDEX('Inputs'!$C$26:$C$28,MATCH(B4,'Inputs'!$A$26:$A$28,0)),0)</f>
         <v/>
       </c>
-      <c r="F4" s="40">
+      <c r="F4" s="41">
         <f>'Scenarios'!$E$6</f>
         <v/>
       </c>
-      <c r="G4" s="41">
+      <c r="G4" s="42">
         <f>C4*E4*F4</f>
         <v/>
       </c>
-      <c r="H4" s="41">
+      <c r="H4" s="42">
         <f>'Inputs'!$C$17*'Scenarios'!$E$7</f>
         <v/>
       </c>
-      <c r="I4" s="41">
+      <c r="I4" s="42">
         <f>G4-H4</f>
         <v/>
       </c>
-      <c r="J4" s="32">
-        <f>'Scenarios'!$E$5</f>
-        <v/>
-      </c>
-      <c r="K4" s="41">
+      <c r="J4" s="33">
+        <f>'Calc_Survival'!$C$7</f>
+        <v/>
+      </c>
+      <c r="K4" s="42">
         <f>I4*J4</f>
         <v/>
       </c>
-      <c r="L4" s="42">
+      <c r="L4" s="43">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^D4,0)</f>
         <v/>
       </c>
-      <c r="M4" s="41">
+      <c r="M4" s="42">
         <f>K4*L4</f>
         <v/>
       </c>
-      <c r="N4" s="41">
+      <c r="N4" s="42">
         <f>C4*E4</f>
         <v/>
       </c>
@@ -5057,55 +5095,55 @@
         <f>'Inputs'!$A$37</f>
         <v/>
       </c>
-      <c r="B5" s="36">
+      <c r="B5" s="37">
         <f>'Inputs'!$B$37</f>
         <v/>
       </c>
-      <c r="C5" s="37">
+      <c r="C5" s="38">
         <f>'Inputs'!$D$37</f>
         <v/>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="39">
         <f>'Inputs'!$G$37</f>
         <v/>
       </c>
-      <c r="E5" s="39">
+      <c r="E5" s="40">
         <f>IFERROR(INDEX('Inputs'!$C$26:$C$28,MATCH(B5,'Inputs'!$A$26:$A$28,0)),0)</f>
         <v/>
       </c>
-      <c r="F5" s="40">
+      <c r="F5" s="41">
         <f>'Scenarios'!$E$6</f>
         <v/>
       </c>
-      <c r="G5" s="41">
+      <c r="G5" s="42">
         <f>C5*E5*F5</f>
         <v/>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="42">
         <f>'Inputs'!$C$17*'Scenarios'!$E$7</f>
         <v/>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="42">
         <f>G5-H5</f>
         <v/>
       </c>
-      <c r="J5" s="32">
-        <f>'Scenarios'!$E$5</f>
-        <v/>
-      </c>
-      <c r="K5" s="41">
+      <c r="J5" s="33">
+        <f>'Calc_Survival'!$C$7</f>
+        <v/>
+      </c>
+      <c r="K5" s="42">
         <f>I5*J5</f>
         <v/>
       </c>
-      <c r="L5" s="42">
+      <c r="L5" s="43">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^D5,0)</f>
         <v/>
       </c>
-      <c r="M5" s="41">
+      <c r="M5" s="42">
         <f>K5*L5</f>
         <v/>
       </c>
-      <c r="N5" s="41">
+      <c r="N5" s="42">
         <f>C5*E5</f>
         <v/>
       </c>
@@ -5115,55 +5153,55 @@
         <f>'Inputs'!$A$38</f>
         <v/>
       </c>
-      <c r="B6" s="36">
+      <c r="B6" s="37">
         <f>'Inputs'!$B$38</f>
         <v/>
       </c>
-      <c r="C6" s="37">
+      <c r="C6" s="38">
         <f>'Inputs'!$D$38</f>
         <v/>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="39">
         <f>'Inputs'!$G$38</f>
         <v/>
       </c>
-      <c r="E6" s="39">
+      <c r="E6" s="40">
         <f>IFERROR(INDEX('Inputs'!$C$26:$C$28,MATCH(B6,'Inputs'!$A$26:$A$28,0)),0)</f>
         <v/>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="41">
         <f>'Scenarios'!$E$6</f>
         <v/>
       </c>
-      <c r="G6" s="41">
+      <c r="G6" s="42">
         <f>C6*E6*F6</f>
         <v/>
       </c>
-      <c r="H6" s="41">
+      <c r="H6" s="42">
         <f>'Inputs'!$C$17*'Scenarios'!$E$7</f>
         <v/>
       </c>
-      <c r="I6" s="41">
+      <c r="I6" s="42">
         <f>G6-H6</f>
         <v/>
       </c>
-      <c r="J6" s="32">
-        <f>'Scenarios'!$E$5</f>
-        <v/>
-      </c>
-      <c r="K6" s="41">
+      <c r="J6" s="33">
+        <f>'Calc_Survival'!$C$7</f>
+        <v/>
+      </c>
+      <c r="K6" s="42">
         <f>I6*J6</f>
         <v/>
       </c>
-      <c r="L6" s="42">
+      <c r="L6" s="43">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^D6,0)</f>
         <v/>
       </c>
-      <c r="M6" s="41">
+      <c r="M6" s="42">
         <f>K6*L6</f>
         <v/>
       </c>
-      <c r="N6" s="41">
+      <c r="N6" s="42">
         <f>C6*E6</f>
         <v/>
       </c>
@@ -5173,55 +5211,55 @@
         <f>'Inputs'!$A$39</f>
         <v/>
       </c>
-      <c r="B7" s="36">
+      <c r="B7" s="37">
         <f>'Inputs'!$B$39</f>
         <v/>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="38">
         <f>'Inputs'!$D$39</f>
         <v/>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="39">
         <f>'Inputs'!$G$39</f>
         <v/>
       </c>
-      <c r="E7" s="39">
+      <c r="E7" s="40">
         <f>IFERROR(INDEX('Inputs'!$C$26:$C$28,MATCH(B7,'Inputs'!$A$26:$A$28,0)),0)</f>
         <v/>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="41">
         <f>'Scenarios'!$E$6</f>
         <v/>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="42">
         <f>C7*E7*F7</f>
         <v/>
       </c>
-      <c r="H7" s="41">
+      <c r="H7" s="42">
         <f>'Inputs'!$C$17*'Scenarios'!$E$7</f>
         <v/>
       </c>
-      <c r="I7" s="41">
+      <c r="I7" s="42">
         <f>G7-H7</f>
         <v/>
       </c>
-      <c r="J7" s="32">
-        <f>'Scenarios'!$E$5</f>
-        <v/>
-      </c>
-      <c r="K7" s="41">
+      <c r="J7" s="33">
+        <f>'Calc_Survival'!$C$7</f>
+        <v/>
+      </c>
+      <c r="K7" s="42">
         <f>I7*J7</f>
         <v/>
       </c>
-      <c r="L7" s="42">
+      <c r="L7" s="43">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^D7,0)</f>
         <v/>
       </c>
-      <c r="M7" s="41">
+      <c r="M7" s="42">
         <f>K7*L7</f>
         <v/>
       </c>
-      <c r="N7" s="41">
+      <c r="N7" s="42">
         <f>C7*E7</f>
         <v/>
       </c>
@@ -5231,55 +5269,55 @@
         <f>'Inputs'!$A$40</f>
         <v/>
       </c>
-      <c r="B8" s="36">
+      <c r="B8" s="37">
         <f>'Inputs'!$B$40</f>
         <v/>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="38">
         <f>'Inputs'!$D$40</f>
         <v/>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="39">
         <f>'Inputs'!$G$40</f>
         <v/>
       </c>
-      <c r="E8" s="39">
+      <c r="E8" s="40">
         <f>IFERROR(INDEX('Inputs'!$C$26:$C$28,MATCH(B8,'Inputs'!$A$26:$A$28,0)),0)</f>
         <v/>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="41">
         <f>'Scenarios'!$E$6</f>
         <v/>
       </c>
-      <c r="G8" s="41">
+      <c r="G8" s="42">
         <f>C8*E8*F8</f>
         <v/>
       </c>
-      <c r="H8" s="41">
+      <c r="H8" s="42">
         <f>'Inputs'!$C$17*'Scenarios'!$E$7</f>
         <v/>
       </c>
-      <c r="I8" s="41">
+      <c r="I8" s="42">
         <f>G8-H8</f>
         <v/>
       </c>
-      <c r="J8" s="32">
-        <f>'Scenarios'!$E$5</f>
-        <v/>
-      </c>
-      <c r="K8" s="41">
+      <c r="J8" s="33">
+        <f>'Calc_Survival'!$C$7</f>
+        <v/>
+      </c>
+      <c r="K8" s="42">
         <f>I8*J8</f>
         <v/>
       </c>
-      <c r="L8" s="42">
+      <c r="L8" s="43">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^D8,0)</f>
         <v/>
       </c>
-      <c r="M8" s="41">
+      <c r="M8" s="42">
         <f>K8*L8</f>
         <v/>
       </c>
-      <c r="N8" s="41">
+      <c r="N8" s="42">
         <f>C8*E8</f>
         <v/>
       </c>
@@ -5289,55 +5327,55 @@
         <f>'Inputs'!$A$41</f>
         <v/>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="37">
         <f>'Inputs'!$B$41</f>
         <v/>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="38">
         <f>'Inputs'!$D$41</f>
         <v/>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="39">
         <f>'Inputs'!$G$41</f>
         <v/>
       </c>
-      <c r="E9" s="39">
+      <c r="E9" s="40">
         <f>IFERROR(INDEX('Inputs'!$C$26:$C$28,MATCH(B9,'Inputs'!$A$26:$A$28,0)),0)</f>
         <v/>
       </c>
-      <c r="F9" s="40">
+      <c r="F9" s="41">
         <f>'Scenarios'!$E$6</f>
         <v/>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="42">
         <f>C9*E9*F9</f>
         <v/>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="42">
         <f>'Inputs'!$C$17*'Scenarios'!$E$7</f>
         <v/>
       </c>
-      <c r="I9" s="41">
+      <c r="I9" s="42">
         <f>G9-H9</f>
         <v/>
       </c>
-      <c r="J9" s="32">
-        <f>'Scenarios'!$E$5</f>
-        <v/>
-      </c>
-      <c r="K9" s="41">
+      <c r="J9" s="33">
+        <f>'Calc_Survival'!$C$7</f>
+        <v/>
+      </c>
+      <c r="K9" s="42">
         <f>I9*J9</f>
         <v/>
       </c>
-      <c r="L9" s="42">
+      <c r="L9" s="43">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^D9,0)</f>
         <v/>
       </c>
-      <c r="M9" s="41">
+      <c r="M9" s="42">
         <f>K9*L9</f>
         <v/>
       </c>
-      <c r="N9" s="41">
+      <c r="N9" s="42">
         <f>C9*E9</f>
         <v/>
       </c>
@@ -5348,19 +5386,19 @@
           <t>Pipeline total (representative)</t>
         </is>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="44">
         <f>SUM(C4:C9)</f>
         <v/>
       </c>
-      <c r="G10" s="44">
+      <c r="G10" s="45">
         <f>SUM(G4:G9)</f>
         <v/>
       </c>
-      <c r="H10" s="44">
+      <c r="H10" s="45">
         <f>SUM(H4:H9)</f>
         <v/>
       </c>
-      <c r="M10" s="44">
+      <c r="M10" s="45">
         <f>SUM(M4:M9)</f>
         <v/>
       </c>
@@ -5371,7 +5409,7 @@
           <t>Blended RTB sale per project (@1x)</t>
         </is>
       </c>
-      <c r="M11" s="45">
+      <c r="M11" s="46">
         <f>AVERAGE('Calc_Project_rNPV'!$N$4:$N$9)</f>
         <v/>
       </c>
@@ -5434,8 +5472,8 @@
           <t>Live cumulative success</t>
         </is>
       </c>
-      <c r="C5" s="32">
-        <f>'Scenarios'!$E$5</f>
+      <c r="C5" s="33">
+        <f>'Calc_Survival'!$C$7</f>
         <v/>
       </c>
     </row>
@@ -5445,7 +5483,7 @@
           <t>Projects target (delivered &amp; sold)</t>
         </is>
       </c>
-      <c r="C6" s="37">
+      <c r="C6" s="38">
         <f>'Inputs'!$C$10</f>
         <v/>
       </c>
@@ -5456,7 +5494,7 @@
           <t>Projects started (funnel)</t>
         </is>
       </c>
-      <c r="C7" s="46">
+      <c r="C7" s="47">
         <f>IFERROR(C6/C5,0)</f>
         <v/>
       </c>
@@ -5467,7 +5505,7 @@
           <t>Projects failed (dropouts)</t>
         </is>
       </c>
-      <c r="C8" s="46">
+      <c r="C8" s="47">
         <f>C7-C6</f>
         <v/>
       </c>
@@ -5478,7 +5516,7 @@
           <t>Dev cost per project (live)</t>
         </is>
       </c>
-      <c r="C9" s="41">
+      <c r="C9" s="42">
         <f>'Inputs'!$C$17*'Scenarios'!$E$7</f>
         <v/>
       </c>
@@ -5489,7 +5527,7 @@
           <t>Total development cost</t>
         </is>
       </c>
-      <c r="C10" s="47">
+      <c r="C10" s="48">
         <f>C6*C9+C8*'Inputs'!$C$18*C9</f>
         <v/>
       </c>
@@ -5507,7 +5545,7 @@
           <t>Blended RTB sale per project (live)</t>
         </is>
       </c>
-      <c r="C12" s="41">
+      <c r="C12" s="42">
         <f>'Calc_Project_rNPV'!$M$11*'Scenarios'!$E$6</f>
         <v/>
       </c>
@@ -5518,7 +5556,7 @@
           <t>Gross proceeds</t>
         </is>
       </c>
-      <c r="C13" s="47">
+      <c r="C13" s="48">
         <f>C6*C12</f>
         <v/>
       </c>
@@ -5529,7 +5567,7 @@
           <t>Entry fee</t>
         </is>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="48">
         <f>'Inputs'!$C$12*'Inputs'!$C$9</f>
         <v/>
       </c>
@@ -5540,7 +5578,7 @@
           <t>Management fee (total)</t>
         </is>
       </c>
-      <c r="C15" s="47">
+      <c r="C15" s="48">
         <f>'Inputs'!$C$13*'Inputs'!$C$9*'Inputs'!$C$11</f>
         <v/>
       </c>
@@ -5551,7 +5589,7 @@
           <t>Invested capital (LP, called)</t>
         </is>
       </c>
-      <c r="C16" s="48">
+      <c r="C16" s="49">
         <f>C10+C14+C15</f>
         <v/>
       </c>
@@ -5569,7 +5607,7 @@
           <t>Profit before carry</t>
         </is>
       </c>
-      <c r="C18" s="47">
+      <c r="C18" s="48">
         <f>C13-C16</f>
         <v/>
       </c>
@@ -5580,7 +5618,7 @@
           <t>Hurdle factor = (1+hurdle)^term − 1</t>
         </is>
       </c>
-      <c r="C19" s="33">
+      <c r="C19" s="34">
         <f>(1+'Inputs'!$C$15)^'Inputs'!$C$11-1</f>
         <v/>
       </c>
@@ -5591,7 +5629,7 @@
           <t>Hurdle amount</t>
         </is>
       </c>
-      <c r="C20" s="47">
+      <c r="C20" s="48">
         <f>C16*C19</f>
         <v/>
       </c>
@@ -5602,7 +5640,7 @@
           <t>Carry to GP</t>
         </is>
       </c>
-      <c r="C21" s="47">
+      <c r="C21" s="48">
         <f>'Inputs'!$C$14*MAX(0,C18-C20)</f>
         <v/>
       </c>
@@ -5613,7 +5651,7 @@
           <t>Distributions to LP</t>
         </is>
       </c>
-      <c r="C22" s="47">
+      <c r="C22" s="48">
         <f>C13-C21</f>
         <v/>
       </c>
@@ -5624,7 +5662,7 @@
           <t>MOIC (net)</t>
         </is>
       </c>
-      <c r="C23" s="49">
+      <c r="C23" s="50">
         <f>IFERROR(C22/C16,0)</f>
         <v/>
       </c>
@@ -5635,7 +5673,7 @@
           <t>Mean distribution period (yrs)</t>
         </is>
       </c>
-      <c r="C24" s="46">
+      <c r="C24" s="47">
         <f>SUMPRODUCT('Timeline'!$B$3:$E$3,'Inputs'!$C$33:$F$33)</f>
         <v/>
       </c>
@@ -5646,7 +5684,7 @@
           <t>Mean capital-call period (yrs)</t>
         </is>
       </c>
-      <c r="C25" s="46">
+      <c r="C25" s="47">
         <f>SUMPRODUCT('Timeline'!$B$3:$E$3,'Inputs'!$C$32:$F$32)</f>
         <v/>
       </c>
@@ -5657,7 +5695,7 @@
           <t>Effective hold (yrs)</t>
         </is>
       </c>
-      <c r="C26" s="46">
+      <c r="C26" s="47">
         <f>C24-C25</f>
         <v/>
       </c>
@@ -5668,7 +5706,7 @@
           <t>Investor IRR (live, closed-form)</t>
         </is>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="35">
         <f>IFERROR(C23^(1/C26)-1,0)</f>
         <v/>
       </c>

--- a/financial_models/BESS_Valuation.xlsx
+++ b/financial_models/BESS_Valuation.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calc_Survival" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calc_Project_rNPV" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calc_Fund" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calc_Company" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Returns" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calc_CrossChecks" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="12" state="visible" r:id="rId12"/>
@@ -33,11 +33,11 @@
   <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="$#,##0.0;($#,##0.0);&quot;–&quot;"/>
-    <numFmt numFmtId="166" formatCode="$#,##0.00;($#,##0.00);&quot;–&quot;"/>
-    <numFmt numFmtId="167" formatCode="$#,##0.000"/>
-    <numFmt numFmtId="168" formatCode="#,##0.0"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="$#,##0.00;($#,##0.00);&quot;–&quot;"/>
+    <numFmt numFmtId="168" formatCode="$#,##0.000"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -154,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -193,8 +193,10 @@
     <xf numFmtId="165" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -205,7 +207,7 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -226,24 +228,25 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -253,7 +256,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -263,10 +265,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -655,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -665,7 +668,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BESS Pipeline Valuation — Develop-and-Flip (RTB)</t>
+          <t>Battery-Developer Startup Valuation — Direct-Equity Stake</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
@@ -682,7 +685,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Investor (LP) IRR/MOIC of an illustrative distribution-BESS develop-and-flip fund (NSW/VIC/SA)</t>
+          <t>Return on OUR shares (equity IRR/MOIC) in an illustrative distribution-BESS develop-and-flip startup (NSW/VIC/SA)</t>
         </is>
       </c>
     </row>
@@ -694,7 +697,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v2.0</t>
         </is>
       </c>
     </row>
@@ -706,7 +709,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Portfolio project (independent rebuild of the manager's projections claims)</t>
+          <t>Portfolio project (independent rebuild; founder/manager claims verified)</t>
         </is>
       </c>
     </row>
@@ -752,7 +755,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>'Checks'!$B$19</f>
+        <f>'Checks'!$B$20</f>
         <v/>
       </c>
     </row>
@@ -771,130 +774,142 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Whether the investor should commit as an LP to an (illustrative) develop-and-flip RTB BESS fund, and at what expected return.</t>
+          <t>Whether to buy SHARES DIRECTLY (a minority equity stake) in an (illustrative) develop-and-flip RTB battery startup, and at what expected return on our shares.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Reframe</t>
+          <t>Structure</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>The fund sells RTB before construction — MERCHANT RISK PASSES TO THE BUYER. The fund's risk is the survival curve (approve→connect→sell) + the RTB price.</t>
+          <t>We invest as a SHAREHOLDER, NOT as a fund limited partner. A cap table (pre-/post-money, ownership, dilution, 1x liquidation preference) turns the company's exit equity value into OUR return. The equity-deal terms are PLACEHOLDERS to confirm.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Outputs</t>
+          <t>Reframe</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Investor IRR &amp; MOIC by scenario, First-Chicago expected return, per-pipeline valuation range, sensitivities.</t>
+          <t>The company sells RTB before construction — MERCHANT RISK PASSES TO THE BUYER. Its risk is the survival curve (approve→connect→sell) + the RTB price; ours is also dilution and the cap-table terms.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Detail / horizon</t>
+          <t>Outputs</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Annual, ~2+1-year term, AUD, $m.</t>
+          <t>Cap table, return on our shares (equity IRR &amp; MOIC) by scenario, First-Chicago expected return, per-pipeline valuation cross-check, sensitivities.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Detail / horizon</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Company programme ~2+1-year cycle; our exit year is a placeholder. AUD, $m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Out of scope</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Post-sale operating/merchant cash flows, construction (buyer-funded), tax structuring, FX, debt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Post-sale operating/merchant cash flows, construction (buyer-funded), full multi-round waterfall, tax structuring, FX, debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Standards followed</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>FAST / ICAEW / Macabacus / Operis: Inputs→Calcs→Outputs zones; one Timeline; one-row-one-calc; no hardcodes in formulas; CHOOSE scenario switch + live-case row; checks built alongside; colour code (blue input / black formula / green link); INDEX-MATCH not VLOOKUP; IFERROR on division; closed-form IRR (no volatile functions).</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20"/>
     <row r="21"/>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="22"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Judgement inputs to OWN (review pass)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Discount rate &amp; premium • the THREE scenario success rates (vs the independent ~45%) • RTB $/MW by state (need independent comps) • dev cost per project &amp; abandonment • fees/carry/hurdle • cash-flow profile. the manager's figures are CLAIMS to verify — defend your own.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Discount rate &amp; premium • the THREE scenario success rates (vs the independent benchmark) • RTB $/MW by state (need independent comps) • dev cost per project &amp; abandonment • the equity-deal terms (pre-money, our cheque, option pool, future dilution, liquidation preference, platform exit multiple, exit year — ALL placeholders). Founder/manager figures are CLAIMS to verify — defend your own.</t>
+        </is>
+      </c>
+    </row>
     <row r="26"/>
     <row r="27"/>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="28"/>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>TO COMPLETE (analyst review pass)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>1. Trace every formula + colour audit; confirm master check = OK; stress the switch in all 3 positions.  2. Replace 🟡 BENCHMARK / manager-claim inputs with verified independent values (RTB comps, per-state success, dev cost).  3. Stress a downside where RTB prices are 20–30% lower and success ≈ the independent ~45%; confirm capital can be lost.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
+    <row r="31">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>1. Trace every formula + colour audit; confirm master check = OK; stress the switch in all 3 positions.  2. Replace BENCHMARK / claim inputs with verified independent values (RTB comps, per-state success, dev cost) and CONFIRM the cap-table terms against a term sheet.  3. Stress a downside where RTB prices are 20–30% lower and success ≈ the independent benchmark; confirm our shares can be wiped out (Conservative = total loss).</t>
+        </is>
+      </c>
+    </row>
     <row r="32"/>
     <row r="33"/>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="34"/>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>DISCLAIMER</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>ILLUSTRATIVE fund built from public benchmark data; an INDEPENDENT rebuild of the the manager's projections (not an endorsement). NOT investment advice. Wholesale-investor context; read the IM. All figures illustrative and must be independently verified. Capital is at risk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>ILLUSTRATIVE startup built from public benchmark data; an INDEPENDENT rebuild (not an endorsement). NOT investment advice. Wholesale-investor context; read the term sheet / IM. The equity-deal terms are placeholders to confirm. All figures illustrative and must be independently verified. Capital is at risk.</t>
+        </is>
+      </c>
+    </row>
     <row r="37"/>
     <row r="38"/>
+    <row r="39"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="B36:B39"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="B25:B28"/>
   </mergeCells>
   <conditionalFormatting sqref="B8">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -918,10 +933,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -931,7 +946,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RETURNS — investor IRR &amp; MOIC by scenario, First-Chicago, valuation range</t>
+          <t>RETURNS — cap table &amp; return on OUR shares by scenario, First-Chicago, valuation range</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
@@ -943,494 +958,555 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Each scenario's funnel is computed independently of the switch. Investor IRR is closed-form over the effective hold. All figures AUD $m unless stated.</t>
+          <t>We buy SHARES directly. Ownership = our investment ÷ post-money, reduced by dilution. Each scenario's company exit equity value (net programme profit × the platform exit multiple) flows through the cap table; our proceeds = the GREATER of our 1× liquidation preference or our as-converted (diluted) share. All figures AUD $m unless stated.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Investor return by scenario (after fees)</t>
+          <t>Cap table (our stake)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Conservative</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Ideal</t>
-        </is>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Pre-money valuation</t>
+        </is>
+      </c>
+      <c r="B4" s="52">
+        <f>'Inputs'!$C$13</f>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Flip success (DA x conn x sale)</t>
-        </is>
-      </c>
-      <c r="B5" s="34">
-        <f>'Scenarios'!$B$5*'Inputs'!$C$23*'Inputs'!$C$24</f>
-        <v/>
-      </c>
-      <c r="C5" s="34">
-        <f>'Scenarios'!$C$5*'Inputs'!$C$23*'Inputs'!$C$24</f>
-        <v/>
-      </c>
-      <c r="D5" s="34">
-        <f>'Scenarios'!$D$5*'Inputs'!$C$23*'Inputs'!$C$24</f>
+          <t>Our investment</t>
+        </is>
+      </c>
+      <c r="B5" s="52">
+        <f>'Inputs'!$C$14</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>RTB price multiplier</t>
-        </is>
-      </c>
-      <c r="B6" s="41">
-        <f>'Scenarios'!$B$6</f>
-        <v/>
-      </c>
-      <c r="C6" s="41">
-        <f>'Scenarios'!$C$6</f>
-        <v/>
-      </c>
-      <c r="D6" s="41">
-        <f>'Scenarios'!$D$6</f>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Post-money = pre-money + investment</t>
+        </is>
+      </c>
+      <c r="B6" s="53">
+        <f>B4+B5</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Dev cost multiplier</t>
-        </is>
-      </c>
-      <c r="B7" s="41">
-        <f>'Scenarios'!$B$7</f>
-        <v/>
-      </c>
-      <c r="C7" s="41">
-        <f>'Scenarios'!$C$7</f>
-        <v/>
-      </c>
-      <c r="D7" s="41">
-        <f>'Scenarios'!$D$7</f>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Ownership at entry = investment ÷ post-money</t>
+        </is>
+      </c>
+      <c r="B7" s="18">
+        <f>IFERROR(B5/B6,0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>Dev cost per project</t>
-        </is>
-      </c>
-      <c r="B8" s="42">
-        <f>'Inputs'!$C$17*B7</f>
-        <v/>
-      </c>
-      <c r="C8" s="42">
-        <f>'Inputs'!$C$17*C7</f>
-        <v/>
-      </c>
-      <c r="D8" s="42">
-        <f>'Inputs'!$C$17*D7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>Projects started</t>
-        </is>
-      </c>
-      <c r="B9" s="47">
-        <f>IFERROR('Inputs'!$C$10/B5,0)</f>
-        <v/>
-      </c>
-      <c r="C9" s="47">
-        <f>IFERROR('Inputs'!$C$10/C5,0)</f>
-        <v/>
-      </c>
-      <c r="D9" s="47">
-        <f>IFERROR('Inputs'!$C$10/D5,0)</f>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Ownership at exit (diluted)</t>
+        </is>
+      </c>
+      <c r="B8" s="37">
+        <f>B7*(1-'Inputs'!$C$15)*(1-'Inputs'!$C$16)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Projects failed</t>
-        </is>
-      </c>
-      <c r="B10" s="47">
-        <f>B9-'Inputs'!$C$10</f>
-        <v/>
-      </c>
-      <c r="C10" s="47">
-        <f>C9-'Inputs'!$C$10</f>
-        <v/>
-      </c>
-      <c r="D10" s="47">
-        <f>D9-'Inputs'!$C$10</f>
-        <v/>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Return on OUR shares by scenario</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Total dev cost</t>
-        </is>
-      </c>
-      <c r="B11" s="48">
-        <f>'Inputs'!$C$10*B8+B10*'Inputs'!$C$18*B8</f>
-        <v/>
-      </c>
-      <c r="C11" s="48">
-        <f>'Inputs'!$C$10*C8+C10*'Inputs'!$C$18*C8</f>
-        <v/>
-      </c>
-      <c r="D11" s="48">
-        <f>'Inputs'!$C$10*D8+D10*'Inputs'!$C$18*D8</f>
-        <v/>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>Gross proceeds</t>
-        </is>
-      </c>
-      <c r="B12" s="48">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*B6</f>
-        <v/>
-      </c>
-      <c r="C12" s="48">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*C6</f>
-        <v/>
-      </c>
-      <c r="D12" s="48">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*D6</f>
+          <t>Flip success (DA × conn × sale)</t>
+        </is>
+      </c>
+      <c r="B12" s="36">
+        <f>'Scenarios'!$B$5*'Inputs'!$C$27*'Inputs'!$C$28</f>
+        <v/>
+      </c>
+      <c r="C12" s="36">
+        <f>'Scenarios'!$C$5*'Inputs'!$C$27*'Inputs'!$C$28</f>
+        <v/>
+      </c>
+      <c r="D12" s="36">
+        <f>'Scenarios'!$D$5*'Inputs'!$C$27*'Inputs'!$C$28</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Invested capital</t>
-        </is>
-      </c>
-      <c r="B13" s="48">
-        <f>B11+'Calc_Fund'!$C$15+'Calc_Fund'!$C$14</f>
-        <v/>
-      </c>
-      <c r="C13" s="48">
-        <f>C11+'Calc_Fund'!$C$15+'Calc_Fund'!$C$14</f>
-        <v/>
-      </c>
-      <c r="D13" s="48">
-        <f>D11+'Calc_Fund'!$C$15+'Calc_Fund'!$C$14</f>
+          <t>RTB price multiplier</t>
+        </is>
+      </c>
+      <c r="B13" s="43">
+        <f>'Scenarios'!$B$6</f>
+        <v/>
+      </c>
+      <c r="C13" s="43">
+        <f>'Scenarios'!$C$6</f>
+        <v/>
+      </c>
+      <c r="D13" s="43">
+        <f>'Scenarios'!$D$6</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Profit before carry</t>
-        </is>
-      </c>
-      <c r="B14" s="48">
-        <f>B12-B13</f>
-        <v/>
-      </c>
-      <c r="C14" s="48">
-        <f>C12-C13</f>
-        <v/>
-      </c>
-      <c r="D14" s="48">
-        <f>D12-D13</f>
+          <t>Dev cost multiplier</t>
+        </is>
+      </c>
+      <c r="B14" s="43">
+        <f>'Scenarios'!$B$7</f>
+        <v/>
+      </c>
+      <c r="C14" s="43">
+        <f>'Scenarios'!$C$7</f>
+        <v/>
+      </c>
+      <c r="D14" s="43">
+        <f>'Scenarios'!$D$7</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Hurdle amount</t>
-        </is>
-      </c>
-      <c r="B15" s="48">
-        <f>B13*'Calc_Fund'!$C$19</f>
-        <v/>
-      </c>
-      <c r="C15" s="48">
-        <f>C13*'Calc_Fund'!$C$19</f>
-        <v/>
-      </c>
-      <c r="D15" s="48">
-        <f>D13*'Calc_Fund'!$C$19</f>
+          <t>Dev cost per project</t>
+        </is>
+      </c>
+      <c r="B15" s="44">
+        <f>'Inputs'!$C$21*B14</f>
+        <v/>
+      </c>
+      <c r="C15" s="44">
+        <f>'Inputs'!$C$21*C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="44">
+        <f>'Inputs'!$C$21*D14</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Carry to GP</t>
-        </is>
-      </c>
-      <c r="B16" s="48">
-        <f>'Inputs'!$C$14*MAX(0,B14-B15)</f>
-        <v/>
-      </c>
-      <c r="C16" s="48">
-        <f>'Inputs'!$C$14*MAX(0,C14-C15)</f>
-        <v/>
-      </c>
-      <c r="D16" s="48">
-        <f>'Inputs'!$C$14*MAX(0,D14-D15)</f>
+          <t>Projects started</t>
+        </is>
+      </c>
+      <c r="B16" s="49">
+        <f>IFERROR('Inputs'!$C$10/B12,0)</f>
+        <v/>
+      </c>
+      <c r="C16" s="49">
+        <f>IFERROR('Inputs'!$C$10/C12,0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="49">
+        <f>IFERROR('Inputs'!$C$10/D12,0)</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>Distributions to LP</t>
-        </is>
-      </c>
-      <c r="B17" s="48">
-        <f>B12-B16</f>
-        <v/>
-      </c>
-      <c r="C17" s="48">
-        <f>C12-C16</f>
-        <v/>
-      </c>
-      <c r="D17" s="48">
-        <f>D12-D16</f>
+          <t>Projects failed</t>
+        </is>
+      </c>
+      <c r="B17" s="49">
+        <f>B16-'Inputs'!$C$10</f>
+        <v/>
+      </c>
+      <c r="C17" s="49">
+        <f>C16-'Inputs'!$C$10</f>
+        <v/>
+      </c>
+      <c r="D17" s="49">
+        <f>D16-'Inputs'!$C$10</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>MOIC (net)</t>
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Total dev cost</t>
         </is>
       </c>
       <c r="B18" s="50">
-        <f>IFERROR(B17/B13,0)</f>
+        <f>'Inputs'!$C$10*B15+B17*'Inputs'!$C$22*B15</f>
         <v/>
       </c>
       <c r="C18" s="50">
-        <f>IFERROR(C17/C13,0)</f>
+        <f>'Inputs'!$C$10*C15+C17*'Inputs'!$C$22*C15</f>
         <v/>
       </c>
       <c r="D18" s="50">
-        <f>IFERROR(D17/D13,0)</f>
+        <f>'Inputs'!$C$10*D15+D17*'Inputs'!$C$22*D15</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Investor IRR</t>
-        </is>
-      </c>
-      <c r="B19" s="18">
-        <f>IFERROR(B18^(1/'Calc_Fund'!$C$26)-1,0)</f>
-        <v/>
-      </c>
-      <c r="C19" s="18">
-        <f>IFERROR(C18^(1/'Calc_Fund'!$C$26)-1,0)</f>
-        <v/>
-      </c>
-      <c r="D19" s="18">
-        <f>IFERROR(D18^(1/'Calc_Fund'!$C$26)-1,0)</f>
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Gross proceeds</t>
+        </is>
+      </c>
+      <c r="B19" s="50">
+        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*B13</f>
+        <v/>
+      </c>
+      <c r="C19" s="50">
+        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*C13</f>
+        <v/>
+      </c>
+      <c r="D19" s="50">
+        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*D13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Net programme profit</t>
+        </is>
+      </c>
+      <c r="B20" s="50">
+        <f>B19-B18</f>
+        <v/>
+      </c>
+      <c r="C20" s="50">
+        <f>C19-C18</f>
+        <v/>
+      </c>
+      <c r="D20" s="50">
+        <f>D19-D18</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>First-Chicago probability-weighted expected return</t>
-        </is>
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>Company exit equity = MAX(0,net)×mult</t>
+        </is>
+      </c>
+      <c r="B21" s="50">
+        <f>MAX(0,B20)*'Inputs'!$C$18</f>
+        <v/>
+      </c>
+      <c r="C21" s="50">
+        <f>MAX(0,C20)*'Inputs'!$C$18</f>
+        <v/>
+      </c>
+      <c r="D21" s="50">
+        <f>MAX(0,D20)*'Inputs'!$C$18</f>
+        <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr"/>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Conservative</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Ideal</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>Expected</t>
-        </is>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>As-converted (diluted × exit equity)</t>
+        </is>
+      </c>
+      <c r="B22" s="44">
+        <f>'Returns'!$B$8*B21</f>
+        <v/>
+      </c>
+      <c r="C22" s="44">
+        <f>'Returns'!$B$8*C21</f>
+        <v/>
+      </c>
+      <c r="D22" s="44">
+        <f>'Returns'!$B$8*D21</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="B23" s="51">
-        <f>'Scenarios'!$B$13</f>
-        <v/>
-      </c>
-      <c r="C23" s="51">
-        <f>'Scenarios'!$C$13</f>
-        <v/>
-      </c>
-      <c r="D23" s="51">
-        <f>'Scenarios'!$D$13</f>
+          <t>Preference claim = MIN(liq×inv, exit eq)</t>
+        </is>
+      </c>
+      <c r="B23" s="44">
+        <f>MIN('Inputs'!$C$17*'Inputs'!$C$14,B21)</f>
+        <v/>
+      </c>
+      <c r="C23" s="44">
+        <f>MIN('Inputs'!$C$17*'Inputs'!$C$14,C21)</f>
+        <v/>
+      </c>
+      <c r="D23" s="44">
+        <f>MIN('Inputs'!$C$17*'Inputs'!$C$14,D21)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Investor IRR</t>
-        </is>
-      </c>
-      <c r="B24" s="33">
-        <f>'Returns'!$B$19</f>
-        <v/>
-      </c>
-      <c r="C24" s="33">
-        <f>'Returns'!$C$19</f>
-        <v/>
-      </c>
-      <c r="D24" s="33">
-        <f>'Returns'!$D$19</f>
-        <v/>
-      </c>
-      <c r="E24" s="35">
-        <f>SUMPRODUCT('Scenarios'!$B$13:$D$13,B24:D24)</f>
+          <t>Our proceeds = MAX(pref, as-converted)</t>
+        </is>
+      </c>
+      <c r="B24" s="47">
+        <f>MAX(B23,B22)</f>
+        <v/>
+      </c>
+      <c r="C24" s="47">
+        <f>MAX(C23,C22)</f>
+        <v/>
+      </c>
+      <c r="D24" s="47">
+        <f>MAX(D23,D22)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>MOIC (net)</t>
-        </is>
-      </c>
-      <c r="B25" s="52">
-        <f>'Returns'!$B$18</f>
-        <v/>
-      </c>
-      <c r="C25" s="52">
-        <f>'Returns'!$C$18</f>
-        <v/>
-      </c>
-      <c r="D25" s="52">
-        <f>'Returns'!$D$18</f>
-        <v/>
-      </c>
-      <c r="E25" s="50">
-        <f>SUMPRODUCT('Scenarios'!$B$13:$D$13,B25:D25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Valuation range (per-pipeline asset value — cross-check)</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>Representative 6-project pipeline, NOT the whole fund.</t>
-        </is>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>MOIC = our proceeds ÷ our investment</t>
+        </is>
+      </c>
+      <c r="B25" s="54">
+        <f>IFERROR(B24/'Inputs'!$C$14,0)</f>
+        <v/>
+      </c>
+      <c r="C25" s="54">
+        <f>IFERROR(C24/'Inputs'!$C$14,0)</f>
+        <v/>
+      </c>
+      <c r="D25" s="54">
+        <f>IFERROR(D24/'Inputs'!$C$14,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Equity IRR = MOIC^(1/exit yr) − 1</t>
+        </is>
+      </c>
+      <c r="B26" s="18">
+        <f>IFERROR(B25^(1/'Inputs'!$C$19)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="C26" s="18">
+        <f>IFERROR(C25^(1/'Inputs'!$C$19)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="D26" s="18">
+        <f>IFERROR(D25^(1/'Inputs'!$C$19)-1,-1)</f>
+        <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>rNPV pipeline (Base)</t>
-        </is>
-      </c>
-      <c r="C28" s="53">
-        <f>'Calc_Project_rNPV'!$M$10</f>
-        <v/>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>First-Chicago probability-weighted expected return</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>$/MW benchmark (dev value)</t>
-        </is>
-      </c>
-      <c r="C29" s="53">
-        <f>'Calc_CrossChecks'!$C$9</f>
-        <v/>
+      <c r="A29" s="8" t="inlineStr"/>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>VC method (today value)</t>
-        </is>
-      </c>
-      <c r="C30" s="53">
-        <f>'Calc_CrossChecks'!$C$18</f>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="B30" s="55">
+        <f>'Scenarios'!$B$13</f>
+        <v/>
+      </c>
+      <c r="C30" s="55">
+        <f>'Scenarios'!$C$13</f>
+        <v/>
+      </c>
+      <c r="D30" s="55">
+        <f>'Scenarios'!$D$13</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C31" s="45">
-        <f>MIN(C28:C30)</f>
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Our proceeds</t>
+        </is>
+      </c>
+      <c r="B31" s="56">
+        <f>'Returns'!$B$24</f>
+        <v/>
+      </c>
+      <c r="C31" s="56">
+        <f>'Returns'!$C$24</f>
+        <v/>
+      </c>
+      <c r="D31" s="56">
+        <f>'Returns'!$D$24</f>
+        <v/>
+      </c>
+      <c r="E31" s="47">
+        <f>SUMPRODUCT('Scenarios'!$B$13:$D$13,B31:D31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Midpoint</t>
-        </is>
-      </c>
-      <c r="C32" s="46">
-        <f>AVERAGE(C28:C30)</f>
+          <t>Expected MOIC = exp proceeds ÷ investment</t>
+        </is>
+      </c>
+      <c r="E32" s="54">
+        <f>IFERROR(E31/'Inputs'!$C$14,0)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
+          <t>Expected equity IRR = exp MOIC^(1/exit yr) − 1</t>
+        </is>
+      </c>
+      <c r="E33" s="37">
+        <f>IFERROR(E32^(1/'Inputs'!$C$19)-1,-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Valuation range (per-pipeline asset value — cross-check)</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Representative 6-project pipeline (asset-level), NOT the company's whole exit equity value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>rNPV pipeline (Base)</t>
+        </is>
+      </c>
+      <c r="C36" s="56">
+        <f>'Calc_Project_rNPV'!$M$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>$/MW benchmark (dev value)</t>
+        </is>
+      </c>
+      <c r="C37" s="56">
+        <f>'Calc_CrossChecks'!$C$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>VC method (today value)</t>
+        </is>
+      </c>
+      <c r="C38" s="56">
+        <f>'Calc_CrossChecks'!$C$18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C39" s="47">
+        <f>MIN(C36:C38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Midpoint</t>
+        </is>
+      </c>
+      <c r="C40" s="48">
+        <f>AVERAGE(C36:C38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="C33" s="45">
-        <f>MAX(C28:C30)</f>
+      <c r="C41" s="47">
+        <f>MAX(C36:C38)</f>
         <v/>
       </c>
     </row>
@@ -1491,7 +1567,7 @@
           <t>Total pipeline MW</t>
         </is>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="27">
         <f>SUM('Calc_Project_rNPV'!$C$4:$C$9)</f>
         <v/>
       </c>
@@ -1502,7 +1578,7 @@
           <t>Gross RTB asset value $m</t>
         </is>
       </c>
-      <c r="C5" s="48">
+      <c r="C5" s="50">
         <f>SUMPRODUCT('Calc_Project_rNPV'!$C$4:$C$9,'Calc_Project_rNPV'!$E$4:$E$9)*'Scenarios'!$C$6</f>
         <v/>
       </c>
@@ -1513,8 +1589,8 @@
           <t>Total dev cost $m</t>
         </is>
       </c>
-      <c r="C6" s="48">
-        <f>'Inputs'!$C$17*'Scenarios'!$C$7*6</f>
+      <c r="C6" s="50">
+        <f>'Inputs'!$C$21*'Scenarios'!$C$7*6</f>
         <v/>
       </c>
     </row>
@@ -1524,7 +1600,7 @@
           <t>Average years to sale</t>
         </is>
       </c>
-      <c r="C7" s="47">
+      <c r="C7" s="49">
         <f>AVERAGE('Calc_Project_rNPV'!$D$4:$D$9)</f>
         <v/>
       </c>
@@ -1535,8 +1611,8 @@
           <t>Flip success (Base, DA x conn x sale)</t>
         </is>
       </c>
-      <c r="C8" s="34">
-        <f>'Scenarios'!$C$5*'Inputs'!$C$23*'Inputs'!$C$24</f>
+      <c r="C8" s="36">
+        <f>'Scenarios'!$C$5*'Inputs'!$C$27*'Inputs'!$C$28</f>
         <v/>
       </c>
     </row>
@@ -1546,7 +1622,7 @@
           <t>$/MW implied dev value $m</t>
         </is>
       </c>
-      <c r="C9" s="45">
+      <c r="C9" s="47">
         <f>IFERROR((C5-C6)*C8/(1+'Inputs'!$C$7)^C7,0)</f>
         <v/>
       </c>
@@ -1564,7 +1640,7 @@
           <t>Total RTB sale value $m</t>
         </is>
       </c>
-      <c r="C12" s="48">
+      <c r="C12" s="50">
         <f>SUMPRODUCT('Calc_Project_rNPV'!$C$4:$C$9,'Calc_Project_rNPV'!$E$4:$E$9)*'Scenarios'!$C$6</f>
         <v/>
       </c>
@@ -1575,7 +1651,7 @@
           <t>Total dev cost $m</t>
         </is>
       </c>
-      <c r="C13" s="48">
+      <c r="C13" s="50">
         <f>C6</f>
         <v/>
       </c>
@@ -1586,7 +1662,7 @@
           <t>Flip success (Base)</t>
         </is>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="35">
         <f>C8</f>
         <v/>
       </c>
@@ -1597,7 +1673,7 @@
           <t>Exit equity value (expected) $m</t>
         </is>
       </c>
-      <c r="C15" s="42">
+      <c r="C15" s="44">
         <f>C14*(C12-C13)</f>
         <v/>
       </c>
@@ -1608,8 +1684,8 @@
           <t>VC target return</t>
         </is>
       </c>
-      <c r="C16" s="33">
-        <f>'Inputs'!$C$30</f>
+      <c r="C16" s="35">
+        <f>'Inputs'!$C$34</f>
         <v/>
       </c>
     </row>
@@ -1619,7 +1695,7 @@
           <t>Hold horizon (yrs)</t>
         </is>
       </c>
-      <c r="C17" s="38">
+      <c r="C17" s="40">
         <f>'Inputs'!$C$11</f>
         <v/>
       </c>
@@ -1630,7 +1706,7 @@
           <t>VC today value $m</t>
         </is>
       </c>
-      <c r="C18" s="45">
+      <c r="C18" s="47">
         <f>IFERROR(C15/(1+C16)^C17,0)</f>
         <v/>
       </c>
@@ -1670,15 +1746,15 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="B22" s="54">
-        <f>'Inputs'!$C$26</f>
-        <v/>
-      </c>
-      <c r="C22" s="54">
-        <f>'Inputs'!$C$20</f>
-        <v/>
-      </c>
-      <c r="D22" s="34">
+      <c r="B22" s="57">
+        <f>'Inputs'!$C$30</f>
+        <v/>
+      </c>
+      <c r="C22" s="57">
+        <f>'Inputs'!$C$24</f>
+        <v/>
+      </c>
+      <c r="D22" s="36">
         <f>IFERROR(B22/C22,0)</f>
         <v/>
       </c>
@@ -1689,15 +1765,15 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="B23" s="54">
-        <f>'Inputs'!$C$27</f>
-        <v/>
-      </c>
-      <c r="C23" s="54">
-        <f>'Inputs'!$C$20</f>
-        <v/>
-      </c>
-      <c r="D23" s="34">
+      <c r="B23" s="57">
+        <f>'Inputs'!$C$31</f>
+        <v/>
+      </c>
+      <c r="C23" s="57">
+        <f>'Inputs'!$C$24</f>
+        <v/>
+      </c>
+      <c r="D23" s="36">
         <f>IFERROR(B23/C23,0)</f>
         <v/>
       </c>
@@ -1708,15 +1784,15 @@
           <t>SA</t>
         </is>
       </c>
-      <c r="B24" s="54">
-        <f>'Inputs'!$C$28</f>
-        <v/>
-      </c>
-      <c r="C24" s="54">
-        <f>'Inputs'!$C$20</f>
-        <v/>
-      </c>
-      <c r="D24" s="34">
+      <c r="B24" s="57">
+        <f>'Inputs'!$C$32</f>
+        <v/>
+      </c>
+      <c r="C24" s="57">
+        <f>'Inputs'!$C$24</f>
+        <v/>
+      </c>
+      <c r="D24" s="36">
         <f>IFERROR(B24/C24,0)</f>
         <v/>
       </c>
@@ -1743,7 +1819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1753,16 +1829,22 @@
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SENSITIVITY — investor MOIC (net): development approval × RTB price</t>
+          <t>SENSITIVITY — OUR equity IRR: development approval × RTB price</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
@@ -1774,357 +1856,514 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Investor MOIC vs DEVELOPMENT-APPROVAL rate (down) × RTB price multiplier (across); all else at Base. Flip success = DA × grid connection × sale, so the funnel widens with the FULL gate chain (not the DA rate alone). IRR ≈ MOIC^(1/eff-hold). Live formula grid. All figures AUD $m / x.</t>
+          <t>Return on OUR shares (equity IRR = MOIC^(1/exit year) − 1) vs DEVELOPMENT-APPROVAL rate (down) × RTB price multiplier (across); all else at Base. Flip success = DA × grid connection × sale, so the funnel widens with the FULL gate chain. Each scenario flows through the company exit equity value, dilution and the 1× liquidation preference. Helper columns H–J (per DA) and the proceeds grid M–Q keep every formula short. AUD $m / %.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
-          <t>Carry %</t>
-        </is>
-      </c>
-      <c r="B4" s="33">
-        <f>'Inputs'!$C$14</f>
+          <t>Conn × sale (flip adj)</t>
+        </is>
+      </c>
+      <c r="B4" s="36">
+        <f>'Inputs'!$C$27*'Inputs'!$C$28</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Hurdle factor</t>
-        </is>
-      </c>
-      <c r="B5" s="33">
-        <f>'Calc_Fund'!$C$19</f>
+          <t>Diluted ownership</t>
+        </is>
+      </c>
+      <c r="B5" s="35">
+        <f>'Returns'!$B$8</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>Fixed fees (mgmt+entry) $m</t>
-        </is>
-      </c>
-      <c r="B6" s="48">
-        <f>'Calc_Fund'!$C$15+'Calc_Fund'!$C$14</f>
+          <t>Platform exit multiple</t>
+        </is>
+      </c>
+      <c r="B6" s="43">
+        <f>'Inputs'!$C$18</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>Conn × sale (flip adj)</t>
-        </is>
-      </c>
-      <c r="B7" s="34">
-        <f>'Inputs'!$C$23*'Inputs'!$C$24</f>
+          <t>Preference cap (liq × investment) $m</t>
+        </is>
+      </c>
+      <c r="B7" s="44">
+        <f>'Inputs'!$C$17*'Inputs'!$C$14</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="55" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Our investment $m</t>
+        </is>
+      </c>
+      <c r="B8" s="56">
+        <f>'Inputs'!$C$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Exit year</t>
+        </is>
+      </c>
+      <c r="B9" s="40">
+        <f>'Inputs'!$C$19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="58" t="inlineStr">
         <is>
           <t>Price mult →</t>
         </is>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C10" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D10" s="32" t="n">
         <v>0.85</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="F10" s="32" t="n">
         <v>1.15</v>
       </c>
-      <c r="G8" s="30" t="n">
+      <c r="G10" s="32" t="n">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="55" t="inlineStr">
+      <c r="M10" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N10" s="32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O10" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q10" s="32" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="58" t="inlineStr">
         <is>
           <t>Gross $m →</t>
         </is>
       </c>
-      <c r="C9" s="56">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*C8</f>
-        <v/>
-      </c>
-      <c r="D9" s="56">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*D8</f>
-        <v/>
-      </c>
-      <c r="E9" s="56">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*E8</f>
-        <v/>
-      </c>
-      <c r="F9" s="56">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*F8</f>
-        <v/>
-      </c>
-      <c r="G9" s="56">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*G8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="57" t="inlineStr">
+      <c r="C11" s="59">
+        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*C10</f>
+        <v/>
+      </c>
+      <c r="D11" s="59">
+        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*D10</f>
+        <v/>
+      </c>
+      <c r="E11" s="59">
+        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*E10</f>
+        <v/>
+      </c>
+      <c r="F11" s="59">
+        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*F10</f>
+        <v/>
+      </c>
+      <c r="G11" s="59">
+        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*G10</f>
+        <v/>
+      </c>
+      <c r="M11" s="59">
+        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*M10</f>
+        <v/>
+      </c>
+      <c r="N11" s="59">
+        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*N10</f>
+        <v/>
+      </c>
+      <c r="O11" s="59">
+        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*O10</f>
+        <v/>
+      </c>
+      <c r="P11" s="59">
+        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*P10</f>
+        <v/>
+      </c>
+      <c r="Q11" s="59">
+        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*Q10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t>DA gate ↓</t>
         </is>
       </c>
-      <c r="C10" s="57" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="D10" s="57" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="E10" s="57" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="F10" s="57" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="G10" s="57" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="C12" s="60" t="inlineStr">
+        <is>
+          <t>IRR</t>
+        </is>
+      </c>
+      <c r="D12" s="60" t="inlineStr">
+        <is>
+          <t>IRR</t>
+        </is>
+      </c>
+      <c r="E12" s="60" t="inlineStr">
+        <is>
+          <t>IRR</t>
+        </is>
+      </c>
+      <c r="F12" s="60" t="inlineStr">
+        <is>
+          <t>IRR</t>
+        </is>
+      </c>
+      <c r="G12" s="60" t="inlineStr">
+        <is>
+          <t>IRR</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Flip succ</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>Started</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>Total dev</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t>Invested</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="24" t="n">
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>Proceeds</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>Proceeds</t>
+        </is>
+      </c>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>Proceeds</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>Proceeds</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>Proceeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="26" t="n">
         <v>0.4</v>
       </c>
-      <c r="C11" s="58">
-        <f>IFERROR((C$9-'Sensitivity'!$B$4*MAX(0,(C$9-$K11)-$K11*'Sensitivity'!$B$5))/$K11,0)</f>
-        <v/>
-      </c>
-      <c r="D11" s="58">
-        <f>IFERROR((D$9-'Sensitivity'!$B$4*MAX(0,(D$9-$K11)-$K11*'Sensitivity'!$B$5))/$K11,0)</f>
-        <v/>
-      </c>
-      <c r="E11" s="58">
-        <f>IFERROR((E$9-'Sensitivity'!$B$4*MAX(0,(E$9-$K11)-$K11*'Sensitivity'!$B$5))/$K11,0)</f>
-        <v/>
-      </c>
-      <c r="F11" s="58">
-        <f>IFERROR((F$9-'Sensitivity'!$B$4*MAX(0,(F$9-$K11)-$K11*'Sensitivity'!$B$5))/$K11,0)</f>
-        <v/>
-      </c>
-      <c r="G11" s="58">
-        <f>IFERROR((G$9-'Sensitivity'!$B$4*MAX(0,(G$9-$K11)-$K11*'Sensitivity'!$B$5))/$K11,0)</f>
-        <v/>
-      </c>
-      <c r="H11" s="34">
-        <f>$B11*'Sensitivity'!$B$7</f>
-        <v/>
-      </c>
-      <c r="I11" s="47">
-        <f>IFERROR('Inputs'!$C$10/H11,0)</f>
-        <v/>
-      </c>
-      <c r="J11" s="48">
-        <f>'Inputs'!$C$10*'Inputs'!$C$17+(I11-'Inputs'!$C$10)*'Inputs'!$C$18*'Inputs'!$C$17</f>
-        <v/>
-      </c>
-      <c r="K11" s="48">
-        <f>J11+'Sensitivity'!$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="24" t="n">
+      <c r="C13" s="36">
+        <f>IFERROR((M13/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="D13" s="36">
+        <f>IFERROR((N13/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="E13" s="36">
+        <f>IFERROR((O13/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="F13" s="36">
+        <f>IFERROR((P13/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="G13" s="36">
+        <f>IFERROR((Q13/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="H13" s="36">
+        <f>$B13*$B$4</f>
+        <v/>
+      </c>
+      <c r="I13" s="49">
+        <f>IFERROR('Inputs'!$C$10/H13,0)</f>
+        <v/>
+      </c>
+      <c r="J13" s="50">
+        <f>'Inputs'!$C$10*'Inputs'!$C$21+(I13-'Inputs'!$C$10)*'Inputs'!$C$22*'Inputs'!$C$21</f>
+        <v/>
+      </c>
+      <c r="M13" s="44">
+        <f>MAX(MIN($B$7,MAX(0,M$11-$J13)*$B$6),$B$5*MAX(0,M$11-$J13)*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N13" s="44">
+        <f>MAX(MIN($B$7,MAX(0,N$11-$J13)*$B$6),$B$5*MAX(0,N$11-$J13)*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O13" s="44">
+        <f>MAX(MIN($B$7,MAX(0,O$11-$J13)*$B$6),$B$5*MAX(0,O$11-$J13)*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P13" s="44">
+        <f>MAX(MIN($B$7,MAX(0,P$11-$J13)*$B$6),$B$5*MAX(0,P$11-$J13)*$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q13" s="44">
+        <f>MAX(MIN($B$7,MAX(0,Q$11-$J13)*$B$6),$B$5*MAX(0,Q$11-$J13)*$B$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="26" t="n">
         <v>0.55</v>
       </c>
-      <c r="C12" s="58">
-        <f>IFERROR((C$9-'Sensitivity'!$B$4*MAX(0,(C$9-$K12)-$K12*'Sensitivity'!$B$5))/$K12,0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="58">
-        <f>IFERROR((D$9-'Sensitivity'!$B$4*MAX(0,(D$9-$K12)-$K12*'Sensitivity'!$B$5))/$K12,0)</f>
-        <v/>
-      </c>
-      <c r="E12" s="58">
-        <f>IFERROR((E$9-'Sensitivity'!$B$4*MAX(0,(E$9-$K12)-$K12*'Sensitivity'!$B$5))/$K12,0)</f>
-        <v/>
-      </c>
-      <c r="F12" s="58">
-        <f>IFERROR((F$9-'Sensitivity'!$B$4*MAX(0,(F$9-$K12)-$K12*'Sensitivity'!$B$5))/$K12,0)</f>
-        <v/>
-      </c>
-      <c r="G12" s="58">
-        <f>IFERROR((G$9-'Sensitivity'!$B$4*MAX(0,(G$9-$K12)-$K12*'Sensitivity'!$B$5))/$K12,0)</f>
-        <v/>
-      </c>
-      <c r="H12" s="34">
-        <f>$B12*'Sensitivity'!$B$7</f>
-        <v/>
-      </c>
-      <c r="I12" s="47">
-        <f>IFERROR('Inputs'!$C$10/H12,0)</f>
-        <v/>
-      </c>
-      <c r="J12" s="48">
-        <f>'Inputs'!$C$10*'Inputs'!$C$17+(I12-'Inputs'!$C$10)*'Inputs'!$C$18*'Inputs'!$C$17</f>
-        <v/>
-      </c>
-      <c r="K12" s="48">
-        <f>J12+'Sensitivity'!$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="24" t="n">
+      <c r="C14" s="36">
+        <f>IFERROR((M14/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="D14" s="36">
+        <f>IFERROR((N14/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="E14" s="36">
+        <f>IFERROR((O14/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="F14" s="36">
+        <f>IFERROR((P14/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="G14" s="36">
+        <f>IFERROR((Q14/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="H14" s="36">
+        <f>$B14*$B$4</f>
+        <v/>
+      </c>
+      <c r="I14" s="49">
+        <f>IFERROR('Inputs'!$C$10/H14,0)</f>
+        <v/>
+      </c>
+      <c r="J14" s="50">
+        <f>'Inputs'!$C$10*'Inputs'!$C$21+(I14-'Inputs'!$C$10)*'Inputs'!$C$22*'Inputs'!$C$21</f>
+        <v/>
+      </c>
+      <c r="M14" s="44">
+        <f>MAX(MIN($B$7,MAX(0,M$11-$J14)*$B$6),$B$5*MAX(0,M$11-$J14)*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N14" s="44">
+        <f>MAX(MIN($B$7,MAX(0,N$11-$J14)*$B$6),$B$5*MAX(0,N$11-$J14)*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O14" s="44">
+        <f>MAX(MIN($B$7,MAX(0,O$11-$J14)*$B$6),$B$5*MAX(0,O$11-$J14)*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P14" s="44">
+        <f>MAX(MIN($B$7,MAX(0,P$11-$J14)*$B$6),$B$5*MAX(0,P$11-$J14)*$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="44">
+        <f>MAX(MIN($B$7,MAX(0,Q$11-$J14)*$B$6),$B$5*MAX(0,Q$11-$J14)*$B$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="26" t="n">
         <v>0.65</v>
       </c>
-      <c r="C13" s="58">
-        <f>IFERROR((C$9-'Sensitivity'!$B$4*MAX(0,(C$9-$K13)-$K13*'Sensitivity'!$B$5))/$K13,0)</f>
-        <v/>
-      </c>
-      <c r="D13" s="58">
-        <f>IFERROR((D$9-'Sensitivity'!$B$4*MAX(0,(D$9-$K13)-$K13*'Sensitivity'!$B$5))/$K13,0)</f>
-        <v/>
-      </c>
-      <c r="E13" s="58">
-        <f>IFERROR((E$9-'Sensitivity'!$B$4*MAX(0,(E$9-$K13)-$K13*'Sensitivity'!$B$5))/$K13,0)</f>
-        <v/>
-      </c>
-      <c r="F13" s="58">
-        <f>IFERROR((F$9-'Sensitivity'!$B$4*MAX(0,(F$9-$K13)-$K13*'Sensitivity'!$B$5))/$K13,0)</f>
-        <v/>
-      </c>
-      <c r="G13" s="58">
-        <f>IFERROR((G$9-'Sensitivity'!$B$4*MAX(0,(G$9-$K13)-$K13*'Sensitivity'!$B$5))/$K13,0)</f>
-        <v/>
-      </c>
-      <c r="H13" s="34">
-        <f>$B13*'Sensitivity'!$B$7</f>
-        <v/>
-      </c>
-      <c r="I13" s="47">
-        <f>IFERROR('Inputs'!$C$10/H13,0)</f>
-        <v/>
-      </c>
-      <c r="J13" s="48">
-        <f>'Inputs'!$C$10*'Inputs'!$C$17+(I13-'Inputs'!$C$10)*'Inputs'!$C$18*'Inputs'!$C$17</f>
-        <v/>
-      </c>
-      <c r="K13" s="48">
-        <f>J13+'Sensitivity'!$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="24" t="n">
+      <c r="C15" s="36">
+        <f>IFERROR((M15/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="D15" s="36">
+        <f>IFERROR((N15/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="E15" s="36">
+        <f>IFERROR((O15/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="F15" s="36">
+        <f>IFERROR((P15/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="G15" s="36">
+        <f>IFERROR((Q15/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="H15" s="36">
+        <f>$B15*$B$4</f>
+        <v/>
+      </c>
+      <c r="I15" s="49">
+        <f>IFERROR('Inputs'!$C$10/H15,0)</f>
+        <v/>
+      </c>
+      <c r="J15" s="50">
+        <f>'Inputs'!$C$10*'Inputs'!$C$21+(I15-'Inputs'!$C$10)*'Inputs'!$C$22*'Inputs'!$C$21</f>
+        <v/>
+      </c>
+      <c r="M15" s="44">
+        <f>MAX(MIN($B$7,MAX(0,M$11-$J15)*$B$6),$B$5*MAX(0,M$11-$J15)*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N15" s="44">
+        <f>MAX(MIN($B$7,MAX(0,N$11-$J15)*$B$6),$B$5*MAX(0,N$11-$J15)*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O15" s="44">
+        <f>MAX(MIN($B$7,MAX(0,O$11-$J15)*$B$6),$B$5*MAX(0,O$11-$J15)*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P15" s="44">
+        <f>MAX(MIN($B$7,MAX(0,P$11-$J15)*$B$6),$B$5*MAX(0,P$11-$J15)*$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q15" s="44">
+        <f>MAX(MIN($B$7,MAX(0,Q$11-$J15)*$B$6),$B$5*MAX(0,Q$11-$J15)*$B$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="26" t="n">
         <v>0.8</v>
       </c>
-      <c r="C14" s="58">
-        <f>IFERROR((C$9-'Sensitivity'!$B$4*MAX(0,(C$9-$K14)-$K14*'Sensitivity'!$B$5))/$K14,0)</f>
-        <v/>
-      </c>
-      <c r="D14" s="58">
-        <f>IFERROR((D$9-'Sensitivity'!$B$4*MAX(0,(D$9-$K14)-$K14*'Sensitivity'!$B$5))/$K14,0)</f>
-        <v/>
-      </c>
-      <c r="E14" s="58">
-        <f>IFERROR((E$9-'Sensitivity'!$B$4*MAX(0,(E$9-$K14)-$K14*'Sensitivity'!$B$5))/$K14,0)</f>
-        <v/>
-      </c>
-      <c r="F14" s="58">
-        <f>IFERROR((F$9-'Sensitivity'!$B$4*MAX(0,(F$9-$K14)-$K14*'Sensitivity'!$B$5))/$K14,0)</f>
-        <v/>
-      </c>
-      <c r="G14" s="58">
-        <f>IFERROR((G$9-'Sensitivity'!$B$4*MAX(0,(G$9-$K14)-$K14*'Sensitivity'!$B$5))/$K14,0)</f>
-        <v/>
-      </c>
-      <c r="H14" s="34">
-        <f>$B14*'Sensitivity'!$B$7</f>
-        <v/>
-      </c>
-      <c r="I14" s="47">
-        <f>IFERROR('Inputs'!$C$10/H14,0)</f>
-        <v/>
-      </c>
-      <c r="J14" s="48">
-        <f>'Inputs'!$C$10*'Inputs'!$C$17+(I14-'Inputs'!$C$10)*'Inputs'!$C$18*'Inputs'!$C$17</f>
-        <v/>
-      </c>
-      <c r="K14" s="48">
-        <f>J14+'Sensitivity'!$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="24" t="n">
+      <c r="C16" s="36">
+        <f>IFERROR((M16/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="D16" s="36">
+        <f>IFERROR((N16/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="E16" s="36">
+        <f>IFERROR((O16/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="F16" s="36">
+        <f>IFERROR((P16/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="G16" s="36">
+        <f>IFERROR((Q16/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="H16" s="36">
+        <f>$B16*$B$4</f>
+        <v/>
+      </c>
+      <c r="I16" s="49">
+        <f>IFERROR('Inputs'!$C$10/H16,0)</f>
+        <v/>
+      </c>
+      <c r="J16" s="50">
+        <f>'Inputs'!$C$10*'Inputs'!$C$21+(I16-'Inputs'!$C$10)*'Inputs'!$C$22*'Inputs'!$C$21</f>
+        <v/>
+      </c>
+      <c r="M16" s="44">
+        <f>MAX(MIN($B$7,MAX(0,M$11-$J16)*$B$6),$B$5*MAX(0,M$11-$J16)*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N16" s="44">
+        <f>MAX(MIN($B$7,MAX(0,N$11-$J16)*$B$6),$B$5*MAX(0,N$11-$J16)*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O16" s="44">
+        <f>MAX(MIN($B$7,MAX(0,O$11-$J16)*$B$6),$B$5*MAX(0,O$11-$J16)*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P16" s="44">
+        <f>MAX(MIN($B$7,MAX(0,P$11-$J16)*$B$6),$B$5*MAX(0,P$11-$J16)*$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q16" s="44">
+        <f>MAX(MIN($B$7,MAX(0,Q$11-$J16)*$B$6),$B$5*MAX(0,Q$11-$J16)*$B$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="26" t="n">
         <v>0.95</v>
       </c>
-      <c r="C15" s="58">
-        <f>IFERROR((C$9-'Sensitivity'!$B$4*MAX(0,(C$9-$K15)-$K15*'Sensitivity'!$B$5))/$K15,0)</f>
-        <v/>
-      </c>
-      <c r="D15" s="58">
-        <f>IFERROR((D$9-'Sensitivity'!$B$4*MAX(0,(D$9-$K15)-$K15*'Sensitivity'!$B$5))/$K15,0)</f>
-        <v/>
-      </c>
-      <c r="E15" s="58">
-        <f>IFERROR((E$9-'Sensitivity'!$B$4*MAX(0,(E$9-$K15)-$K15*'Sensitivity'!$B$5))/$K15,0)</f>
-        <v/>
-      </c>
-      <c r="F15" s="58">
-        <f>IFERROR((F$9-'Sensitivity'!$B$4*MAX(0,(F$9-$K15)-$K15*'Sensitivity'!$B$5))/$K15,0)</f>
-        <v/>
-      </c>
-      <c r="G15" s="58">
-        <f>IFERROR((G$9-'Sensitivity'!$B$4*MAX(0,(G$9-$K15)-$K15*'Sensitivity'!$B$5))/$K15,0)</f>
-        <v/>
-      </c>
-      <c r="H15" s="34">
-        <f>$B15*'Sensitivity'!$B$7</f>
-        <v/>
-      </c>
-      <c r="I15" s="47">
-        <f>IFERROR('Inputs'!$C$10/H15,0)</f>
-        <v/>
-      </c>
-      <c r="J15" s="48">
-        <f>'Inputs'!$C$10*'Inputs'!$C$17+(I15-'Inputs'!$C$10)*'Inputs'!$C$18*'Inputs'!$C$17</f>
-        <v/>
-      </c>
-      <c r="K15" s="48">
-        <f>J15+'Sensitivity'!$B$6</f>
+      <c r="C17" s="36">
+        <f>IFERROR((M17/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="D17" s="36">
+        <f>IFERROR((N17/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="E17" s="36">
+        <f>IFERROR((O17/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="F17" s="36">
+        <f>IFERROR((P17/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="G17" s="36">
+        <f>IFERROR((Q17/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="H17" s="36">
+        <f>$B17*$B$4</f>
+        <v/>
+      </c>
+      <c r="I17" s="49">
+        <f>IFERROR('Inputs'!$C$10/H17,0)</f>
+        <v/>
+      </c>
+      <c r="J17" s="50">
+        <f>'Inputs'!$C$10*'Inputs'!$C$21+(I17-'Inputs'!$C$10)*'Inputs'!$C$22*'Inputs'!$C$21</f>
+        <v/>
+      </c>
+      <c r="M17" s="44">
+        <f>MAX(MIN($B$7,MAX(0,M$11-$J17)*$B$6),$B$5*MAX(0,M$11-$J17)*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N17" s="44">
+        <f>MAX(MIN($B$7,MAX(0,N$11-$J17)*$B$6),$B$5*MAX(0,N$11-$J17)*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O17" s="44">
+        <f>MAX(MIN($B$7,MAX(0,O$11-$J17)*$B$6),$B$5*MAX(0,O$11-$J17)*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P17" s="44">
+        <f>MAX(MIN($B$7,MAX(0,P$11-$J17)*$B$6),$B$5*MAX(0,P$11-$J17)*$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q17" s="44">
+        <f>MAX(MIN($B$7,MAX(0,Q$11-$J17)*$B$6),$B$5*MAX(0,Q$11-$J17)*$B$6)</f>
         <v/>
       </c>
     </row>
@@ -2143,7 +2382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -2190,8 +2429,8 @@
           <t>Every gate probability ∈ [0,1]</t>
         </is>
       </c>
-      <c r="B4" s="36">
-        <f>IF(AND(MIN('Inputs'!$C$22:$C$24)&gt;=0,MAX('Inputs'!$C$22:$C$24)&lt;=1),"OK","ERROR")</f>
+      <c r="B4" s="38">
+        <f>IF(AND(MIN('Inputs'!$C$26:$C$28)&gt;=0,MAX('Inputs'!$C$26:$C$28)&lt;=1),"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -2206,7 +2445,7 @@
           <t>Flip success ≤ each gate</t>
         </is>
       </c>
-      <c r="B5" s="36">
+      <c r="B5" s="38">
         <f>IF('Calc_Survival'!$C$7&lt;=MIN('Calc_Survival'!$B$4:$B$6)+0.000001,"OK","ERROR")</f>
         <v/>
       </c>
@@ -2222,8 +2461,8 @@
           <t>All MW positive</t>
         </is>
       </c>
-      <c r="B6" s="36">
-        <f>IF(MIN('Inputs'!$D$36:$D$41)&gt;0,"OK","ERROR")</f>
+      <c r="B6" s="38">
+        <f>IF(MIN('Inputs'!$D$40:$D$45)&gt;0,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -2238,7 +2477,7 @@
           <t>All RTB sale values positive</t>
         </is>
       </c>
-      <c r="B7" s="36">
+      <c r="B7" s="38">
         <f>IF(MIN('Calc_Project_rNPV'!$G$4:$G$9)&gt;0,"OK","ERROR")</f>
         <v/>
       </c>
@@ -2254,8 +2493,8 @@
           <t>Dev cost positive</t>
         </is>
       </c>
-      <c r="B8" s="36">
-        <f>IF('Inputs'!$C$17&gt;0,"OK","ERROR")</f>
+      <c r="B8" s="38">
+        <f>IF('Inputs'!$C$21&gt;0,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -2270,7 +2509,7 @@
           <t>Scenario switch ∈ {1,2,3}</t>
         </is>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="38">
         <f>IF(AND('Scenarios'!$B$2&gt;=1,'Scenarios'!$B$2&lt;=3),"OK","ERROR")</f>
         <v/>
       </c>
@@ -2286,7 +2525,7 @@
           <t>Scenario DA-gate monotonic</t>
         </is>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="38">
         <f>IF(AND('Scenarios'!$B$5&lt;='Scenarios'!$C$5,'Scenarios'!$C$5&lt;='Scenarios'!$D$5),"OK","ERROR")</f>
         <v/>
       </c>
@@ -2299,152 +2538,168 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>Investor IRR monotonic</t>
-        </is>
-      </c>
-      <c r="B11" s="36">
-        <f>IF(AND('Returns'!$B$19&lt;='Returns'!$C$19,'Returns'!$C$19&lt;='Returns'!$D$19),"OK","ERROR")</f>
+          <t>Post-money = pre-money + investment</t>
+        </is>
+      </c>
+      <c r="B11" s="38">
+        <f>IF(ABS('Returns'!$B$6-('Inputs'!$C$13+'Inputs'!$C$14))&lt;0.0001,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Cons ≤ Base ≤ Ideal</t>
+          <t>Cap-table identity</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>Scenario weights sum to 100%</t>
-        </is>
-      </c>
-      <c r="B12" s="36">
-        <f>IF(ABS('Scenarios'!$E$13-1)&lt;0.001,"OK","ERROR")</f>
+          <t>Ownership = investment ÷ post-money</t>
+        </is>
+      </c>
+      <c r="B12" s="38">
+        <f>IF(ABS('Returns'!$B$7-'Inputs'!$C$14/'Returns'!$B$6)&lt;0.0001,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>First-Chicago weights</t>
+          <t>Cap-table identity</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Capital-call profile sums to 100%</t>
-        </is>
-      </c>
-      <c r="B13" s="36">
-        <f>IF(ABS(SUM('Inputs'!$C$32:$F$32)-1)&lt;0.001,"OK","ERROR")</f>
+          <t>Diluted ownership ≤ entry ownership</t>
+        </is>
+      </c>
+      <c r="B13" s="38">
+        <f>IF('Returns'!$B$8&lt;='Returns'!$B$7+0.0001,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Cash-flow profile</t>
+          <t>Dilution sign</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Distribution profile sums to 100%</t>
-        </is>
-      </c>
-      <c r="B14" s="36">
-        <f>IF(ABS(SUM('Inputs'!$C$33:$F$33)-1)&lt;0.001,"OK","ERROR")</f>
+          <t>Investor MOIC monotonic</t>
+        </is>
+      </c>
+      <c r="B14" s="38">
+        <f>IF(AND('Returns'!$B$25&lt;='Returns'!$C$25,'Returns'!$C$25&lt;='Returns'!$D$25),"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Cash-flow profile</t>
+          <t>Cons ≤ Base ≤ Ideal</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>First-Chicago IRR within scenario range</t>
-        </is>
-      </c>
-      <c r="B15" s="36">
-        <f>IF(AND(G15&gt;=E15-0.0001,G15&lt;=F15+0.0001),"OK","ERROR")</f>
+          <t>Scenario weights sum to 100%</t>
+        </is>
+      </c>
+      <c r="B15" s="38">
+        <f>IF(ABS('Scenarios'!$E$13-1)&lt;0.001,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Weighting sanity (helpers E:G)</t>
-        </is>
-      </c>
-      <c r="E15" s="59">
-        <f>MIN('Returns'!$B$19:$D$19)</f>
-        <v/>
-      </c>
-      <c r="F15" s="59">
-        <f>MAX('Returns'!$B$19:$D$19)</f>
-        <v/>
-      </c>
-      <c r="G15" s="51">
-        <f>'Returns'!$E$24</f>
-        <v/>
+          <t>First-Chicago weights</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Invested capital positive (all scenarios)</t>
-        </is>
-      </c>
-      <c r="B16" s="36">
-        <f>IF(MIN('Returns'!$B$13:$D$13)&gt;0,"OK","ERROR")</f>
+          <t>First-Chicago IRR within scenario range</t>
+        </is>
+      </c>
+      <c r="B16" s="38">
+        <f>IF(AND(G16&gt;=E16-0.0001,G16&lt;=F16+0.0001),"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Sign check</t>
-        </is>
+          <t>Weighting sanity (helpers E:G)</t>
+        </is>
+      </c>
+      <c r="E16" s="61">
+        <f>MIN('Returns'!$B$26:$D$26)</f>
+        <v/>
+      </c>
+      <c r="F16" s="61">
+        <f>MAX('Returns'!$B$26:$D$26)</f>
+        <v/>
+      </c>
+      <c r="G16" s="55">
+        <f>'Returns'!$E$33</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
+          <t>Our proceeds non-negative (all scenarios)</t>
+        </is>
+      </c>
+      <c r="B17" s="38">
+        <f>IF(MIN('Returns'!$B$24:$D$24)&gt;=0,"OK","ERROR")</f>
+        <v/>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Sign check</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
           <t>No error cells in key outputs</t>
         </is>
       </c>
-      <c r="B17" s="36">
-        <f>IF(SUM(E17:G17)=0,"OK","ERROR")</f>
-        <v/>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="B18" s="38">
+        <f>IF(SUM(E18:G18)=0,"OK","ERROR")</f>
+        <v/>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>#REF!/#DIV0! scan</t>
         </is>
       </c>
-      <c r="E17" s="36">
+      <c r="E18" s="38">
         <f>SUMPRODUCT(--ISERROR('Calc_Project_rNPV'!$M$4:$M$10))</f>
         <v/>
       </c>
-      <c r="F17" s="36">
-        <f>SUMPRODUCT(--ISERROR('Returns'!$B$19:$D$19))</f>
-        <v/>
-      </c>
-      <c r="G17" s="36">
-        <f>SUMPRODUCT(--ISERROR('Sensitivity'!$C$11:$G$15))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="F18" s="38">
+        <f>SUMPRODUCT(--ISERROR('Returns'!$B$26:$D$26))</f>
+        <v/>
+      </c>
+      <c r="G18" s="38">
+        <f>SUMPRODUCT(--ISERROR('Sensitivity'!$C$13:$G$17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>MASTER CHECK</t>
         </is>
       </c>
-      <c r="B19" s="60">
-        <f>IF(COUNTIF(B4:B17,"ERROR")=0,"OK","ERROR")</f>
+      <c r="B20" s="62">
+        <f>IF(COUNTIF(B4:B18,"ERROR")=0,"OK","ERROR")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:B19">
+  <conditionalFormatting sqref="B4:B20">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -2466,20 +2721,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ILLUSTRATIVE DISTRIBUTION-BESS DEVELOP-AND-FLIP FUND — DASHBOARD</t>
+          <t>ILLUSTRATIVE BATTERY-DEVELOPER STARTUP — DIRECT-EQUITY DASHBOARD</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
@@ -2491,7 +2746,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Develop ~5 MW distribution BESS to RTB, sell before construction (NSW/VIC/SA). ILLUSTRATIVE — the manager figures are manager claims to verify. Not investment advice.</t>
+          <t>We buy SHARES directly in an illustrative ~5 MW distribution-BESS develop-and-flip startup (NSW/VIC/SA). ILLUSTRATIVE — founder/manager figures are claims and the equity-deal terms are placeholders to confirm. Not investment advice.</t>
         </is>
       </c>
     </row>
@@ -2510,40 +2765,40 @@
           <t>Master check</t>
         </is>
       </c>
-      <c r="E4" s="61">
-        <f>'Checks'!$B$19</f>
+      <c r="E4" s="63">
+        <f>'Checks'!$B$20</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>EXPECTED INVESTOR RETURN (First-Chicago)</t>
+          <t>EXPECTED RETURN ON OUR SHARES (First-Chicago)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>LIVE SCENARIO</t>
+          <t>OUR STAKE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Expected IRR (after fees)</t>
-        </is>
-      </c>
-      <c r="B7" s="32">
-        <f>'Returns'!$E$24</f>
-        <v/>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Investor IRR (live)</t>
-        </is>
-      </c>
-      <c r="E7" s="32">
-        <f>'Calc_Fund'!$C$27</f>
+          <t>Expected equity IRR</t>
+        </is>
+      </c>
+      <c r="B7" s="34">
+        <f>'Returns'!$E$33</f>
+        <v/>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Post-money valuation $m</t>
+        </is>
+      </c>
+      <c r="E7" s="52">
+        <f>'Returns'!$B$6</f>
         <v/>
       </c>
     </row>
@@ -2553,163 +2808,196 @@
           <t>Expected MOIC</t>
         </is>
       </c>
-      <c r="B8" s="52">
-        <f>'Returns'!$E$25</f>
+      <c r="B8" s="64">
+        <f>'Returns'!$E$32</f>
         <v/>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>MOIC (live)</t>
-        </is>
-      </c>
-      <c r="E8" s="52">
-        <f>'Calc_Fund'!$C$23</f>
+          <t>Ownership at entry</t>
+        </is>
+      </c>
+      <c r="E8" s="35">
+        <f>'Returns'!$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Ownership at exit (diluted)</t>
+        </is>
+      </c>
+      <c r="E9" s="35">
+        <f>'Returns'!$B$8</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>INVESTOR IRR BY SCENARIO</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Liquidation preference (x)</t>
+        </is>
+      </c>
+      <c r="E10" s="64">
+        <f>'Inputs'!$C$17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Exit year</t>
+        </is>
+      </c>
+      <c r="E11" s="40">
+        <f>'Inputs'!$C$19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>RETURN ON OUR SHARES BY SCENARIO</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>KEY ASSUMPTIONS &amp; FLAG</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Flip succ</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>IRR</t>
-        </is>
-      </c>
-      <c r="D11" s="62" t="inlineStr">
-        <is>
-          <t>Committed capital $m</t>
-        </is>
-      </c>
-      <c r="E11" s="63">
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Equity IRR</t>
+        </is>
+      </c>
+      <c r="D14" s="65" t="inlineStr">
+        <is>
+          <t>Programme capital $m</t>
+        </is>
+      </c>
+      <c r="E14" s="52">
         <f>'Inputs'!$C$9</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
       </c>
-      <c r="B12" s="34">
-        <f>'Scenarios'!$B$5*'Inputs'!$C$23*'Inputs'!$C$24</f>
-        <v/>
-      </c>
-      <c r="C12" s="33">
-        <f>'Returns'!$B$19</f>
-        <v/>
-      </c>
-      <c r="D12" s="58" t="inlineStr">
+      <c r="B15" s="36">
+        <f>'Scenarios'!$B$5*'Inputs'!$C$27*'Inputs'!$C$28</f>
+        <v/>
+      </c>
+      <c r="C15" s="35">
+        <f>'Returns'!$B$26</f>
+        <v/>
+      </c>
+      <c r="D15" s="66" t="inlineStr">
         <is>
           <t>Projects target</t>
         </is>
       </c>
-      <c r="E12" s="38">
+      <c r="E15" s="40">
         <f>'Inputs'!$C$10</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="B13" s="34">
-        <f>'Scenarios'!$C$5*'Inputs'!$C$23*'Inputs'!$C$24</f>
-        <v/>
-      </c>
-      <c r="C13" s="33">
-        <f>'Returns'!$C$19</f>
-        <v/>
-      </c>
-      <c r="D13" s="58" t="inlineStr">
+      <c r="B16" s="36">
+        <f>'Scenarios'!$C$5*'Inputs'!$C$27*'Inputs'!$C$28</f>
+        <v/>
+      </c>
+      <c r="C16" s="35">
+        <f>'Returns'!$C$26</f>
+        <v/>
+      </c>
+      <c r="D16" s="66" t="inlineStr">
         <is>
           <t>Manager headline DA gate (Base)</t>
         </is>
       </c>
-      <c r="E13" s="33">
+      <c r="E16" s="35">
         <f>'Scenarios'!$C$5</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Ideal</t>
         </is>
       </c>
-      <c r="B14" s="34">
-        <f>'Scenarios'!$D$5*'Inputs'!$C$23*'Inputs'!$C$24</f>
-        <v/>
-      </c>
-      <c r="C14" s="33">
-        <f>'Returns'!$D$19</f>
-        <v/>
-      </c>
-      <c r="D14" s="58" t="inlineStr">
+      <c r="B17" s="36">
+        <f>'Scenarios'!$D$5*'Inputs'!$C$27*'Inputs'!$C$28</f>
+        <v/>
+      </c>
+      <c r="C17" s="35">
+        <f>'Returns'!$D$26</f>
+        <v/>
+      </c>
+      <c r="D17" s="66" t="inlineStr">
         <is>
           <t>True flip success (Base, DAxconnxsale)</t>
         </is>
       </c>
-      <c r="E14" s="33">
+      <c r="E17" s="35">
         <f>'Calc_Survival'!$C$13</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="D15" s="15" t="inlineStr">
+    <row r="18">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>Independent flip success (benchmark)</t>
         </is>
       </c>
-      <c r="E15" s="33">
+      <c r="E18" s="35">
         <f>'Calc_Survival'!$C$10</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Conclusion (illustrative)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>A real, policy-backed, capital-light niche with a viable RTB exit — but the develop-and-flip economics are THIN once the gates are modelled correctly. The manager's 65% is the development-approval gate ALONE; true flip success = approval x grid connection x sale is ~36% at Base, so the expected investor return is only marginally positive and the Conservative case loses capital. The single biggest risk is EXIT/BUYER risk, then development/approval. On these numbers the flip is the WEAKEST entry — building or holding the asset earns far more (see the stage analysis). Pursue only on verified buyer depth, RTB comps and a survivable downside.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>A real, policy-backed, capital-light niche with a viable RTB exit — but the return on OUR shares is THIN once the gates are modelled and the cap table applied. The 65% headline is the development-approval gate ALONE; true flip success = approval x grid connection x sale is ~36% at Base, so the company's exit equity value is modest and — after dilution and our 1x liquidation preference — the expected return on our shares is only marginally positive while the Conservative case is a total loss. Biggest risks: EXIT/BUYER risk, then development/approval, then the equity-deal terms (all placeholders). Pursue only on verified buyer depth, RTB comps, a survivable downside, and confirmed cap-table terms.</t>
+        </is>
+      </c>
+    </row>
     <row r="22"/>
     <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A18:E23"/>
+    <mergeCell ref="A21:E26"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1" r:id="rId1"/>
@@ -2725,7 +3013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2810,12 +3098,12 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>CSIRO GenCost-anchored build cost; context only — the buyer (not the fund) funds construction</t>
+          <t>CSIRO GenCost-anchored build cost; context only — the buyer funds construction</t>
         </is>
       </c>
     </row>
@@ -2832,12 +3120,12 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>the manager's projections (claim ~$500k/project) — verify bottom-up: site+EIA+grid+community+overhead</t>
+          <t>Manager claim ~$500k/project — verify bottom-up</t>
         </is>
       </c>
     </row>
@@ -2982,58 +3270,118 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Funnel</t>
+          <t>Development funnel</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>projects_started = target ÷ success; you fund dev cost on every started project (full on delivered, partial on dropouts).</t>
+          <t>projects_started = target ÷ flip success; the company funds dev cost on every started project (full on delivered, partial on dropouts).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Carry / hurdle</t>
+          <t>Net programme profit</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>GP carried interest (20%) earned only on profit above the LP preferred return (8%).</t>
+          <t>The company's gross RTB proceeds minus its total development cost across the programme.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MOIC / IRR</t>
+          <t>Pre-money / post-money</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Multiple on invested capital; annualised return (closed-form over the effective hold).</t>
+          <t>Pre-money = the company's agreed value before our money goes in; post-money = pre-money + our investment.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>First Chicago</t>
+          <t>Ownership %</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Probability-weight the scenario returns into a single expected return.</t>
+          <t>Our share of the company = our investment ÷ post-money valuation.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>Dilution</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>The fall in our ownership % when new shares are issued — here a staff option pool and future funding rounds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Cap table</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>The schedule of who owns what % of the company; we run our stake through it to get our exit proceeds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Liquidation preference</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>A preferred right to get our money back (1x) before ordinary holders at exit; 1x non-participating means we take the GREATER of that or our as-converted share.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>MOIC / equity IRR</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Multiple on OUR investment; annualised return on our shares (MOIC^(1/exit year) − 1; a total loss is −100%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>First Chicago</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Probability-weight the scenarios' proceeds into a single expected return on our shares.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
           <t>Develop-and-flip</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>Develop, de-risk, then sell RTB — the margin is the value uplift; merchant risk passes to the buyer.</t>
         </is>
@@ -3142,7 +3490,7 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>All assumptions + imported data (blue)</t>
+          <t>All assumptions + cap-table deal terms + imported data (blue)</t>
         </is>
       </c>
     </row>
@@ -3212,12 +3560,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Calc_Fund</t>
+          <t>Calc_Company</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Funnel, fees, investor IRR/MOIC (live)</t>
+          <t>Company programme: funnel → net profit → company exit equity value (live)</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3580,7 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Investor IRR/MOIC by scenario, First-Chicago, valuation range</t>
+          <t>Cap table; return on OUR shares (equity IRR/MOIC) by scenario, First-Chicago, valuation range</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3610,7 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Investor MOIC grid (development approval × price)</t>
+          <t>Our equity IRR grid (development approval × RTB price)</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3396,7 +3744,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Initial build: survival curve, per-project rNPV, fund funnel + fees, investor IRR/MOIC, First-Chicago, cross-checks, sensitivity, checks, dashboard.</t>
+          <t>Initial build: survival curve, per-project rNPV, programme funnel, returns, First-Chicago, cross-checks, sensitivity, checks, dashboard.</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
@@ -3406,7 +3754,29 @@
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="13" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Reframed from a fund LP investment to a DIRECT-EQUITY stake: removed fees/carry/hurdle; renamed Calc_Fund→Calc_Company (programme → net profit → company exit equity value); added a cap table (pre-/post-money, ownership, dilution, 1x liquidation preference) on Returns; outputs are now the return on OUR shares (equity IRR/MOIC), First-Chicago weights proceeds; sensitivity outputs our equity IRR.</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Claude Code (v2 reframe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>[Analyst review pass — record changes here]</t>
         </is>
@@ -3427,7 +3797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3455,7 +3825,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>ILLUSTRATIVE develop-and-flip RTB fund. the manager figures are the manager's CLAIMS — verify. Every input traces to a source.</t>
+          <t>We buy SHARES directly in an ILLUSTRATIVE battery-developer startup (not a fund LP). Founder/manager figures are CLAIMS — verify; the equity-deal terms are placeholders to confirm. Every input traces to a source.</t>
         </is>
       </c>
     </row>
@@ -3583,14 +3953,14 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fund structure &amp; fees (the manager claim — verify in IM)</t>
+          <t>The company's development programme (the startup we buy shares in)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>Committed capital</t>
+          <t>Programme capital (company's dev programme)</t>
         </is>
       </c>
       <c r="C9" s="19" t="n">
@@ -3678,47 +4048,24 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Entry fee (% of committed)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>Illustrative / the manager claim (see config)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>BENCHMARK</t>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Direct-equity deal terms (cap table) — placeholders to confirm</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Management fee (% p.a.)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>0.02</v>
+          <t>Pre-money valuation</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>8</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>$m</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -3733,22 +4080,22 @@
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>BENCHMARK</t>
+          <t>TO CONFIRM</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Carried interest (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>0.2</v>
+          <t>Our investment</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>$m</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -3763,18 +4110,18 @@
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>BENCHMARK</t>
+          <t>TO CONFIRM</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Hurdle / preferred return (%)</t>
+          <t>Option pool % (created at our round)</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
@@ -3793,59 +4140,82 @@
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>BENCHMARK</t>
+          <t>TO CONFIRM</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Development cost &amp; funnel attrition</t>
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Future-round dilution %</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>Illustrative / the manager claim (see config)</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>Development cost per project</t>
+          <t>Liquidation preference (x)</t>
         </is>
       </c>
       <c r="C17" s="21" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>$m/project</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>the manager's projections (claim ~$500k/project) — verify bottom-up: site+EIA+grid+community+overhead</t>
+          <t>Illustrative / the manager claim (see config)</t>
         </is>
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>BENCHMARK</t>
+          <t>TO CONFIRM</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Abandonment fraction (failed projects)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="n">
-        <v>0.3</v>
+          <t>Platform exit multiple (on net programme profit)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="n">
+        <v>4</v>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
@@ -3860,76 +4230,99 @@
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Exit year (we sell our shares)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>Illustrative / the manager claim (see config)</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Development cost &amp; funnel attrition</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>Development cost per project</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>$m/project</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>Manager claim ~$500k/project — verify bottom-up</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
           <t>BENCHMARK</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Build cost CONTEXT (buyer-funded — NOT in margin)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>Built-asset cost (context)</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>$m/MW</t>
-        </is>
-      </c>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>CSIRO GenCost-anchored build cost; context only — the buyer (not the fund) funds construction</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>BENCHMARK</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Survival gates — SEPARATE; scenarios move ONLY development approval</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>Development approval — public benchmark</t>
+          <t>Abandonment fraction (failed projects)</t>
         </is>
       </c>
       <c r="C22" s="16" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>prob</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>NSW Planning Portal — approved vs refused/withdrawn BESS major projects (benchmark)</t>
+          <t>Illustrative / the manager claim (see config)</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
@@ -3937,197 +4330,174 @@
           <t>BENCHMARK</t>
         </is>
       </c>
-      <c r="H22" s="23" t="n">
-        <v>1.25</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Grid connection (separate gate)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>prob</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>AEMO Connections Scorecard / KCI — connection success rate &amp; duration (benchmark)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>BENCHMARK</t>
-        </is>
-      </c>
-      <c r="H23" s="23" t="n">
-        <v>1.5</v>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Build cost CONTEXT (buyer-funded — NOT in margin)</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>Reach sale — flip exit (separate gate)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="n">
-        <v>0.8</v>
+          <t>Built-asset cost (context)</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="n">
+        <v>1.8</v>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>prob</t>
+          <t>$m/MW</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>AEMO proposed-&gt;committed attrition + active buyer pool (benchmark)</t>
+          <t>CSIRO GenCost-anchored build cost; context only — the buyer funds construction</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
           <t>BENCHMARK</t>
         </is>
-      </c>
-      <c r="H24" s="23" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>RTB exit price — $/MW by state (the manager claim — verify)</t>
+          <t>Survival gates — SEPARATE; scenarios move ONLY development approval</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>NSW</t>
-        </is>
-      </c>
-      <c r="C26" s="22" t="n">
-        <v>0.2</v>
+          <t>Development approval — public benchmark</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>0.8</v>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>$m/MW</t>
+          <t>prob</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>RTB $/MW by state (manager claim — independent comps needed)</t>
+          <t>NSW Planning Portal — approved vs refused/withdrawn BESS major projects (benchmark)</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
           <t>BENCHMARK</t>
         </is>
+      </c>
+      <c r="H26" s="25" t="n">
+        <v>1.25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>VIC</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="n">
-        <v>0.18</v>
+          <t>Grid connection (separate gate)</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>0.7</v>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>$m/MW</t>
+          <t>prob</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>RTB $/MW by state (manager claim — independent comps needed)</t>
+          <t>AEMO Connections Scorecard / KCI — connection success rate &amp; duration (benchmark)</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
           <t>BENCHMARK</t>
         </is>
+      </c>
+      <c r="H27" s="25" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="n">
-        <v>0.12</v>
+          <t>Reach sale — flip exit (separate gate)</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>0.8</v>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>$m/MW</t>
+          <t>prob</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>RTB $/MW by state (manager claim — independent comps needed)</t>
+          <t>AEMO proposed-&gt;committed attrition + active buyer pool (benchmark)</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
           <t>BENCHMARK</t>
         </is>
+      </c>
+      <c r="H28" s="25" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>VC method</t>
+          <t>RTB exit price — $/MW by state (the manager claim — verify)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>VC target return (cross-check)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="n">
-        <v>0.25</v>
+          <t>NSW</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="n">
+        <v>0.2</v>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>$m/MW</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Illustrative / the manager claim (see config)</t>
+          <t>RTB $/MW by state (manager claim — independent comps needed)</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
@@ -4142,271 +4512,368 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Investor cash-flow profile (period 0..3; each sums to 100%)</t>
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>$m/MW</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>RTB $/MW by state (manager claim — independent comps needed)</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>BENCHMARK</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>$m/MW</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>RTB $/MW by state (manager claim — independent comps needed)</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>BENCHMARK</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>VC method</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>VC target return (cross-check)</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>Illustrative / the manager claim (see config)</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>BENCHMARK</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Investor cash-flow profile (period 0..3; each sums to 100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
           <t>Capital call profile</t>
         </is>
       </c>
-      <c r="C32" s="24" t="n">
+      <c r="C36" s="26" t="n">
         <v>0.5</v>
       </c>
-      <c r="D32" s="24" t="n">
+      <c r="D36" s="26" t="n">
         <v>0.5</v>
       </c>
-      <c r="E32" s="24" t="n">
+      <c r="E36" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="24" t="n">
+      <c r="F36" s="26" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Distribution profile</t>
         </is>
       </c>
-      <c r="C33" s="24" t="n">
+      <c r="C37" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="24" t="n">
+      <c r="D37" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E33" s="24" t="n">
+      <c r="E37" s="26" t="n">
         <v>0.5</v>
       </c>
-      <c r="F33" s="24" t="n">
+      <c r="F37" s="26" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>Illustrative pipeline (representative ~5 MW distribution projects)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>MW</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>Duration (h)</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>MWh</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>Years to sale</t>
         </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>Riverina 5MW BESS (illustrative)</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>NSW</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>Wagga Wagga, NSW</t>
-        </is>
-      </c>
-      <c r="D36" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="E36" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F36" s="25">
-        <f>D36*E36</f>
-        <v/>
-      </c>
-      <c r="G36" s="23" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>Hunter Edge 5MW BESS (illustrative)</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>NSW</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>Hunter Valley, NSW</t>
-        </is>
-      </c>
-      <c r="D37" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="E37" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="F37" s="25">
-        <f>D37*E37</f>
-        <v/>
-      </c>
-      <c r="G37" s="23" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>Illawarra 5MW BESS (illustrative)</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>NSW</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>Wollongong, NSW</t>
-        </is>
-      </c>
-      <c r="D38" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="E38" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F38" s="25">
-        <f>D38*E38</f>
-        <v/>
-      </c>
-      <c r="G38" s="23" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>Latrobe 5MW BESS (illustrative)</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>VIC</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>Latrobe Valley, VIC</t>
-        </is>
-      </c>
-      <c r="D39" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="E39" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F39" s="25">
-        <f>D39*E39</f>
-        <v/>
-      </c>
-      <c r="G39" s="23" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Western Plains 5MW BESS (illustrative)</t>
+          <t>Riverina 5MW BESS (illustrative)</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>VIC</t>
+          <t>NSW</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Horsham, VIC</t>
+          <t>Wagga Wagga, NSW</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="E40" s="23" t="n">
+      <c r="E40" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="F40" s="25">
+      <c r="F40" s="27">
         <f>D40*E40</f>
         <v/>
       </c>
-      <c r="G40" s="23" t="n">
-        <v>2</v>
+      <c r="G40" s="25" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Mid-North 5MW BESS (illustrative)</t>
+          <t>Hunter Edge 5MW BESS (illustrative)</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>NSW</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Port Pirie, SA</t>
+          <t>Hunter Valley, NSW</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="E41" s="23" t="n">
+      <c r="E41" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" s="27">
+        <f>D41*E41</f>
+        <v/>
+      </c>
+      <c r="G41" s="25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Illawarra 5MW BESS (illustrative)</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>NSW</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>Wollongong, NSW</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="F41" s="25">
-        <f>D41*E41</f>
-        <v/>
-      </c>
-      <c r="G41" s="23" t="n">
+      <c r="F42" s="27">
+        <f>D42*E42</f>
+        <v/>
+      </c>
+      <c r="G42" s="25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Latrobe 5MW BESS (illustrative)</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>Latrobe Valley, VIC</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E43" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="27">
+        <f>D43*E43</f>
+        <v/>
+      </c>
+      <c r="G43" s="25" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>Western Plains 5MW BESS (illustrative)</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>Horsham, VIC</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" s="27">
+        <f>D44*E44</f>
+        <v/>
+      </c>
+      <c r="G44" s="25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Mid-North 5MW BESS (illustrative)</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>Port Pirie, SA</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E45" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" s="27">
+        <f>D45*E45</f>
+        <v/>
+      </c>
+      <c r="G45" s="25" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -4463,16 +4930,16 @@
           <t>Period number</t>
         </is>
       </c>
-      <c r="B3" s="26" t="n">
+      <c r="B3" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="26" t="n">
+      <c r="C3" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="26" t="n">
+      <c r="D3" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="26" t="n">
+      <c r="E3" s="28" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4482,19 +4949,19 @@
           <t>Year</t>
         </is>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="29">
         <f>$B$2+B3</f>
         <v/>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="29">
         <f>$B$2+C3</f>
         <v/>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="29">
         <f>$B$2+D3</f>
         <v/>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="29">
         <f>$B$2+E3</f>
         <v/>
       </c>
@@ -4505,19 +4972,19 @@
           <t>Discount factor @ live discount</t>
         </is>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="30">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^B3,0)</f>
         <v/>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="30">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^C3,0)</f>
         <v/>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="30">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^D3,0)</f>
         <v/>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="30">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^E3,0)</f>
         <v/>
       </c>
@@ -4565,7 +5032,7 @@
           <t>Scenario switch  (1=Conservative 2=Base 3=Ideal)</t>
         </is>
       </c>
-      <c r="B2" s="29" t="n">
+      <c r="B2" s="31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4613,13 +5080,13 @@
           <t>Development-approval rate (DA gate — the 40/65/80%)</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="26" t="n">
         <v>0.4</v>
       </c>
-      <c r="C5" s="24" t="n">
+      <c r="C5" s="26" t="n">
         <v>0.65</v>
       </c>
-      <c r="D5" s="24" t="n">
+      <c r="D5" s="26" t="n">
         <v>0.8</v>
       </c>
       <c r="E5" s="18">
@@ -4633,16 +5100,16 @@
           <t>RTB price multiplier</t>
         </is>
       </c>
-      <c r="B6" s="30" t="n">
+      <c r="B6" s="32" t="n">
         <v>0.85</v>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C6" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="30" t="n">
+      <c r="D6" s="32" t="n">
         <v>1.15</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="33">
         <f>CHOOSE('Scenarios'!$B$2,B6,C6,D6)</f>
         <v/>
       </c>
@@ -4653,16 +5120,16 @@
           <t>Dev cost multiplier</t>
         </is>
       </c>
-      <c r="B7" s="30" t="n">
+      <c r="B7" s="32" t="n">
         <v>1.05</v>
       </c>
-      <c r="C7" s="30" t="n">
+      <c r="C7" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="30" t="n">
+      <c r="D7" s="32" t="n">
         <v>0.97</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="33">
         <f>CHOOSE('Scenarios'!$B$2,B7,C7,D7)</f>
         <v/>
       </c>
@@ -4673,7 +5140,7 @@
           <t>Live discount rate (= base; scenarios don't move it)</t>
         </is>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="34">
         <f>'Inputs'!$C$7</f>
         <v/>
       </c>
@@ -4714,13 +5181,13 @@
           <t>Weight</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="26" t="n">
         <v>0.3</v>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="26" t="n">
         <v>0.5</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="26" t="n">
         <v>0.2</v>
       </c>
       <c r="E13" s="18">
@@ -4800,11 +5267,11 @@
           <t>Development approval (live scenario DA gate)</t>
         </is>
       </c>
-      <c r="B4" s="33">
+      <c r="B4" s="35">
         <f>'Scenarios'!$E$5</f>
         <v/>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="36">
         <f>B4</f>
         <v/>
       </c>
@@ -4815,11 +5282,11 @@
           <t>Grid connection</t>
         </is>
       </c>
-      <c r="B5" s="33">
-        <f>'Inputs'!$C$23</f>
-        <v/>
-      </c>
-      <c r="C5" s="34">
+      <c r="B5" s="35">
+        <f>'Inputs'!$C$27</f>
+        <v/>
+      </c>
+      <c r="C5" s="36">
         <f>C4*B5</f>
         <v/>
       </c>
@@ -4830,11 +5297,11 @@
           <t>Reach sale (flip exit)</t>
         </is>
       </c>
-      <c r="B6" s="33">
-        <f>'Inputs'!$C$24</f>
-        <v/>
-      </c>
-      <c r="C6" s="34">
+      <c r="B6" s="35">
+        <f>'Inputs'!$C$28</f>
+        <v/>
+      </c>
+      <c r="C6" s="36">
         <f>C5*B6</f>
         <v/>
       </c>
@@ -4845,7 +5312,7 @@
           <t>LIVE flip success (DA x connection x sale)</t>
         </is>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="37">
         <f>C6</f>
         <v/>
       </c>
@@ -4856,8 +5323,8 @@
           <t>Public-benchmark development approval</t>
         </is>
       </c>
-      <c r="C9" s="33">
-        <f>'Inputs'!$C$22</f>
+      <c r="C9" s="35">
+        <f>'Inputs'!$C$26</f>
         <v/>
       </c>
     </row>
@@ -4868,7 +5335,7 @@
         </is>
       </c>
       <c r="C10" s="18">
-        <f>C9*'Inputs'!$C$23*'Inputs'!$C$24</f>
+        <f>C9*'Inputs'!$C$27*'Inputs'!$C$28</f>
         <v/>
       </c>
     </row>
@@ -4878,7 +5345,7 @@
           <t>Manager's headline DA rate (Base — the '65%')</t>
         </is>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="35">
         <f>'Scenarios'!$C$5</f>
         <v/>
       </c>
@@ -4890,12 +5357,12 @@
         </is>
       </c>
       <c r="C13" s="18">
-        <f>'Scenarios'!$C$5*'Inputs'!$C$23*'Inputs'!$C$24</f>
+        <f>'Scenarios'!$C$5*'Inputs'!$C$27*'Inputs'!$C$28</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="C14" s="36">
+      <c r="C14" s="38">
         <f>IF(C13&lt;C12,"FLAG: 65% is the DA gate only","ok")</f>
         <v/>
       </c>
@@ -5034,348 +5501,348 @@
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <f>'Inputs'!$A$36</f>
-        <v/>
-      </c>
-      <c r="B4" s="37">
-        <f>'Inputs'!$B$36</f>
-        <v/>
-      </c>
-      <c r="C4" s="38">
-        <f>'Inputs'!$D$36</f>
-        <v/>
-      </c>
-      <c r="D4" s="39">
-        <f>'Inputs'!$G$36</f>
-        <v/>
-      </c>
-      <c r="E4" s="40">
-        <f>IFERROR(INDEX('Inputs'!$C$26:$C$28,MATCH(B4,'Inputs'!$A$26:$A$28,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F4" s="41">
+        <f>'Inputs'!$A$40</f>
+        <v/>
+      </c>
+      <c r="B4" s="39">
+        <f>'Inputs'!$B$40</f>
+        <v/>
+      </c>
+      <c r="C4" s="40">
+        <f>'Inputs'!$D$40</f>
+        <v/>
+      </c>
+      <c r="D4" s="41">
+        <f>'Inputs'!$G$40</f>
+        <v/>
+      </c>
+      <c r="E4" s="42">
+        <f>IFERROR(INDEX('Inputs'!$C$30:$C$32,MATCH(B4,'Inputs'!$A$30:$A$32,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F4" s="43">
         <f>'Scenarios'!$E$6</f>
         <v/>
       </c>
-      <c r="G4" s="42">
+      <c r="G4" s="44">
         <f>C4*E4*F4</f>
         <v/>
       </c>
-      <c r="H4" s="42">
-        <f>'Inputs'!$C$17*'Scenarios'!$E$7</f>
-        <v/>
-      </c>
-      <c r="I4" s="42">
+      <c r="H4" s="44">
+        <f>'Inputs'!$C$21*'Scenarios'!$E$7</f>
+        <v/>
+      </c>
+      <c r="I4" s="44">
         <f>G4-H4</f>
         <v/>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="35">
         <f>'Calc_Survival'!$C$7</f>
         <v/>
       </c>
-      <c r="K4" s="42">
+      <c r="K4" s="44">
         <f>I4*J4</f>
         <v/>
       </c>
-      <c r="L4" s="43">
+      <c r="L4" s="45">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^D4,0)</f>
         <v/>
       </c>
-      <c r="M4" s="42">
+      <c r="M4" s="44">
         <f>K4*L4</f>
         <v/>
       </c>
-      <c r="N4" s="42">
+      <c r="N4" s="44">
         <f>C4*E4</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <f>'Inputs'!$A$37</f>
-        <v/>
-      </c>
-      <c r="B5" s="37">
-        <f>'Inputs'!$B$37</f>
-        <v/>
-      </c>
-      <c r="C5" s="38">
-        <f>'Inputs'!$D$37</f>
-        <v/>
-      </c>
-      <c r="D5" s="39">
-        <f>'Inputs'!$G$37</f>
-        <v/>
-      </c>
-      <c r="E5" s="40">
-        <f>IFERROR(INDEX('Inputs'!$C$26:$C$28,MATCH(B5,'Inputs'!$A$26:$A$28,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F5" s="41">
+        <f>'Inputs'!$A$41</f>
+        <v/>
+      </c>
+      <c r="B5" s="39">
+        <f>'Inputs'!$B$41</f>
+        <v/>
+      </c>
+      <c r="C5" s="40">
+        <f>'Inputs'!$D$41</f>
+        <v/>
+      </c>
+      <c r="D5" s="41">
+        <f>'Inputs'!$G$41</f>
+        <v/>
+      </c>
+      <c r="E5" s="42">
+        <f>IFERROR(INDEX('Inputs'!$C$30:$C$32,MATCH(B5,'Inputs'!$A$30:$A$32,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F5" s="43">
         <f>'Scenarios'!$E$6</f>
         <v/>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="44">
         <f>C5*E5*F5</f>
         <v/>
       </c>
-      <c r="H5" s="42">
-        <f>'Inputs'!$C$17*'Scenarios'!$E$7</f>
-        <v/>
-      </c>
-      <c r="I5" s="42">
+      <c r="H5" s="44">
+        <f>'Inputs'!$C$21*'Scenarios'!$E$7</f>
+        <v/>
+      </c>
+      <c r="I5" s="44">
         <f>G5-H5</f>
         <v/>
       </c>
-      <c r="J5" s="33">
+      <c r="J5" s="35">
         <f>'Calc_Survival'!$C$7</f>
         <v/>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="44">
         <f>I5*J5</f>
         <v/>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="45">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^D5,0)</f>
         <v/>
       </c>
-      <c r="M5" s="42">
+      <c r="M5" s="44">
         <f>K5*L5</f>
         <v/>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="44">
         <f>C5*E5</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <f>'Inputs'!$A$38</f>
-        <v/>
-      </c>
-      <c r="B6" s="37">
-        <f>'Inputs'!$B$38</f>
-        <v/>
-      </c>
-      <c r="C6" s="38">
-        <f>'Inputs'!$D$38</f>
-        <v/>
-      </c>
-      <c r="D6" s="39">
-        <f>'Inputs'!$G$38</f>
-        <v/>
-      </c>
-      <c r="E6" s="40">
-        <f>IFERROR(INDEX('Inputs'!$C$26:$C$28,MATCH(B6,'Inputs'!$A$26:$A$28,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F6" s="41">
+        <f>'Inputs'!$A$42</f>
+        <v/>
+      </c>
+      <c r="B6" s="39">
+        <f>'Inputs'!$B$42</f>
+        <v/>
+      </c>
+      <c r="C6" s="40">
+        <f>'Inputs'!$D$42</f>
+        <v/>
+      </c>
+      <c r="D6" s="41">
+        <f>'Inputs'!$G$42</f>
+        <v/>
+      </c>
+      <c r="E6" s="42">
+        <f>IFERROR(INDEX('Inputs'!$C$30:$C$32,MATCH(B6,'Inputs'!$A$30:$A$32,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F6" s="43">
         <f>'Scenarios'!$E$6</f>
         <v/>
       </c>
-      <c r="G6" s="42">
+      <c r="G6" s="44">
         <f>C6*E6*F6</f>
         <v/>
       </c>
-      <c r="H6" s="42">
-        <f>'Inputs'!$C$17*'Scenarios'!$E$7</f>
-        <v/>
-      </c>
-      <c r="I6" s="42">
+      <c r="H6" s="44">
+        <f>'Inputs'!$C$21*'Scenarios'!$E$7</f>
+        <v/>
+      </c>
+      <c r="I6" s="44">
         <f>G6-H6</f>
         <v/>
       </c>
-      <c r="J6" s="33">
+      <c r="J6" s="35">
         <f>'Calc_Survival'!$C$7</f>
         <v/>
       </c>
-      <c r="K6" s="42">
+      <c r="K6" s="44">
         <f>I6*J6</f>
         <v/>
       </c>
-      <c r="L6" s="43">
+      <c r="L6" s="45">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^D6,0)</f>
         <v/>
       </c>
-      <c r="M6" s="42">
+      <c r="M6" s="44">
         <f>K6*L6</f>
         <v/>
       </c>
-      <c r="N6" s="42">
+      <c r="N6" s="44">
         <f>C6*E6</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <f>'Inputs'!$A$39</f>
-        <v/>
-      </c>
-      <c r="B7" s="37">
-        <f>'Inputs'!$B$39</f>
-        <v/>
-      </c>
-      <c r="C7" s="38">
-        <f>'Inputs'!$D$39</f>
-        <v/>
-      </c>
-      <c r="D7" s="39">
-        <f>'Inputs'!$G$39</f>
-        <v/>
-      </c>
-      <c r="E7" s="40">
-        <f>IFERROR(INDEX('Inputs'!$C$26:$C$28,MATCH(B7,'Inputs'!$A$26:$A$28,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F7" s="41">
+        <f>'Inputs'!$A$43</f>
+        <v/>
+      </c>
+      <c r="B7" s="39">
+        <f>'Inputs'!$B$43</f>
+        <v/>
+      </c>
+      <c r="C7" s="40">
+        <f>'Inputs'!$D$43</f>
+        <v/>
+      </c>
+      <c r="D7" s="41">
+        <f>'Inputs'!$G$43</f>
+        <v/>
+      </c>
+      <c r="E7" s="42">
+        <f>IFERROR(INDEX('Inputs'!$C$30:$C$32,MATCH(B7,'Inputs'!$A$30:$A$32,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F7" s="43">
         <f>'Scenarios'!$E$6</f>
         <v/>
       </c>
-      <c r="G7" s="42">
+      <c r="G7" s="44">
         <f>C7*E7*F7</f>
         <v/>
       </c>
-      <c r="H7" s="42">
-        <f>'Inputs'!$C$17*'Scenarios'!$E$7</f>
-        <v/>
-      </c>
-      <c r="I7" s="42">
+      <c r="H7" s="44">
+        <f>'Inputs'!$C$21*'Scenarios'!$E$7</f>
+        <v/>
+      </c>
+      <c r="I7" s="44">
         <f>G7-H7</f>
         <v/>
       </c>
-      <c r="J7" s="33">
+      <c r="J7" s="35">
         <f>'Calc_Survival'!$C$7</f>
         <v/>
       </c>
-      <c r="K7" s="42">
+      <c r="K7" s="44">
         <f>I7*J7</f>
         <v/>
       </c>
-      <c r="L7" s="43">
+      <c r="L7" s="45">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^D7,0)</f>
         <v/>
       </c>
-      <c r="M7" s="42">
+      <c r="M7" s="44">
         <f>K7*L7</f>
         <v/>
       </c>
-      <c r="N7" s="42">
+      <c r="N7" s="44">
         <f>C7*E7</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <f>'Inputs'!$A$40</f>
-        <v/>
-      </c>
-      <c r="B8" s="37">
-        <f>'Inputs'!$B$40</f>
-        <v/>
-      </c>
-      <c r="C8" s="38">
-        <f>'Inputs'!$D$40</f>
-        <v/>
-      </c>
-      <c r="D8" s="39">
-        <f>'Inputs'!$G$40</f>
-        <v/>
-      </c>
-      <c r="E8" s="40">
-        <f>IFERROR(INDEX('Inputs'!$C$26:$C$28,MATCH(B8,'Inputs'!$A$26:$A$28,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F8" s="41">
+        <f>'Inputs'!$A$44</f>
+        <v/>
+      </c>
+      <c r="B8" s="39">
+        <f>'Inputs'!$B$44</f>
+        <v/>
+      </c>
+      <c r="C8" s="40">
+        <f>'Inputs'!$D$44</f>
+        <v/>
+      </c>
+      <c r="D8" s="41">
+        <f>'Inputs'!$G$44</f>
+        <v/>
+      </c>
+      <c r="E8" s="42">
+        <f>IFERROR(INDEX('Inputs'!$C$30:$C$32,MATCH(B8,'Inputs'!$A$30:$A$32,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="43">
         <f>'Scenarios'!$E$6</f>
         <v/>
       </c>
-      <c r="G8" s="42">
+      <c r="G8" s="44">
         <f>C8*E8*F8</f>
         <v/>
       </c>
-      <c r="H8" s="42">
-        <f>'Inputs'!$C$17*'Scenarios'!$E$7</f>
-        <v/>
-      </c>
-      <c r="I8" s="42">
+      <c r="H8" s="44">
+        <f>'Inputs'!$C$21*'Scenarios'!$E$7</f>
+        <v/>
+      </c>
+      <c r="I8" s="44">
         <f>G8-H8</f>
         <v/>
       </c>
-      <c r="J8" s="33">
+      <c r="J8" s="35">
         <f>'Calc_Survival'!$C$7</f>
         <v/>
       </c>
-      <c r="K8" s="42">
+      <c r="K8" s="44">
         <f>I8*J8</f>
         <v/>
       </c>
-      <c r="L8" s="43">
+      <c r="L8" s="45">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^D8,0)</f>
         <v/>
       </c>
-      <c r="M8" s="42">
+      <c r="M8" s="44">
         <f>K8*L8</f>
         <v/>
       </c>
-      <c r="N8" s="42">
+      <c r="N8" s="44">
         <f>C8*E8</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <f>'Inputs'!$A$41</f>
-        <v/>
-      </c>
-      <c r="B9" s="37">
-        <f>'Inputs'!$B$41</f>
-        <v/>
-      </c>
-      <c r="C9" s="38">
-        <f>'Inputs'!$D$41</f>
-        <v/>
-      </c>
-      <c r="D9" s="39">
-        <f>'Inputs'!$G$41</f>
-        <v/>
-      </c>
-      <c r="E9" s="40">
-        <f>IFERROR(INDEX('Inputs'!$C$26:$C$28,MATCH(B9,'Inputs'!$A$26:$A$28,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F9" s="41">
+        <f>'Inputs'!$A$45</f>
+        <v/>
+      </c>
+      <c r="B9" s="39">
+        <f>'Inputs'!$B$45</f>
+        <v/>
+      </c>
+      <c r="C9" s="40">
+        <f>'Inputs'!$D$45</f>
+        <v/>
+      </c>
+      <c r="D9" s="41">
+        <f>'Inputs'!$G$45</f>
+        <v/>
+      </c>
+      <c r="E9" s="42">
+        <f>IFERROR(INDEX('Inputs'!$C$30:$C$32,MATCH(B9,'Inputs'!$A$30:$A$32,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F9" s="43">
         <f>'Scenarios'!$E$6</f>
         <v/>
       </c>
-      <c r="G9" s="42">
+      <c r="G9" s="44">
         <f>C9*E9*F9</f>
         <v/>
       </c>
-      <c r="H9" s="42">
-        <f>'Inputs'!$C$17*'Scenarios'!$E$7</f>
-        <v/>
-      </c>
-      <c r="I9" s="42">
+      <c r="H9" s="44">
+        <f>'Inputs'!$C$21*'Scenarios'!$E$7</f>
+        <v/>
+      </c>
+      <c r="I9" s="44">
         <f>G9-H9</f>
         <v/>
       </c>
-      <c r="J9" s="33">
+      <c r="J9" s="35">
         <f>'Calc_Survival'!$C$7</f>
         <v/>
       </c>
-      <c r="K9" s="42">
+      <c r="K9" s="44">
         <f>I9*J9</f>
         <v/>
       </c>
-      <c r="L9" s="43">
+      <c r="L9" s="45">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^D9,0)</f>
         <v/>
       </c>
-      <c r="M9" s="42">
+      <c r="M9" s="44">
         <f>K9*L9</f>
         <v/>
       </c>
-      <c r="N9" s="42">
+      <c r="N9" s="44">
         <f>C9*E9</f>
         <v/>
       </c>
@@ -5386,19 +5853,19 @@
           <t>Pipeline total (representative)</t>
         </is>
       </c>
-      <c r="C10" s="44">
+      <c r="C10" s="46">
         <f>SUM(C4:C9)</f>
         <v/>
       </c>
-      <c r="G10" s="45">
+      <c r="G10" s="47">
         <f>SUM(G4:G9)</f>
         <v/>
       </c>
-      <c r="H10" s="45">
+      <c r="H10" s="47">
         <f>SUM(H4:H9)</f>
         <v/>
       </c>
-      <c r="M10" s="45">
+      <c r="M10" s="47">
         <f>SUM(M4:M9)</f>
         <v/>
       </c>
@@ -5409,7 +5876,7 @@
           <t>Blended RTB sale per project (@1x)</t>
         </is>
       </c>
-      <c r="M11" s="46">
+      <c r="M11" s="48">
         <f>AVERAGE('Calc_Project_rNPV'!$N$4:$N$9)</f>
         <v/>
       </c>
@@ -5429,7 +5896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -5443,7 +5910,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CALC — FUND FUNNEL, FEES &amp; INVESTOR RETURN (live scenario)</t>
+          <t>CALC — THE COMPANY'S DEVELOPMENT PROGRAMME &amp; EXIT EQUITY VALUE (live scenario)</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
@@ -5455,24 +5922,24 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>The funnel: projects_started = target ÷ success (widens as success falls). Full dev cost on delivered + partial on dropouts. Fees: entry + management + carry over the hurdle. Investor IRR is closed-form over the effective hold (so it reproduces in any Excel). All figures AUD $m.</t>
+          <t>The company's own business plan (no fund fees, no carry): the funnel widens as success falls (projects_started = target ÷ flip success). Net programme profit = gross proceeds − total development cost. We value the company at exit as a repeatable platform = net profit × the platform exit multiple. All figures AUD $m.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Funnel (live scenario)</t>
+          <t>Development funnel (live scenario)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Live cumulative success</t>
-        </is>
-      </c>
-      <c r="C5" s="33">
+          <t>Live flip success (DA × conn × sale)</t>
+        </is>
+      </c>
+      <c r="C5" s="35">
         <f>'Calc_Survival'!$C$7</f>
         <v/>
       </c>
@@ -5483,7 +5950,7 @@
           <t>Projects target (delivered &amp; sold)</t>
         </is>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="40">
         <f>'Inputs'!$C$10</f>
         <v/>
       </c>
@@ -5494,7 +5961,7 @@
           <t>Projects started (funnel)</t>
         </is>
       </c>
-      <c r="C7" s="47">
+      <c r="C7" s="49">
         <f>IFERROR(C6/C5,0)</f>
         <v/>
       </c>
@@ -5505,7 +5972,7 @@
           <t>Projects failed (dropouts)</t>
         </is>
       </c>
-      <c r="C8" s="47">
+      <c r="C8" s="49">
         <f>C7-C6</f>
         <v/>
       </c>
@@ -5516,8 +5983,8 @@
           <t>Dev cost per project (live)</t>
         </is>
       </c>
-      <c r="C9" s="42">
-        <f>'Inputs'!$C$17*'Scenarios'!$E$7</f>
+      <c r="C9" s="44">
+        <f>'Inputs'!$C$21*'Scenarios'!$E$7</f>
         <v/>
       </c>
     </row>
@@ -5527,15 +5994,15 @@
           <t>Total development cost</t>
         </is>
       </c>
-      <c r="C10" s="48">
-        <f>C6*C9+C8*'Inputs'!$C$18*C9</f>
+      <c r="C10" s="50">
+        <f>C6*C9+C8*'Inputs'!$C$22*C9</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Proceeds &amp; fees</t>
+          <t>Proceeds &amp; net programme profit</t>
         </is>
       </c>
     </row>
@@ -5545,7 +6012,7 @@
           <t>Blended RTB sale per project (live)</t>
         </is>
       </c>
-      <c r="C12" s="42">
+      <c r="C12" s="44">
         <f>'Calc_Project_rNPV'!$M$11*'Scenarios'!$E$6</f>
         <v/>
       </c>
@@ -5556,158 +6023,48 @@
           <t>Gross proceeds</t>
         </is>
       </c>
-      <c r="C13" s="48">
+      <c r="C13" s="50">
         <f>C6*C12</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Entry fee</t>
-        </is>
-      </c>
-      <c r="C14" s="48">
-        <f>'Inputs'!$C$12*'Inputs'!$C$9</f>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Net programme profit (gross − total dev cost)</t>
+        </is>
+      </c>
+      <c r="C14" s="50">
+        <f>C13-C10</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>Management fee (total)</t>
-        </is>
-      </c>
-      <c r="C15" s="48">
-        <f>'Inputs'!$C$13*'Inputs'!$C$9*'Inputs'!$C$11</f>
-        <v/>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Company exit equity value (live)</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Invested capital (LP, called)</t>
-        </is>
-      </c>
-      <c r="C16" s="49">
-        <f>C10+C14+C15</f>
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Platform exit multiple</t>
+        </is>
+      </c>
+      <c r="C16" s="43">
+        <f>'Inputs'!$C$18</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Carry, distributions &amp; return (live)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Profit before carry</t>
-        </is>
-      </c>
-      <c r="C18" s="48">
-        <f>C13-C16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Hurdle factor = (1+hurdle)^term − 1</t>
-        </is>
-      </c>
-      <c r="C19" s="34">
-        <f>(1+'Inputs'!$C$15)^'Inputs'!$C$11-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>Hurdle amount</t>
-        </is>
-      </c>
-      <c r="C20" s="48">
-        <f>C16*C19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>Carry to GP</t>
-        </is>
-      </c>
-      <c r="C21" s="48">
-        <f>'Inputs'!$C$14*MAX(0,C18-C20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Distributions to LP</t>
-        </is>
-      </c>
-      <c r="C22" s="48">
-        <f>C13-C21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>MOIC (net)</t>
-        </is>
-      </c>
-      <c r="C23" s="50">
-        <f>IFERROR(C22/C16,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>Mean distribution period (yrs)</t>
-        </is>
-      </c>
-      <c r="C24" s="47">
-        <f>SUMPRODUCT('Timeline'!$B$3:$E$3,'Inputs'!$C$33:$F$33)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>Mean capital-call period (yrs)</t>
-        </is>
-      </c>
-      <c r="C25" s="47">
-        <f>SUMPRODUCT('Timeline'!$B$3:$E$3,'Inputs'!$C$32:$F$32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Effective hold (yrs)</t>
-        </is>
-      </c>
-      <c r="C26" s="47">
-        <f>C24-C25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Investor IRR (live, closed-form)</t>
-        </is>
-      </c>
-      <c r="C27" s="35">
-        <f>IFERROR(C23^(1/C26)-1,0)</f>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Company exit equity = MAX(0, net) × multiple</t>
+        </is>
+      </c>
+      <c r="C17" s="51">
+        <f>MAX(0,C14)*C16</f>
         <v/>
       </c>
     </row>

--- a/financial_models/BESS_Valuation.xlsx
+++ b/financial_models/BESS_Valuation.xlsx
@@ -154,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -246,6 +246,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="167" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
@@ -755,7 +756,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>'Checks'!$B$20</f>
+        <f>'Checks'!$B$22</f>
         <v/>
       </c>
     </row>
@@ -848,7 +849,7 @@
     <row r="19">
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>FAST / ICAEW / Macabacus / Operis: Inputs→Calcs→Outputs zones; one Timeline; one-row-one-calc; no hardcodes in formulas; CHOOSE scenario switch + live-case row; checks built alongside; colour code (blue input / black formula / green link); INDEX-MATCH not VLOOKUP; IFERROR on division; closed-form IRR (no volatile functions).</t>
+          <t>FAST / ICAEW / Macabacus / Operis + VC-method structure: Inputs→Calcs→Outputs zones; one Timeline; one-row-one-calc; no hardcodes in formulas; CHOOSE scenario switch + live-case row; checks built alongside; colour code (blue input / black formula / green link); INDEX-MATCH not VLOOKUP; IFERROR on division. VC method: work back from the company's exit equity value through the cap table; ownership = investment ÷ post-money; the required/target return (≥25%, VC cross-check) is a RETURN HURDLE that compensates for failure risk — NOT a WACC — and failure risk is also handled explicitly via First-Chicago scenario weighting.</t>
         </is>
       </c>
     </row>
@@ -882,13 +883,14 @@
     <row r="31">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>1. Trace every formula + colour audit; confirm master check = OK; stress the switch in all 3 positions.  2. Replace BENCHMARK / claim inputs with verified independent values (RTB comps, per-state success, dev cost) and CONFIRM the cap-table terms against a term sheet.  3. Stress a downside where RTB prices are 20–30% lower and success ≈ the independent benchmark; confirm our shares can be wiped out (Conservative = total loss).</t>
+          <t>1. Trace every formula + colour audit; confirm master check = OK; stress the switch in all 3 positions.  2. Replace BENCHMARK / claim inputs with verified independent values (RTB comps, per-state success, dev cost) and CONFIRM the cap-table terms against a term sheet.  3. Stress a downside where RTB prices are 20–30% lower and success ≈ the independent benchmark; confirm our shares can be wiped out (Conservative = total loss).  4. Depth left out: a SINGLE funding round and a 1× NON-PARTICIPATING liquidation preference are scaffolded — add later rounds (Series B/C) to the cap table, and participation / anti-dilution / accrued preferred dividends if the term sheet carries them.</t>
         </is>
       </c>
     </row>
     <row r="32"/>
     <row r="33"/>
     <row r="34"/>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
@@ -906,9 +908,9 @@
     <row r="39"/>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B31:B35"/>
+    <mergeCell ref="B19:B22"/>
     <mergeCell ref="B36:B39"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="B31:B34"/>
     <mergeCell ref="B25:B28"/>
   </mergeCells>
   <conditionalFormatting sqref="B8">
@@ -933,7 +935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1507,6 +1509,154 @@
       </c>
       <c r="C41" s="47">
         <f>MAX(C36:C38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Full cap table — who owns what (mechanical; ties to 100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Holder</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>At entry %</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>At exit (diluted) %</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>Founders / existing holders</t>
+        </is>
+      </c>
+      <c r="B45" s="36">
+        <f>1-'Returns'!$B$7</f>
+        <v/>
+      </c>
+      <c r="C45" s="36">
+        <f>(1-'Returns'!$B$7)*(1-'Inputs'!$C$15)*(1-'Inputs'!$C$16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Us (new investor)</t>
+        </is>
+      </c>
+      <c r="B46" s="35">
+        <f>'Returns'!$B$7</f>
+        <v/>
+      </c>
+      <c r="C46" s="57">
+        <f>'Returns'!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>Option pool (staff)</t>
+        </is>
+      </c>
+      <c r="B47" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="36">
+        <f>'Inputs'!$C$15*(1-'Inputs'!$C$16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>Future-round investors</t>
+        </is>
+      </c>
+      <c r="B48" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="35">
+        <f>'Inputs'!$C$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Total (must = 100%)</t>
+        </is>
+      </c>
+      <c r="B49" s="18">
+        <f>SUM(B45:B48)</f>
+        <v/>
+      </c>
+      <c r="C49" s="18">
+        <f>SUM(C45:C48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Exit waterfall (Base) — full distribution of exit equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>Company exit equity (Base)</t>
+        </is>
+      </c>
+      <c r="C52" s="56">
+        <f>'Returns'!$C$21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Our proceeds (1x pref / as-converted)</t>
+        </is>
+      </c>
+      <c r="C53" s="56">
+        <f>'Returns'!$C$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>Other holders' proceeds (residual)</t>
+        </is>
+      </c>
+      <c r="C54" s="44">
+        <f>C52-C53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Distributed (ours + others = exit equity)</t>
+        </is>
+      </c>
+      <c r="C55" s="47">
+        <f>C53+C54</f>
         <v/>
       </c>
     </row>
@@ -1746,11 +1896,11 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="B22" s="57">
+      <c r="B22" s="58">
         <f>'Inputs'!$C$30</f>
         <v/>
       </c>
-      <c r="C22" s="57">
+      <c r="C22" s="58">
         <f>'Inputs'!$C$24</f>
         <v/>
       </c>
@@ -1765,11 +1915,11 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="B23" s="57">
+      <c r="B23" s="58">
         <f>'Inputs'!$C$31</f>
         <v/>
       </c>
-      <c r="C23" s="57">
+      <c r="C23" s="58">
         <f>'Inputs'!$C$24</f>
         <v/>
       </c>
@@ -1784,11 +1934,11 @@
           <t>SA</t>
         </is>
       </c>
-      <c r="B24" s="57">
+      <c r="B24" s="58">
         <f>'Inputs'!$C$32</f>
         <v/>
       </c>
-      <c r="C24" s="57">
+      <c r="C24" s="58">
         <f>'Inputs'!$C$24</f>
         <v/>
       </c>
@@ -1927,7 +2077,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="58" t="inlineStr">
+      <c r="B10" s="59" t="inlineStr">
         <is>
           <t>Price mult →</t>
         </is>
@@ -1964,79 +2114,79 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="58" t="inlineStr">
+      <c r="B11" s="59" t="inlineStr">
         <is>
           <t>Gross $m →</t>
         </is>
       </c>
-      <c r="C11" s="59">
+      <c r="C11" s="60">
         <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*C10</f>
         <v/>
       </c>
-      <c r="D11" s="59">
+      <c r="D11" s="60">
         <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*D10</f>
         <v/>
       </c>
-      <c r="E11" s="59">
+      <c r="E11" s="60">
         <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*E10</f>
         <v/>
       </c>
-      <c r="F11" s="59">
+      <c r="F11" s="60">
         <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*F10</f>
         <v/>
       </c>
-      <c r="G11" s="59">
+      <c r="G11" s="60">
         <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*G10</f>
         <v/>
       </c>
-      <c r="M11" s="59">
+      <c r="M11" s="60">
         <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*M10</f>
         <v/>
       </c>
-      <c r="N11" s="59">
+      <c r="N11" s="60">
         <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*N10</f>
         <v/>
       </c>
-      <c r="O11" s="59">
+      <c r="O11" s="60">
         <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*O10</f>
         <v/>
       </c>
-      <c r="P11" s="59">
+      <c r="P11" s="60">
         <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*P10</f>
         <v/>
       </c>
-      <c r="Q11" s="59">
+      <c r="Q11" s="60">
         <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*Q10</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="60" t="inlineStr">
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t>DA gate ↓</t>
         </is>
       </c>
-      <c r="C12" s="60" t="inlineStr">
+      <c r="C12" s="61" t="inlineStr">
         <is>
           <t>IRR</t>
         </is>
       </c>
-      <c r="D12" s="60" t="inlineStr">
+      <c r="D12" s="61" t="inlineStr">
         <is>
           <t>IRR</t>
         </is>
       </c>
-      <c r="E12" s="60" t="inlineStr">
+      <c r="E12" s="61" t="inlineStr">
         <is>
           <t>IRR</t>
         </is>
       </c>
-      <c r="F12" s="60" t="inlineStr">
+      <c r="F12" s="61" t="inlineStr">
         <is>
           <t>IRR</t>
         </is>
       </c>
-      <c r="G12" s="60" t="inlineStr">
+      <c r="G12" s="61" t="inlineStr">
         <is>
           <t>IRR</t>
         </is>
@@ -2382,7 +2532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -2630,11 +2780,11 @@
           <t>Weighting sanity (helpers E:G)</t>
         </is>
       </c>
-      <c r="E16" s="61">
+      <c r="E16" s="62">
         <f>MIN('Returns'!$B$26:$D$26)</f>
         <v/>
       </c>
-      <c r="F16" s="61">
+      <c r="F16" s="62">
         <f>MAX('Returns'!$B$26:$D$26)</f>
         <v/>
       </c>
@@ -2687,19 +2837,51 @@
         <v/>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Cap table ties (ownership sums to 100%)</t>
+        </is>
+      </c>
+      <c r="B19" s="38">
+        <f>IF(AND(ABS('Returns'!$B$49-1)&lt;0.001,ABS('Returns'!$C$49-1)&lt;0.001),"OK","ERROR")</f>
+        <v/>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>VC cap-table integrity</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Exit equity fully distributed (ours + others)</t>
+        </is>
+      </c>
+      <c r="B20" s="38">
+        <f>IF(ABS('Returns'!$C$55-'Returns'!$C$52)&lt;0.001,"OK","ERROR")</f>
+        <v/>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>VC waterfall integrity</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>MASTER CHECK</t>
         </is>
       </c>
-      <c r="B20" s="62">
-        <f>IF(COUNTIF(B4:B18,"ERROR")=0,"OK","ERROR")</f>
+      <c r="B22" s="63">
+        <f>IF(COUNTIF(B4:B20,"ERROR")=0,"OK","ERROR")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:B20">
+  <conditionalFormatting sqref="B4:B22">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -2765,8 +2947,8 @@
           <t>Master check</t>
         </is>
       </c>
-      <c r="E4" s="63">
-        <f>'Checks'!$B$20</f>
+      <c r="E4" s="64">
+        <f>'Checks'!$B$22</f>
         <v/>
       </c>
     </row>
@@ -2808,7 +2990,7 @@
           <t>Expected MOIC</t>
         </is>
       </c>
-      <c r="B8" s="64">
+      <c r="B8" s="65">
         <f>'Returns'!$E$32</f>
         <v/>
       </c>
@@ -2839,7 +3021,7 @@
           <t>Liquidation preference (x)</t>
         </is>
       </c>
-      <c r="E10" s="64">
+      <c r="E10" s="65">
         <f>'Inputs'!$C$17</f>
         <v/>
       </c>
@@ -2883,7 +3065,7 @@
           <t>Equity IRR</t>
         </is>
       </c>
-      <c r="D14" s="65" t="inlineStr">
+      <c r="D14" s="66" t="inlineStr">
         <is>
           <t>Programme capital $m</t>
         </is>
@@ -2907,7 +3089,7 @@
         <f>'Returns'!$B$26</f>
         <v/>
       </c>
-      <c r="D15" s="66" t="inlineStr">
+      <c r="D15" s="67" t="inlineStr">
         <is>
           <t>Projects target</t>
         </is>
@@ -2931,7 +3113,7 @@
         <f>'Returns'!$C$26</f>
         <v/>
       </c>
-      <c r="D16" s="66" t="inlineStr">
+      <c r="D16" s="67" t="inlineStr">
         <is>
           <t>Manager headline DA gate (Base)</t>
         </is>
@@ -2955,7 +3137,7 @@
         <f>'Returns'!$D$26</f>
         <v/>
       </c>
-      <c r="D17" s="66" t="inlineStr">
+      <c r="D17" s="67" t="inlineStr">
         <is>
           <t>True flip success (Base, DAxconnxsale)</t>
         </is>

--- a/financial_models/BESS_Valuation.xlsx
+++ b/financial_models/BESS_Valuation.xlsx
@@ -154,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -193,7 +193,6 @@
     <xf numFmtId="165" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -201,6 +200,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -238,8 +238,8 @@
     <xf numFmtId="167" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -248,6 +248,7 @@
     <xf numFmtId="167" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -698,7 +699,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>v2.0</t>
+          <t>v3.0</t>
         </is>
       </c>
     </row>
@@ -756,7 +757,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>'Checks'!$B$22</f>
+        <f>'Checks'!$B$23</f>
         <v/>
       </c>
     </row>
@@ -794,46 +795,58 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Reframe</t>
+          <t>Exit basis</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>The company sells RTB before construction — MERCHANT RISK PASSES TO THE BUYER. Its risk is the survival curve (approve→connect→sell) + the RTB price; ours is also dilution and the cap-table terms.</t>
+          <t>PRIMARY exit equity = forward-pipeline rNPV (projects in flight at exit) + retained cash − debt — what a buyer of a development platform pays. The earnings multiple is a CROSS-CHECK only (run-rate × a sourced low/base/high range). Pipeline depth at exit is the main sensitivity (Exhibit D).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Outputs</t>
+          <t>Reframe</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Cap table, return on our shares (equity IRR &amp; MOIC) by scenario, First-Chicago expected return, per-pipeline valuation cross-check, sensitivities.</t>
+          <t>The company sells RTB before construction — MERCHANT RISK PASSES TO THE BUYER. Its risk is the survival curve (approve→connect→sell) + the RTB price; ours is also dilution and the cap-table terms.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Detail / horizon</t>
+          <t>Outputs</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Company programme ~2+1-year cycle; our exit year is a placeholder. AUD, $m.</t>
+          <t>Cap table, return on our shares (equity IRR &amp; MOIC) by scenario, First-Chicago expected return, forward-pipeline exit + earnings-multiple cross-check, per-pipeline valuation cross-check, sensitivities.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Detail / horizon</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Company programme ~2+1-year cycle; our exit year is a placeholder. AUD, $m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Out of scope</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Post-sale operating/merchant cash flows, construction (buyer-funded), full multi-round waterfall, tax structuring, FX, debt.</t>
         </is>
@@ -866,7 +879,7 @@
     <row r="25">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Discount rate &amp; premium • the THREE scenario success rates (vs the independent benchmark) • RTB $/MW by state (need independent comps) • dev cost per project &amp; abandonment • the equity-deal terms (pre-money, our cheque, option pool, future dilution, liquidation preference, platform exit multiple, exit year — ALL placeholders). Founder/manager figures are CLAIMS to verify — defend your own.</t>
+          <t>Discount rate &amp; premium • the THREE scenario success rates (vs the independent benchmark) • RTB $/MW by state (need independent comps) • dev cost per project &amp; abandonment • the equity-deal terms (pre-money, our cheque, option pool, future dilution, liquidation preference, exit year) • the EXIT-VALUE drivers (pipeline depth at exit, distribution fraction, debt at exit, and the cross-check multiple range — ALL placeholders). Founder/manager figures are CLAIMS to verify — defend your own.</t>
         </is>
       </c>
     </row>
@@ -883,7 +896,7 @@
     <row r="31">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>1. Trace every formula + colour audit; confirm master check = OK; stress the switch in all 3 positions.  2. Replace BENCHMARK / claim inputs with verified independent values (RTB comps, per-state success, dev cost) and CONFIRM the cap-table terms against a term sheet.  3. Stress a downside where RTB prices are 20–30% lower and success ≈ the independent benchmark; confirm our shares can be wiped out (Conservative = total loss).  4. Depth left out: a SINGLE funding round and a 1× NON-PARTICIPATING liquidation preference are scaffolded — add later rounds (Series B/C) to the cap table, and participation / anti-dilution / accrued preferred dividends if the term sheet carries them.</t>
+          <t>1. Trace every formula + colour audit; confirm master check = OK; stress the switch in all 3 positions.  2. Replace BENCHMARK / claim inputs with verified independent values (RTB comps, per-state success, dev cost) and CONFIRM the cap-table terms against a term sheet.  3. Stress a downside where RTB prices are 20–30% lower and success ≈ the independent benchmark; confirm our shares can be wiped out (Conservative = total loss).  4. Pressure-test the EXIT BASIS (now the biggest swing factor): vary pipeline depth at exit and the discount rate (Exhibit D); confirm comps if any (else the pipeline basis stands).  5. Depth left out: a SINGLE funding round and a 1× NON-PARTICIPATING liquidation preference are scaffolded — add later rounds (Series B/C) to the cap table, and participation / anti-dilution / accrued preferred dividends if the term sheet carries them.</t>
         </is>
       </c>
     </row>
@@ -935,7 +948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -960,7 +973,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>We buy SHARES directly. Ownership = our investment ÷ post-money, reduced by dilution. Each scenario's company exit equity value (net programme profit × the platform exit multiple) flows through the cap table; our proceeds = the GREATER of our 1× liquidation preference or our as-converted (diluted) share. All figures AUD $m unless stated.</t>
+          <t>We buy SHARES directly. Ownership = our investment ÷ post-money, reduced by dilution. Each scenario's company exit equity value (PRIMARY basis: forward-pipeline rNPV + retained cash − debt) flows through the cap table; our TERMINAL proceeds = the GREATER of our 1× liquidation preference or our as-converted (diluted) share, plus any INTERIM distributions (convention (b); dist fraction is a placeholder, default 0). All figures AUD $m unless stated.</t>
         </is>
       </c>
     </row>
@@ -977,7 +990,7 @@
           <t>Pre-money valuation</t>
         </is>
       </c>
-      <c r="B4" s="52">
+      <c r="B4" s="51">
         <f>'Inputs'!$C$13</f>
         <v/>
       </c>
@@ -988,7 +1001,7 @@
           <t>Our investment</t>
         </is>
       </c>
-      <c r="B5" s="52">
+      <c r="B5" s="51">
         <f>'Inputs'!$C$14</f>
         <v/>
       </c>
@@ -1210,7 +1223,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>Net programme profit</t>
+          <t>Realised net programme profit</t>
         </is>
       </c>
       <c r="B20" s="50">
@@ -1229,434 +1242,510 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Company exit equity = MAX(0,net)×mult</t>
-        </is>
-      </c>
-      <c r="B21" s="50">
-        <f>MAX(0,B20)*'Inputs'!$C$18</f>
-        <v/>
-      </c>
-      <c r="C21" s="50">
-        <f>MAX(0,C20)*'Inputs'!$C$18</f>
-        <v/>
-      </c>
-      <c r="D21" s="50">
-        <f>MAX(0,D20)*'Inputs'!$C$18</f>
+          <t>Forward pipeline rNPV at exit (depth × per-project)</t>
+        </is>
+      </c>
+      <c r="B21" s="44">
+        <f>'Inputs'!$C$48*('Calc_Project_rNPV'!$M$11*B13-B15)*B12*'Calc_Company'!$C$18</f>
+        <v/>
+      </c>
+      <c r="C21" s="44">
+        <f>'Inputs'!$C$48*('Calc_Project_rNPV'!$M$11*C13-C15)*C12*'Calc_Company'!$C$18</f>
+        <v/>
+      </c>
+      <c r="D21" s="44">
+        <f>'Inputs'!$C$48*('Calc_Project_rNPV'!$M$11*D13-D15)*D12*'Calc_Company'!$C$18</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
+          <t>Net cash retained = MAX(0,realised)×(1−dist)</t>
+        </is>
+      </c>
+      <c r="B22" s="44">
+        <f>MAX(0,B20)*(1-'Inputs'!$C$49)</f>
+        <v/>
+      </c>
+      <c r="C22" s="44">
+        <f>MAX(0,C20)*(1-'Inputs'!$C$49)</f>
+        <v/>
+      </c>
+      <c r="D22" s="44">
+        <f>MAX(0,D20)*(1-'Inputs'!$C$49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Company exit equity = fwd + retained − debt</t>
+        </is>
+      </c>
+      <c r="B23" s="53">
+        <f>MAX(0,B21+B22-'Inputs'!$C$50)</f>
+        <v/>
+      </c>
+      <c r="C23" s="53">
+        <f>MAX(0,C21+C22-'Inputs'!$C$50)</f>
+        <v/>
+      </c>
+      <c r="D23" s="53">
+        <f>MAX(0,D21+D22-'Inputs'!$C$50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
           <t>As-converted (diluted × exit equity)</t>
         </is>
       </c>
-      <c r="B22" s="44">
-        <f>'Returns'!$B$8*B21</f>
-        <v/>
-      </c>
-      <c r="C22" s="44">
-        <f>'Returns'!$B$8*C21</f>
-        <v/>
-      </c>
-      <c r="D22" s="44">
-        <f>'Returns'!$B$8*D21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="B24" s="44">
+        <f>'Returns'!$B$8*B23</f>
+        <v/>
+      </c>
+      <c r="C24" s="44">
+        <f>'Returns'!$B$8*C23</f>
+        <v/>
+      </c>
+      <c r="D24" s="44">
+        <f>'Returns'!$B$8*D23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Preference claim = MIN(liq×inv, exit eq)</t>
         </is>
       </c>
-      <c r="B23" s="44">
-        <f>MIN('Inputs'!$C$17*'Inputs'!$C$14,B21)</f>
-        <v/>
-      </c>
-      <c r="C23" s="44">
-        <f>MIN('Inputs'!$C$17*'Inputs'!$C$14,C21)</f>
-        <v/>
-      </c>
-      <c r="D23" s="44">
-        <f>MIN('Inputs'!$C$17*'Inputs'!$C$14,D21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Our proceeds = MAX(pref, as-converted)</t>
-        </is>
-      </c>
-      <c r="B24" s="47">
-        <f>MAX(B23,B22)</f>
-        <v/>
-      </c>
-      <c r="C24" s="47">
-        <f>MAX(C23,C22)</f>
-        <v/>
-      </c>
-      <c r="D24" s="47">
-        <f>MAX(D23,D22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>MOIC = our proceeds ÷ our investment</t>
-        </is>
-      </c>
-      <c r="B25" s="54">
-        <f>IFERROR(B24/'Inputs'!$C$14,0)</f>
-        <v/>
-      </c>
-      <c r="C25" s="54">
-        <f>IFERROR(C24/'Inputs'!$C$14,0)</f>
-        <v/>
-      </c>
-      <c r="D25" s="54">
-        <f>IFERROR(D24/'Inputs'!$C$14,0)</f>
+      <c r="B25" s="44">
+        <f>MIN('Inputs'!$C$17*'Inputs'!$C$14,B23)</f>
+        <v/>
+      </c>
+      <c r="C25" s="44">
+        <f>MIN('Inputs'!$C$17*'Inputs'!$C$14,C23)</f>
+        <v/>
+      </c>
+      <c r="D25" s="44">
+        <f>MIN('Inputs'!$C$17*'Inputs'!$C$14,D23)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>Terminal proceeds = MAX(pref, as-converted)</t>
+        </is>
+      </c>
+      <c r="B26" s="47">
+        <f>MAX(B25,B24)</f>
+        <v/>
+      </c>
+      <c r="C26" s="47">
+        <f>MAX(C25,C24)</f>
+        <v/>
+      </c>
+      <c r="D26" s="47">
+        <f>MAX(D25,D24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Interim distributions (diluted×dist×realised)</t>
+        </is>
+      </c>
+      <c r="B27" s="44">
+        <f>'Returns'!$B$8*'Inputs'!$C$49*MAX(0,B20)</f>
+        <v/>
+      </c>
+      <c r="C27" s="44">
+        <f>'Returns'!$B$8*'Inputs'!$C$49*MAX(0,C20)</f>
+        <v/>
+      </c>
+      <c r="D27" s="44">
+        <f>'Returns'!$B$8*'Inputs'!$C$49*MAX(0,D20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Our total proceeds = terminal + interim</t>
+        </is>
+      </c>
+      <c r="B28" s="47">
+        <f>B26+B27</f>
+        <v/>
+      </c>
+      <c r="C28" s="47">
+        <f>C26+C27</f>
+        <v/>
+      </c>
+      <c r="D28" s="47">
+        <f>D26+D27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>MOIC = our proceeds ÷ our investment</t>
+        </is>
+      </c>
+      <c r="B29" s="54">
+        <f>IFERROR(B28/'Inputs'!$C$14,0)</f>
+        <v/>
+      </c>
+      <c r="C29" s="54">
+        <f>IFERROR(C28/'Inputs'!$C$14,0)</f>
+        <v/>
+      </c>
+      <c r="D29" s="54">
+        <f>IFERROR(D28/'Inputs'!$C$14,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
           <t>Equity IRR = MOIC^(1/exit yr) − 1</t>
         </is>
       </c>
-      <c r="B26" s="18">
-        <f>IFERROR(B25^(1/'Inputs'!$C$19)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="C26" s="18">
-        <f>IFERROR(C25^(1/'Inputs'!$C$19)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="D26" s="18">
-        <f>IFERROR(D25^(1/'Inputs'!$C$19)-1,-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="B30" s="18">
+        <f>IFERROR(B29^(1/'Inputs'!$C$18)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="C30" s="18">
+        <f>IFERROR(C29^(1/'Inputs'!$C$18)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="D30" s="18">
+        <f>IFERROR(D29^(1/'Inputs'!$C$18)-1,-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>First-Chicago probability-weighted expected return</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr"/>
-      <c r="B29" s="8" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr"/>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>Ideal</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>Expected</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
-      <c r="B30" s="55">
+      <c r="B34" s="55">
         <f>'Scenarios'!$B$13</f>
         <v/>
       </c>
-      <c r="C30" s="55">
+      <c r="C34" s="55">
         <f>'Scenarios'!$C$13</f>
         <v/>
       </c>
-      <c r="D30" s="55">
+      <c r="D34" s="55">
         <f>'Scenarios'!$D$13</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Our proceeds</t>
         </is>
       </c>
-      <c r="B31" s="56">
-        <f>'Returns'!$B$24</f>
-        <v/>
-      </c>
-      <c r="C31" s="56">
-        <f>'Returns'!$C$24</f>
-        <v/>
-      </c>
-      <c r="D31" s="56">
-        <f>'Returns'!$D$24</f>
-        <v/>
-      </c>
-      <c r="E31" s="47">
-        <f>SUMPRODUCT('Scenarios'!$B$13:$D$13,B31:D31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="B35" s="56">
+        <f>'Returns'!$B$28</f>
+        <v/>
+      </c>
+      <c r="C35" s="56">
+        <f>'Returns'!$C$28</f>
+        <v/>
+      </c>
+      <c r="D35" s="56">
+        <f>'Returns'!$D$28</f>
+        <v/>
+      </c>
+      <c r="E35" s="47">
+        <f>SUMPRODUCT('Scenarios'!$B$13:$D$13,B35:D35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Expected MOIC = exp proceeds ÷ investment</t>
         </is>
       </c>
-      <c r="E32" s="54">
-        <f>IFERROR(E31/'Inputs'!$C$14,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="E36" s="54">
+        <f>IFERROR(E35/'Inputs'!$C$14,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Expected equity IRR = exp MOIC^(1/exit yr) − 1</t>
         </is>
       </c>
-      <c r="E33" s="37">
-        <f>IFERROR(E32^(1/'Inputs'!$C$19)-1,-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="E37" s="37">
+        <f>IFERROR(E36^(1/'Inputs'!$C$18)-1,-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Valuation range (per-pipeline asset value — cross-check)</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>Representative 6-project pipeline (asset-level), NOT the company's whole exit equity value.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>rNPV pipeline (Base)</t>
         </is>
       </c>
-      <c r="C36" s="56">
+      <c r="C40" s="56">
         <f>'Calc_Project_rNPV'!$M$10</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>$/MW benchmark (dev value)</t>
         </is>
       </c>
-      <c r="C37" s="56">
+      <c r="C41" s="56">
         <f>'Calc_CrossChecks'!$C$9</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>VC method (today value)</t>
         </is>
       </c>
-      <c r="C38" s="56">
+      <c r="C42" s="56">
         <f>'Calc_CrossChecks'!$C$18</f>
         <v/>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="C39" s="47">
-        <f>MIN(C36:C38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="C43" s="47">
+        <f>MIN(C40:C42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Midpoint</t>
         </is>
       </c>
-      <c r="C40" s="48">
-        <f>AVERAGE(C36:C38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="C44" s="48">
+        <f>AVERAGE(C40:C42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="C41" s="47">
-        <f>MAX(C36:C38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="C45" s="47">
+        <f>MAX(C40:C42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>Full cap table — who owns what (mechanical; ties to 100%)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>Holder</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>At entry %</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>At exit (diluted) %</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
         <is>
           <t>Founders / existing holders</t>
         </is>
       </c>
-      <c r="B45" s="36">
+      <c r="B49" s="36">
         <f>1-'Returns'!$B$7</f>
         <v/>
       </c>
-      <c r="C45" s="36">
+      <c r="C49" s="36">
         <f>(1-'Returns'!$B$7)*(1-'Inputs'!$C$15)*(1-'Inputs'!$C$16)</f>
         <v/>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Us (new investor)</t>
         </is>
       </c>
-      <c r="B46" s="35">
+      <c r="B50" s="35">
         <f>'Returns'!$B$7</f>
         <v/>
       </c>
-      <c r="C46" s="57">
+      <c r="C50" s="57">
         <f>'Returns'!$B$8</f>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>Option pool (staff)</t>
         </is>
       </c>
-      <c r="B47" s="36" t="n">
+      <c r="B51" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="C47" s="36">
+      <c r="C51" s="36">
         <f>'Inputs'!$C$15*(1-'Inputs'!$C$16)</f>
         <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>Future-round investors</t>
-        </is>
-      </c>
-      <c r="B48" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C48" s="35">
-        <f>'Inputs'!$C$16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Total (must = 100%)</t>
-        </is>
-      </c>
-      <c r="B49" s="18">
-        <f>SUM(B45:B48)</f>
-        <v/>
-      </c>
-      <c r="C49" s="18">
-        <f>SUM(C45:C48)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Exit waterfall (Base) — full distribution of exit equity</t>
-        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="15" t="inlineStr">
         <is>
-          <t>Company exit equity (Base)</t>
-        </is>
-      </c>
-      <c r="C52" s="56">
-        <f>'Returns'!$C$21</f>
+          <t>Future-round investors</t>
+        </is>
+      </c>
+      <c r="B52" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="35">
+        <f>'Inputs'!$C$16</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Our proceeds (1x pref / as-converted)</t>
-        </is>
-      </c>
-      <c r="C53" s="56">
-        <f>'Returns'!$C$24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="15" t="inlineStr">
+          <t>Total (must = 100%)</t>
+        </is>
+      </c>
+      <c r="B53" s="18">
+        <f>SUM(B49:B52)</f>
+        <v/>
+      </c>
+      <c r="C53" s="18">
+        <f>SUM(C49:C52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Exit waterfall (Base) — full distribution of exit equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>Company exit equity (Base)</t>
+        </is>
+      </c>
+      <c r="C56" s="56">
+        <f>'Returns'!$C$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Our terminal proceeds (1x pref / as-converted)</t>
+        </is>
+      </c>
+      <c r="C57" s="56">
+        <f>'Returns'!$C$26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
         <is>
           <t>Other holders' proceeds (residual)</t>
         </is>
       </c>
-      <c r="C54" s="44">
-        <f>C52-C53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="C58" s="44">
+        <f>C56-C57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>Distributed (ours + others = exit equity)</t>
         </is>
       </c>
-      <c r="C55" s="47">
-        <f>C53+C54</f>
+      <c r="C59" s="47">
+        <f>C57+C58</f>
         <v/>
       </c>
     </row>
@@ -1717,7 +1806,7 @@
           <t>Total pipeline MW</t>
         </is>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="26">
         <f>SUM('Calc_Project_rNPV'!$C$4:$C$9)</f>
         <v/>
       </c>
@@ -1969,32 +2058,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
     <col width="3" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="3" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SENSITIVITY — OUR equity IRR: development approval × RTB price</t>
+          <t>SENSITIVITY — OUR equity IRR: development approval × RTB price (forward-pipeline exit basis)</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
@@ -2006,7 +2100,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Return on OUR shares (equity IRR = MOIC^(1/exit year) − 1) vs DEVELOPMENT-APPROVAL rate (down) × RTB price multiplier (across); all else at Base. Flip success = DA × grid connection × sale, so the funnel widens with the FULL gate chain. Each scenario flows through the company exit equity value, dilution and the 1× liquidation preference. Helper columns H–J (per DA) and the proceeds grid M–Q keep every formula short. AUD $m / %.</t>
+          <t>Return on OUR shares (equity IRR = MOIC^(1/exit year) − 1) vs DEVELOPMENT-APPROVAL rate (down) × RTB price multiplier (across); all else at Base. Exit equity now uses the PRIMARY forward-pipeline basis: forward rNPV (depth × per-project) + retained cash − debt; our proceeds = the GREATER of the 1× liquidation preference or our as-converted share. Helper columns H–J (per DA), the exit-equity grid L–P and the proceeds grid R–V keep every formula short. The exit assumption (pipeline depth × discount) is profiled separately in IC_MEMO Exhibit D. AUD $m / %.</t>
         </is>
       </c>
     </row>
@@ -2035,11 +2129,11 @@
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>Platform exit multiple</t>
-        </is>
-      </c>
-      <c r="B6" s="43">
-        <f>'Inputs'!$C$18</f>
+          <t>Pipeline depth at exit</t>
+        </is>
+      </c>
+      <c r="B6" s="40">
+        <f>'Inputs'!$C$48</f>
         <v/>
       </c>
     </row>
@@ -2072,448 +2166,593 @@
         </is>
       </c>
       <c r="B9" s="40">
-        <f>'Inputs'!$C$19</f>
+        <f>'Inputs'!$C$18</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="59" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Base blended sale/project $m</t>
+        </is>
+      </c>
+      <c r="B10" s="56">
+        <f>'Calc_Project_rNPV'!$M$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Dev cost/project $m</t>
+        </is>
+      </c>
+      <c r="B11" s="56">
+        <f>'Inputs'!$C$21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Disc factor @ base over avg years</t>
+        </is>
+      </c>
+      <c r="B12" s="59">
+        <f>'Calc_Company'!$C$18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Retain fraction (1 − dist)</t>
+        </is>
+      </c>
+      <c r="B13" s="36">
+        <f>1-'Inputs'!$C$49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Debt at exit $m</t>
+        </is>
+      </c>
+      <c r="B14" s="56">
+        <f>'Inputs'!$C$50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>Price mult →</t>
         </is>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C17" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="D10" s="32" t="n">
+      <c r="D17" s="32" t="n">
         <v>0.85</v>
       </c>
-      <c r="E10" s="32" t="n">
+      <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="32" t="n">
+      <c r="F17" s="32" t="n">
         <v>1.15</v>
       </c>
-      <c r="G10" s="32" t="n">
+      <c r="G17" s="32" t="n">
         <v>1.3</v>
       </c>
-      <c r="M10" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N10" s="32" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="O10" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" s="32" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Q10" s="32" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="59" t="inlineStr">
+    </row>
+    <row r="18">
+      <c r="B18" s="60" t="inlineStr">
         <is>
           <t>Gross $m →</t>
         </is>
       </c>
-      <c r="C11" s="60">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*C10</f>
-        <v/>
-      </c>
-      <c r="D11" s="60">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*D10</f>
-        <v/>
-      </c>
-      <c r="E11" s="60">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*E10</f>
-        <v/>
-      </c>
-      <c r="F11" s="60">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*F10</f>
-        <v/>
-      </c>
-      <c r="G11" s="60">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*G10</f>
-        <v/>
-      </c>
-      <c r="M11" s="60">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*M10</f>
-        <v/>
-      </c>
-      <c r="N11" s="60">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*N10</f>
-        <v/>
-      </c>
-      <c r="O11" s="60">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*O10</f>
-        <v/>
-      </c>
-      <c r="P11" s="60">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*P10</f>
-        <v/>
-      </c>
-      <c r="Q11" s="60">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*Q10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="61" t="inlineStr">
+      <c r="C18" s="61">
+        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="61">
+        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="61">
+        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="61">
+        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="61">
+        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*G17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="62" t="inlineStr">
         <is>
           <t>DA gate ↓</t>
         </is>
       </c>
-      <c r="C12" s="61" t="inlineStr">
+      <c r="C19" s="62" t="inlineStr">
         <is>
           <t>IRR</t>
         </is>
       </c>
-      <c r="D12" s="61" t="inlineStr">
+      <c r="D19" s="62" t="inlineStr">
         <is>
           <t>IRR</t>
         </is>
       </c>
-      <c r="E12" s="61" t="inlineStr">
+      <c r="E19" s="62" t="inlineStr">
         <is>
           <t>IRR</t>
         </is>
       </c>
-      <c r="F12" s="61" t="inlineStr">
+      <c r="F19" s="62" t="inlineStr">
         <is>
           <t>IRR</t>
         </is>
       </c>
-      <c r="G12" s="61" t="inlineStr">
+      <c r="G19" s="62" t="inlineStr">
         <is>
           <t>IRR</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>Flip succ</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>Started</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>Total dev</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>Exit eq</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>Exit eq</t>
+        </is>
+      </c>
+      <c r="N19" s="8" t="inlineStr">
+        <is>
+          <t>Exit eq</t>
+        </is>
+      </c>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>Exit eq</t>
+        </is>
+      </c>
+      <c r="P19" s="8" t="inlineStr">
+        <is>
+          <t>Exit eq</t>
+        </is>
+      </c>
+      <c r="R19" s="8" t="inlineStr">
         <is>
           <t>Proceeds</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr">
+      <c r="S19" s="8" t="inlineStr">
         <is>
           <t>Proceeds</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>Proceeds</t>
         </is>
       </c>
-      <c r="P12" s="8" t="inlineStr">
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>Proceeds</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="V19" s="8" t="inlineStr">
         <is>
           <t>Proceeds</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="26" t="n">
+    <row r="20">
+      <c r="B20" s="25" t="n">
         <v>0.4</v>
       </c>
-      <c r="C13" s="36">
-        <f>IFERROR((M13/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="D13" s="36">
-        <f>IFERROR((N13/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="E13" s="36">
-        <f>IFERROR((O13/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="F13" s="36">
-        <f>IFERROR((P13/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="G13" s="36">
-        <f>IFERROR((Q13/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="H13" s="36">
-        <f>$B13*$B$4</f>
-        <v/>
-      </c>
-      <c r="I13" s="49">
-        <f>IFERROR('Inputs'!$C$10/H13,0)</f>
-        <v/>
-      </c>
-      <c r="J13" s="50">
-        <f>'Inputs'!$C$10*'Inputs'!$C$21+(I13-'Inputs'!$C$10)*'Inputs'!$C$22*'Inputs'!$C$21</f>
-        <v/>
-      </c>
-      <c r="M13" s="44">
-        <f>MAX(MIN($B$7,MAX(0,M$11-$J13)*$B$6),$B$5*MAX(0,M$11-$J13)*$B$6)</f>
-        <v/>
-      </c>
-      <c r="N13" s="44">
-        <f>MAX(MIN($B$7,MAX(0,N$11-$J13)*$B$6),$B$5*MAX(0,N$11-$J13)*$B$6)</f>
-        <v/>
-      </c>
-      <c r="O13" s="44">
-        <f>MAX(MIN($B$7,MAX(0,O$11-$J13)*$B$6),$B$5*MAX(0,O$11-$J13)*$B$6)</f>
-        <v/>
-      </c>
-      <c r="P13" s="44">
-        <f>MAX(MIN($B$7,MAX(0,P$11-$J13)*$B$6),$B$5*MAX(0,P$11-$J13)*$B$6)</f>
-        <v/>
-      </c>
-      <c r="Q13" s="44">
-        <f>MAX(MIN($B$7,MAX(0,Q$11-$J13)*$B$6),$B$5*MAX(0,Q$11-$J13)*$B$6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="26" t="n">
+      <c r="C20" s="36">
+        <f>IFERROR((R20/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="D20" s="36">
+        <f>IFERROR((S20/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="E20" s="36">
+        <f>IFERROR((T20/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="F20" s="36">
+        <f>IFERROR((U20/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="G20" s="36">
+        <f>IFERROR((V20/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="H20" s="36">
+        <f>$B20*$B$4</f>
+        <v/>
+      </c>
+      <c r="I20" s="49">
+        <f>IFERROR('Inputs'!$C$10/H20,0)</f>
+        <v/>
+      </c>
+      <c r="J20" s="50">
+        <f>'Inputs'!$C$10*'Inputs'!$C$21+(I20-'Inputs'!$C$10)*'Inputs'!$C$22*'Inputs'!$C$21</f>
+        <v/>
+      </c>
+      <c r="L20" s="44">
+        <f>MAX(0,$B$6*($B$10*C$17-$B$11)*$H20*$B$12+MAX(0,C$18-$J20)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="M20" s="44">
+        <f>MAX(0,$B$6*($B$10*D$17-$B$11)*$H20*$B$12+MAX(0,D$18-$J20)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="N20" s="44">
+        <f>MAX(0,$B$6*($B$10*E$17-$B$11)*$H20*$B$12+MAX(0,E$18-$J20)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="O20" s="44">
+        <f>MAX(0,$B$6*($B$10*F$17-$B$11)*$H20*$B$12+MAX(0,F$18-$J20)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="P20" s="44">
+        <f>MAX(0,$B$6*($B$10*G$17-$B$11)*$H20*$B$12+MAX(0,G$18-$J20)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="R20" s="44">
+        <f>MAX(MIN($B$7,L20),$B$5*L20)</f>
+        <v/>
+      </c>
+      <c r="S20" s="44">
+        <f>MAX(MIN($B$7,M20),$B$5*M20)</f>
+        <v/>
+      </c>
+      <c r="T20" s="44">
+        <f>MAX(MIN($B$7,N20),$B$5*N20)</f>
+        <v/>
+      </c>
+      <c r="U20" s="44">
+        <f>MAX(MIN($B$7,O20),$B$5*O20)</f>
+        <v/>
+      </c>
+      <c r="V20" s="44">
+        <f>MAX(MIN($B$7,P20),$B$5*P20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="25" t="n">
         <v>0.55</v>
       </c>
-      <c r="C14" s="36">
-        <f>IFERROR((M14/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="D14" s="36">
-        <f>IFERROR((N14/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="E14" s="36">
-        <f>IFERROR((O14/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="F14" s="36">
-        <f>IFERROR((P14/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="G14" s="36">
-        <f>IFERROR((Q14/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="H14" s="36">
-        <f>$B14*$B$4</f>
-        <v/>
-      </c>
-      <c r="I14" s="49">
-        <f>IFERROR('Inputs'!$C$10/H14,0)</f>
-        <v/>
-      </c>
-      <c r="J14" s="50">
-        <f>'Inputs'!$C$10*'Inputs'!$C$21+(I14-'Inputs'!$C$10)*'Inputs'!$C$22*'Inputs'!$C$21</f>
-        <v/>
-      </c>
-      <c r="M14" s="44">
-        <f>MAX(MIN($B$7,MAX(0,M$11-$J14)*$B$6),$B$5*MAX(0,M$11-$J14)*$B$6)</f>
-        <v/>
-      </c>
-      <c r="N14" s="44">
-        <f>MAX(MIN($B$7,MAX(0,N$11-$J14)*$B$6),$B$5*MAX(0,N$11-$J14)*$B$6)</f>
-        <v/>
-      </c>
-      <c r="O14" s="44">
-        <f>MAX(MIN($B$7,MAX(0,O$11-$J14)*$B$6),$B$5*MAX(0,O$11-$J14)*$B$6)</f>
-        <v/>
-      </c>
-      <c r="P14" s="44">
-        <f>MAX(MIN($B$7,MAX(0,P$11-$J14)*$B$6),$B$5*MAX(0,P$11-$J14)*$B$6)</f>
-        <v/>
-      </c>
-      <c r="Q14" s="44">
-        <f>MAX(MIN($B$7,MAX(0,Q$11-$J14)*$B$6),$B$5*MAX(0,Q$11-$J14)*$B$6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="26" t="n">
+      <c r="C21" s="36">
+        <f>IFERROR((R21/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="D21" s="36">
+        <f>IFERROR((S21/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="E21" s="36">
+        <f>IFERROR((T21/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="F21" s="36">
+        <f>IFERROR((U21/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="G21" s="36">
+        <f>IFERROR((V21/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="H21" s="36">
+        <f>$B21*$B$4</f>
+        <v/>
+      </c>
+      <c r="I21" s="49">
+        <f>IFERROR('Inputs'!$C$10/H21,0)</f>
+        <v/>
+      </c>
+      <c r="J21" s="50">
+        <f>'Inputs'!$C$10*'Inputs'!$C$21+(I21-'Inputs'!$C$10)*'Inputs'!$C$22*'Inputs'!$C$21</f>
+        <v/>
+      </c>
+      <c r="L21" s="44">
+        <f>MAX(0,$B$6*($B$10*C$17-$B$11)*$H21*$B$12+MAX(0,C$18-$J21)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="M21" s="44">
+        <f>MAX(0,$B$6*($B$10*D$17-$B$11)*$H21*$B$12+MAX(0,D$18-$J21)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="N21" s="44">
+        <f>MAX(0,$B$6*($B$10*E$17-$B$11)*$H21*$B$12+MAX(0,E$18-$J21)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="O21" s="44">
+        <f>MAX(0,$B$6*($B$10*F$17-$B$11)*$H21*$B$12+MAX(0,F$18-$J21)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="P21" s="44">
+        <f>MAX(0,$B$6*($B$10*G$17-$B$11)*$H21*$B$12+MAX(0,G$18-$J21)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="R21" s="44">
+        <f>MAX(MIN($B$7,L21),$B$5*L21)</f>
+        <v/>
+      </c>
+      <c r="S21" s="44">
+        <f>MAX(MIN($B$7,M21),$B$5*M21)</f>
+        <v/>
+      </c>
+      <c r="T21" s="44">
+        <f>MAX(MIN($B$7,N21),$B$5*N21)</f>
+        <v/>
+      </c>
+      <c r="U21" s="44">
+        <f>MAX(MIN($B$7,O21),$B$5*O21)</f>
+        <v/>
+      </c>
+      <c r="V21" s="44">
+        <f>MAX(MIN($B$7,P21),$B$5*P21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="25" t="n">
         <v>0.65</v>
       </c>
-      <c r="C15" s="36">
-        <f>IFERROR((M15/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="D15" s="36">
-        <f>IFERROR((N15/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="E15" s="36">
-        <f>IFERROR((O15/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="F15" s="36">
-        <f>IFERROR((P15/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="G15" s="36">
-        <f>IFERROR((Q15/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="H15" s="36">
-        <f>$B15*$B$4</f>
-        <v/>
-      </c>
-      <c r="I15" s="49">
-        <f>IFERROR('Inputs'!$C$10/H15,0)</f>
-        <v/>
-      </c>
-      <c r="J15" s="50">
-        <f>'Inputs'!$C$10*'Inputs'!$C$21+(I15-'Inputs'!$C$10)*'Inputs'!$C$22*'Inputs'!$C$21</f>
-        <v/>
-      </c>
-      <c r="M15" s="44">
-        <f>MAX(MIN($B$7,MAX(0,M$11-$J15)*$B$6),$B$5*MAX(0,M$11-$J15)*$B$6)</f>
-        <v/>
-      </c>
-      <c r="N15" s="44">
-        <f>MAX(MIN($B$7,MAX(0,N$11-$J15)*$B$6),$B$5*MAX(0,N$11-$J15)*$B$6)</f>
-        <v/>
-      </c>
-      <c r="O15" s="44">
-        <f>MAX(MIN($B$7,MAX(0,O$11-$J15)*$B$6),$B$5*MAX(0,O$11-$J15)*$B$6)</f>
-        <v/>
-      </c>
-      <c r="P15" s="44">
-        <f>MAX(MIN($B$7,MAX(0,P$11-$J15)*$B$6),$B$5*MAX(0,P$11-$J15)*$B$6)</f>
-        <v/>
-      </c>
-      <c r="Q15" s="44">
-        <f>MAX(MIN($B$7,MAX(0,Q$11-$J15)*$B$6),$B$5*MAX(0,Q$11-$J15)*$B$6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="26" t="n">
+      <c r="C22" s="36">
+        <f>IFERROR((R22/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="D22" s="36">
+        <f>IFERROR((S22/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="E22" s="36">
+        <f>IFERROR((T22/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="F22" s="36">
+        <f>IFERROR((U22/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="G22" s="36">
+        <f>IFERROR((V22/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="H22" s="36">
+        <f>$B22*$B$4</f>
+        <v/>
+      </c>
+      <c r="I22" s="49">
+        <f>IFERROR('Inputs'!$C$10/H22,0)</f>
+        <v/>
+      </c>
+      <c r="J22" s="50">
+        <f>'Inputs'!$C$10*'Inputs'!$C$21+(I22-'Inputs'!$C$10)*'Inputs'!$C$22*'Inputs'!$C$21</f>
+        <v/>
+      </c>
+      <c r="L22" s="44">
+        <f>MAX(0,$B$6*($B$10*C$17-$B$11)*$H22*$B$12+MAX(0,C$18-$J22)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="M22" s="44">
+        <f>MAX(0,$B$6*($B$10*D$17-$B$11)*$H22*$B$12+MAX(0,D$18-$J22)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="N22" s="44">
+        <f>MAX(0,$B$6*($B$10*E$17-$B$11)*$H22*$B$12+MAX(0,E$18-$J22)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="O22" s="44">
+        <f>MAX(0,$B$6*($B$10*F$17-$B$11)*$H22*$B$12+MAX(0,F$18-$J22)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="P22" s="44">
+        <f>MAX(0,$B$6*($B$10*G$17-$B$11)*$H22*$B$12+MAX(0,G$18-$J22)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="R22" s="44">
+        <f>MAX(MIN($B$7,L22),$B$5*L22)</f>
+        <v/>
+      </c>
+      <c r="S22" s="44">
+        <f>MAX(MIN($B$7,M22),$B$5*M22)</f>
+        <v/>
+      </c>
+      <c r="T22" s="44">
+        <f>MAX(MIN($B$7,N22),$B$5*N22)</f>
+        <v/>
+      </c>
+      <c r="U22" s="44">
+        <f>MAX(MIN($B$7,O22),$B$5*O22)</f>
+        <v/>
+      </c>
+      <c r="V22" s="44">
+        <f>MAX(MIN($B$7,P22),$B$5*P22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="25" t="n">
         <v>0.8</v>
       </c>
-      <c r="C16" s="36">
-        <f>IFERROR((M16/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="D16" s="36">
-        <f>IFERROR((N16/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="E16" s="36">
-        <f>IFERROR((O16/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="F16" s="36">
-        <f>IFERROR((P16/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="G16" s="36">
-        <f>IFERROR((Q16/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="H16" s="36">
-        <f>$B16*$B$4</f>
-        <v/>
-      </c>
-      <c r="I16" s="49">
-        <f>IFERROR('Inputs'!$C$10/H16,0)</f>
-        <v/>
-      </c>
-      <c r="J16" s="50">
-        <f>'Inputs'!$C$10*'Inputs'!$C$21+(I16-'Inputs'!$C$10)*'Inputs'!$C$22*'Inputs'!$C$21</f>
-        <v/>
-      </c>
-      <c r="M16" s="44">
-        <f>MAX(MIN($B$7,MAX(0,M$11-$J16)*$B$6),$B$5*MAX(0,M$11-$J16)*$B$6)</f>
-        <v/>
-      </c>
-      <c r="N16" s="44">
-        <f>MAX(MIN($B$7,MAX(0,N$11-$J16)*$B$6),$B$5*MAX(0,N$11-$J16)*$B$6)</f>
-        <v/>
-      </c>
-      <c r="O16" s="44">
-        <f>MAX(MIN($B$7,MAX(0,O$11-$J16)*$B$6),$B$5*MAX(0,O$11-$J16)*$B$6)</f>
-        <v/>
-      </c>
-      <c r="P16" s="44">
-        <f>MAX(MIN($B$7,MAX(0,P$11-$J16)*$B$6),$B$5*MAX(0,P$11-$J16)*$B$6)</f>
-        <v/>
-      </c>
-      <c r="Q16" s="44">
-        <f>MAX(MIN($B$7,MAX(0,Q$11-$J16)*$B$6),$B$5*MAX(0,Q$11-$J16)*$B$6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="26" t="n">
+      <c r="C23" s="36">
+        <f>IFERROR((R23/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="D23" s="36">
+        <f>IFERROR((S23/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="E23" s="36">
+        <f>IFERROR((T23/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="F23" s="36">
+        <f>IFERROR((U23/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="G23" s="36">
+        <f>IFERROR((V23/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="H23" s="36">
+        <f>$B23*$B$4</f>
+        <v/>
+      </c>
+      <c r="I23" s="49">
+        <f>IFERROR('Inputs'!$C$10/H23,0)</f>
+        <v/>
+      </c>
+      <c r="J23" s="50">
+        <f>'Inputs'!$C$10*'Inputs'!$C$21+(I23-'Inputs'!$C$10)*'Inputs'!$C$22*'Inputs'!$C$21</f>
+        <v/>
+      </c>
+      <c r="L23" s="44">
+        <f>MAX(0,$B$6*($B$10*C$17-$B$11)*$H23*$B$12+MAX(0,C$18-$J23)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="M23" s="44">
+        <f>MAX(0,$B$6*($B$10*D$17-$B$11)*$H23*$B$12+MAX(0,D$18-$J23)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="N23" s="44">
+        <f>MAX(0,$B$6*($B$10*E$17-$B$11)*$H23*$B$12+MAX(0,E$18-$J23)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="O23" s="44">
+        <f>MAX(0,$B$6*($B$10*F$17-$B$11)*$H23*$B$12+MAX(0,F$18-$J23)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="P23" s="44">
+        <f>MAX(0,$B$6*($B$10*G$17-$B$11)*$H23*$B$12+MAX(0,G$18-$J23)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="R23" s="44">
+        <f>MAX(MIN($B$7,L23),$B$5*L23)</f>
+        <v/>
+      </c>
+      <c r="S23" s="44">
+        <f>MAX(MIN($B$7,M23),$B$5*M23)</f>
+        <v/>
+      </c>
+      <c r="T23" s="44">
+        <f>MAX(MIN($B$7,N23),$B$5*N23)</f>
+        <v/>
+      </c>
+      <c r="U23" s="44">
+        <f>MAX(MIN($B$7,O23),$B$5*O23)</f>
+        <v/>
+      </c>
+      <c r="V23" s="44">
+        <f>MAX(MIN($B$7,P23),$B$5*P23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="25" t="n">
         <v>0.95</v>
       </c>
-      <c r="C17" s="36">
-        <f>IFERROR((M17/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="D17" s="36">
-        <f>IFERROR((N17/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="E17" s="36">
-        <f>IFERROR((O17/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="F17" s="36">
-        <f>IFERROR((P17/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="G17" s="36">
-        <f>IFERROR((Q17/$B$8)^(1/$B$9)-1,-1)</f>
-        <v/>
-      </c>
-      <c r="H17" s="36">
-        <f>$B17*$B$4</f>
-        <v/>
-      </c>
-      <c r="I17" s="49">
-        <f>IFERROR('Inputs'!$C$10/H17,0)</f>
-        <v/>
-      </c>
-      <c r="J17" s="50">
-        <f>'Inputs'!$C$10*'Inputs'!$C$21+(I17-'Inputs'!$C$10)*'Inputs'!$C$22*'Inputs'!$C$21</f>
-        <v/>
-      </c>
-      <c r="M17" s="44">
-        <f>MAX(MIN($B$7,MAX(0,M$11-$J17)*$B$6),$B$5*MAX(0,M$11-$J17)*$B$6)</f>
-        <v/>
-      </c>
-      <c r="N17" s="44">
-        <f>MAX(MIN($B$7,MAX(0,N$11-$J17)*$B$6),$B$5*MAX(0,N$11-$J17)*$B$6)</f>
-        <v/>
-      </c>
-      <c r="O17" s="44">
-        <f>MAX(MIN($B$7,MAX(0,O$11-$J17)*$B$6),$B$5*MAX(0,O$11-$J17)*$B$6)</f>
-        <v/>
-      </c>
-      <c r="P17" s="44">
-        <f>MAX(MIN($B$7,MAX(0,P$11-$J17)*$B$6),$B$5*MAX(0,P$11-$J17)*$B$6)</f>
-        <v/>
-      </c>
-      <c r="Q17" s="44">
-        <f>MAX(MIN($B$7,MAX(0,Q$11-$J17)*$B$6),$B$5*MAX(0,Q$11-$J17)*$B$6)</f>
+      <c r="C24" s="36">
+        <f>IFERROR((R24/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="D24" s="36">
+        <f>IFERROR((S24/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="E24" s="36">
+        <f>IFERROR((T24/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="F24" s="36">
+        <f>IFERROR((U24/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="G24" s="36">
+        <f>IFERROR((V24/$B$8)^(1/$B$9)-1,-1)</f>
+        <v/>
+      </c>
+      <c r="H24" s="36">
+        <f>$B24*$B$4</f>
+        <v/>
+      </c>
+      <c r="I24" s="49">
+        <f>IFERROR('Inputs'!$C$10/H24,0)</f>
+        <v/>
+      </c>
+      <c r="J24" s="50">
+        <f>'Inputs'!$C$10*'Inputs'!$C$21+(I24-'Inputs'!$C$10)*'Inputs'!$C$22*'Inputs'!$C$21</f>
+        <v/>
+      </c>
+      <c r="L24" s="44">
+        <f>MAX(0,$B$6*($B$10*C$17-$B$11)*$H24*$B$12+MAX(0,C$18-$J24)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="M24" s="44">
+        <f>MAX(0,$B$6*($B$10*D$17-$B$11)*$H24*$B$12+MAX(0,D$18-$J24)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="N24" s="44">
+        <f>MAX(0,$B$6*($B$10*E$17-$B$11)*$H24*$B$12+MAX(0,E$18-$J24)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="O24" s="44">
+        <f>MAX(0,$B$6*($B$10*F$17-$B$11)*$H24*$B$12+MAX(0,F$18-$J24)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="P24" s="44">
+        <f>MAX(0,$B$6*($B$10*G$17-$B$11)*$H24*$B$12+MAX(0,G$18-$J24)*$B$13-$B$14)</f>
+        <v/>
+      </c>
+      <c r="R24" s="44">
+        <f>MAX(MIN($B$7,L24),$B$5*L24)</f>
+        <v/>
+      </c>
+      <c r="S24" s="44">
+        <f>MAX(MIN($B$7,M24),$B$5*M24)</f>
+        <v/>
+      </c>
+      <c r="T24" s="44">
+        <f>MAX(MIN($B$7,N24),$B$5*N24)</f>
+        <v/>
+      </c>
+      <c r="U24" s="44">
+        <f>MAX(MIN($B$7,O24),$B$5*O24)</f>
+        <v/>
+      </c>
+      <c r="V24" s="44">
+        <f>MAX(MIN($B$7,P24),$B$5*P24)</f>
         <v/>
       </c>
     </row>
@@ -2532,7 +2771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -2740,7 +2979,7 @@
         </is>
       </c>
       <c r="B14" s="38">
-        <f>IF(AND('Returns'!$B$25&lt;='Returns'!$C$25,'Returns'!$C$25&lt;='Returns'!$D$25),"OK","ERROR")</f>
+        <f>IF(AND('Returns'!$B$29&lt;='Returns'!$C$29,'Returns'!$C$29&lt;='Returns'!$D$29),"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -2780,16 +3019,16 @@
           <t>Weighting sanity (helpers E:G)</t>
         </is>
       </c>
-      <c r="E16" s="62">
-        <f>MIN('Returns'!$B$26:$D$26)</f>
-        <v/>
-      </c>
-      <c r="F16" s="62">
-        <f>MAX('Returns'!$B$26:$D$26)</f>
+      <c r="E16" s="63">
+        <f>MIN('Returns'!$B$30:$D$30)</f>
+        <v/>
+      </c>
+      <c r="F16" s="63">
+        <f>MAX('Returns'!$B$30:$D$30)</f>
         <v/>
       </c>
       <c r="G16" s="55">
-        <f>'Returns'!$E$33</f>
+        <f>'Returns'!$E$37</f>
         <v/>
       </c>
     </row>
@@ -2800,7 +3039,7 @@
         </is>
       </c>
       <c r="B17" s="38">
-        <f>IF(MIN('Returns'!$B$24:$D$24)&gt;=0,"OK","ERROR")</f>
+        <f>IF(MIN('Returns'!$B$28:$D$28)&gt;=0,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -2829,11 +3068,11 @@
         <v/>
       </c>
       <c r="F18" s="38">
-        <f>SUMPRODUCT(--ISERROR('Returns'!$B$26:$D$26))</f>
+        <f>SUMPRODUCT(--ISERROR('Returns'!$B$30:$D$30))</f>
         <v/>
       </c>
       <c r="G18" s="38">
-        <f>SUMPRODUCT(--ISERROR('Sensitivity'!$C$13:$G$17))</f>
+        <f>SUMPRODUCT(--ISERROR('Sensitivity'!$C$20:$G$24))</f>
         <v/>
       </c>
     </row>
@@ -2844,7 +3083,7 @@
         </is>
       </c>
       <c r="B19" s="38">
-        <f>IF(AND(ABS('Returns'!$B$49-1)&lt;0.001,ABS('Returns'!$C$49-1)&lt;0.001),"OK","ERROR")</f>
+        <f>IF(AND(ABS('Returns'!$B$53-1)&lt;0.001,ABS('Returns'!$C$53-1)&lt;0.001),"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -2860,7 +3099,7 @@
         </is>
       </c>
       <c r="B20" s="38">
-        <f>IF(ABS('Returns'!$C$55-'Returns'!$C$52)&lt;0.001,"OK","ERROR")</f>
+        <f>IF(ABS('Returns'!$C$59-'Returns'!$C$56)&lt;0.001,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -2869,19 +3108,35 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>No double-count (exit value ≤ realised + forward pipeline)</t>
+        </is>
+      </c>
+      <c r="B21" s="38">
+        <f>IF('Returns'!$C$23&lt;='Returns'!$C$21+'Returns'!$C$22+0.000001,"OK","ERROR")</f>
+        <v/>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Retained-cash-only guard</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>MASTER CHECK</t>
         </is>
       </c>
-      <c r="B22" s="63">
-        <f>IF(COUNTIF(B4:B20,"ERROR")=0,"OK","ERROR")</f>
+      <c r="B23" s="64">
+        <f>IF(COUNTIF(B4:B21,"ERROR")=0,"OK","ERROR")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:B22">
+  <conditionalFormatting sqref="B4:B23">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -2947,8 +3202,8 @@
           <t>Master check</t>
         </is>
       </c>
-      <c r="E4" s="64">
-        <f>'Checks'!$B$22</f>
+      <c r="E4" s="65">
+        <f>'Checks'!$B$23</f>
         <v/>
       </c>
     </row>
@@ -2971,7 +3226,7 @@
         </is>
       </c>
       <c r="B7" s="34">
-        <f>'Returns'!$E$33</f>
+        <f>'Returns'!$E$37</f>
         <v/>
       </c>
       <c r="D7" s="15" t="inlineStr">
@@ -2979,7 +3234,7 @@
           <t>Post-money valuation $m</t>
         </is>
       </c>
-      <c r="E7" s="52">
+      <c r="E7" s="51">
         <f>'Returns'!$B$6</f>
         <v/>
       </c>
@@ -2990,8 +3245,8 @@
           <t>Expected MOIC</t>
         </is>
       </c>
-      <c r="B8" s="65">
-        <f>'Returns'!$E$32</f>
+      <c r="B8" s="66">
+        <f>'Returns'!$E$36</f>
         <v/>
       </c>
       <c r="D8" s="15" t="inlineStr">
@@ -3021,7 +3276,7 @@
           <t>Liquidation preference (x)</t>
         </is>
       </c>
-      <c r="E10" s="65">
+      <c r="E10" s="66">
         <f>'Inputs'!$C$17</f>
         <v/>
       </c>
@@ -3033,7 +3288,7 @@
         </is>
       </c>
       <c r="E11" s="40">
-        <f>'Inputs'!$C$19</f>
+        <f>'Inputs'!$C$18</f>
         <v/>
       </c>
     </row>
@@ -3065,12 +3320,12 @@
           <t>Equity IRR</t>
         </is>
       </c>
-      <c r="D14" s="66" t="inlineStr">
+      <c r="D14" s="67" t="inlineStr">
         <is>
           <t>Programme capital $m</t>
         </is>
       </c>
-      <c r="E14" s="52">
+      <c r="E14" s="51">
         <f>'Inputs'!$C$9</f>
         <v/>
       </c>
@@ -3086,10 +3341,10 @@
         <v/>
       </c>
       <c r="C15" s="35">
-        <f>'Returns'!$B$26</f>
-        <v/>
-      </c>
-      <c r="D15" s="67" t="inlineStr">
+        <f>'Returns'!$B$30</f>
+        <v/>
+      </c>
+      <c r="D15" s="68" t="inlineStr">
         <is>
           <t>Projects target</t>
         </is>
@@ -3110,10 +3365,10 @@
         <v/>
       </c>
       <c r="C16" s="35">
-        <f>'Returns'!$C$26</f>
-        <v/>
-      </c>
-      <c r="D16" s="67" t="inlineStr">
+        <f>'Returns'!$C$30</f>
+        <v/>
+      </c>
+      <c r="D16" s="68" t="inlineStr">
         <is>
           <t>Manager headline DA gate (Base)</t>
         </is>
@@ -3134,10 +3389,10 @@
         <v/>
       </c>
       <c r="C17" s="35">
-        <f>'Returns'!$D$26</f>
-        <v/>
-      </c>
-      <c r="D17" s="67" t="inlineStr">
+        <f>'Returns'!$D$30</f>
+        <v/>
+      </c>
+      <c r="D17" s="68" t="inlineStr">
         <is>
           <t>True flip success (Base, DAxconnxsale)</t>
         </is>
@@ -3195,7 +3450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3464,106 +3719,142 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Net programme profit</t>
+          <t>Realised net programme profit</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>The company's gross RTB proceeds minus its total development cost across the programme.</t>
+          <t>The company's gross RTB proceeds minus its total development cost — profit EARNED by exit (feeds retained cash; counted once, at face value).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Pre-money / post-money</t>
+          <t>Forward pipeline rNPV</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Pre-money = the company's agreed value before our money goes in; post-money = pre-money + our investment.</t>
+          <t>The risk-adjusted value of projects still IN FLIGHT at exit (depth × per-project rNPV) — the PRIMARY exit equity, what a buyer of a development platform pays for.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Ownership %</t>
+          <t>Retained cash / run-rate</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Our share of the company = our investment ÷ post-money valuation.</t>
+          <t>Retained cash = realised profit not yet distributed (carried into the exit value). Run-rate = realised profit ÷ term — the yearly stream the earnings-multiple CROSS-CHECK is applied to.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Dilution</t>
+          <t>Exit equity (primary)</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>The fall in our ownership % when new shares are issued — here a staff option pool and future funding rounds.</t>
+          <t>Forward-pipeline rNPV + retained cash − debt at exit. The earnings multiple on run-rate profit is a CROSS-CHECK, not the headline.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Cap table</t>
+          <t>Pre-money / post-money</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>The schedule of who owns what % of the company; we run our stake through it to get our exit proceeds.</t>
+          <t>Pre-money = the company's agreed value before our money goes in; post-money = pre-money + our investment.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Liquidation preference</t>
+          <t>Ownership %</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>A preferred right to get our money back (1x) before ordinary holders at exit; 1x non-participating means we take the GREATER of that or our as-converted share.</t>
+          <t>Our share of the company = our investment ÷ post-money valuation.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>MOIC / equity IRR</t>
+          <t>Dilution</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Multiple on OUR investment; annualised return on our shares (MOIC^(1/exit year) − 1; a total loss is −100%).</t>
+          <t>The fall in our ownership % when new shares are issued — here a staff option pool and future funding rounds.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>First Chicago</t>
+          <t>Cap table</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Probability-weight the scenarios' proceeds into a single expected return on our shares.</t>
+          <t>The schedule of who owns what % of the company; we run our stake through it to get our exit proceeds.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
+          <t>Liquidation preference</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>A preferred right to get our money back (1x) before ordinary holders at exit; 1x non-participating means we take the GREATER of that or our as-converted share.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>MOIC / equity IRR</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>Multiple on OUR investment; annualised return on our shares (MOIC^(1/exit year) − 1; a total loss is −100%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>First Chicago</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>Probability-weight the scenarios' proceeds into a single expected return on our shares.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
           <t>Develop-and-flip</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>Develop, de-risk, then sell RTB — the margin is the value uplift; merchant risk passes to the buyer.</t>
         </is>
@@ -3747,7 +4038,7 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Company programme: funnel → net profit → company exit equity value (live)</t>
+          <t>Company programme: funnel → realised profit + forward-pipeline rNPV → exit equity value (+ earnings cross-check)</t>
         </is>
       </c>
     </row>
@@ -3870,7 +4161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3958,7 +4249,29 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="13" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>v3.0</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Fixed the exit-value basis (change2.md): PRIMARY exit equity is now FORWARD-PIPELINE rNPV (depth × per-project) + retained cash − debt, not net profit × a platform multiple. The earnings multiple is demoted to a CROSS-CHECK on FORWARD RUN-RATE profit (a sourced low/base/high range). Added pipeline depth / distribution-fraction / debt inputs; a retained-cash double-count guard; and the exit-value sensitivity (Exhibit D). Return = terminal proceeds + interim distributions (convention (b)).</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Claude Code (v3 exit-basis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>[Analyst review pass — record changes here]</t>
         </is>
@@ -3979,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4389,15 +4702,15 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Platform exit multiple (on net programme profit)</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="n">
-        <v>4</v>
+          <t>Exit year (we sell our shares)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>multiple</t>
+          <t>years</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
@@ -4416,36 +4729,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Exit year (we sell our shares)</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>Illustrative / the manager claim (see config)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>TO CONFIRM</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -4459,7 +4743,7 @@
           <t>Development cost per project</t>
         </is>
       </c>
-      <c r="C21" s="23" t="n">
+      <c r="C21" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="D21" s="15" t="inlineStr">
@@ -4526,7 +4810,7 @@
           <t>Built-asset cost (context)</t>
         </is>
       </c>
-      <c r="C24" s="24" t="n">
+      <c r="C24" s="23" t="n">
         <v>1.8</v>
       </c>
       <c r="D24" s="15" t="inlineStr">
@@ -4586,7 +4870,7 @@
           <t>BENCHMARK</t>
         </is>
       </c>
-      <c r="H26" s="25" t="n">
+      <c r="H26" s="24" t="n">
         <v>1.25</v>
       </c>
     </row>
@@ -4619,7 +4903,7 @@
           <t>BENCHMARK</t>
         </is>
       </c>
-      <c r="H27" s="25" t="n">
+      <c r="H27" s="24" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -4652,7 +4936,7 @@
           <t>BENCHMARK</t>
         </is>
       </c>
-      <c r="H28" s="25" t="n">
+      <c r="H28" s="24" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4669,7 +4953,7 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="C30" s="24" t="n">
+      <c r="C30" s="23" t="n">
         <v>0.2</v>
       </c>
       <c r="D30" s="15" t="inlineStr">
@@ -4699,7 +4983,7 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="C31" s="24" t="n">
+      <c r="C31" s="23" t="n">
         <v>0.18</v>
       </c>
       <c r="D31" s="15" t="inlineStr">
@@ -4729,7 +5013,7 @@
           <t>SA</t>
         </is>
       </c>
-      <c r="C32" s="24" t="n">
+      <c r="C32" s="23" t="n">
         <v>0.12</v>
       </c>
       <c r="D32" s="15" t="inlineStr">
@@ -4803,16 +5087,16 @@
           <t>Capital call profile</t>
         </is>
       </c>
-      <c r="C36" s="26" t="n">
+      <c r="C36" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="D36" s="26" t="n">
+      <c r="D36" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="E36" s="26" t="n">
+      <c r="E36" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F36" s="26" t="n">
+      <c r="F36" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4822,16 +5106,16 @@
           <t>Distribution profile</t>
         </is>
       </c>
-      <c r="C37" s="26" t="n">
+      <c r="C37" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D37" s="26" t="n">
+      <c r="D37" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="26" t="n">
+      <c r="E37" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="F37" s="26" t="n">
+      <c r="F37" s="25" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4898,14 +5182,14 @@
       <c r="D40" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="E40" s="25" t="n">
+      <c r="E40" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="F40" s="27">
+      <c r="F40" s="26">
         <f>D40*E40</f>
         <v/>
       </c>
-      <c r="G40" s="25" t="n">
+      <c r="G40" s="24" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -4928,14 +5212,14 @@
       <c r="D41" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="E41" s="25" t="n">
+      <c r="E41" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="F41" s="27">
+      <c r="F41" s="26">
         <f>D41*E41</f>
         <v/>
       </c>
-      <c r="G41" s="25" t="n">
+      <c r="G41" s="24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4958,14 +5242,14 @@
       <c r="D42" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="E42" s="25" t="n">
+      <c r="E42" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="F42" s="27">
+      <c r="F42" s="26">
         <f>D42*E42</f>
         <v/>
       </c>
-      <c r="G42" s="25" t="n">
+      <c r="G42" s="24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4988,14 +5272,14 @@
       <c r="D43" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="E43" s="25" t="n">
+      <c r="E43" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="F43" s="27">
+      <c r="F43" s="26">
         <f>D43*E43</f>
         <v/>
       </c>
-      <c r="G43" s="25" t="n">
+      <c r="G43" s="24" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -5018,14 +5302,14 @@
       <c r="D44" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="E44" s="25" t="n">
+      <c r="E44" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="F44" s="27">
+      <c r="F44" s="26">
         <f>D44*E44</f>
         <v/>
       </c>
-      <c r="G44" s="25" t="n">
+      <c r="G44" s="24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5048,15 +5332,210 @@
       <c r="D45" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="E45" s="25" t="n">
+      <c r="E45" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="27">
+      <c r="F45" s="26">
         <f>D45*E45</f>
         <v/>
       </c>
-      <c r="G45" s="25" t="n">
+      <c r="G45" s="24" t="n">
         <v>2.5</v>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Exit value — PRIMARY basis (forward-pipeline rNPV + retained cash − debt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>Pipeline depth at exit (projects in flight)</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>Illustrative / the manager claim (see config)</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G48" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>Interim distribution fraction (of realised profit)</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>Illustrative / the manager claim (see config)</t>
+        </is>
+      </c>
+      <c r="F49" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>Debt at exit</t>
+        </is>
+      </c>
+      <c r="C50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>$m</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>Illustrative / the manager claim (see config)</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Exit value CROSS-CHECK — earnings multiple on forward run-rate profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>Cross-check multiple — low</t>
+        </is>
+      </c>
+      <c r="C52" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>Illustrative / the manager claim (see config)</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>Cross-check multiple — base</t>
+        </is>
+      </c>
+      <c r="C53" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>Illustrative / the manager claim (see config)</t>
+        </is>
+      </c>
+      <c r="F53" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G53" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>Cross-check multiple — high</t>
+        </is>
+      </c>
+      <c r="C54" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="inlineStr">
+        <is>
+          <t>Illustrative / the manager claim (see config)</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5262,13 +5741,13 @@
           <t>Development-approval rate (DA gate — the 40/65/80%)</t>
         </is>
       </c>
-      <c r="B5" s="26" t="n">
+      <c r="B5" s="25" t="n">
         <v>0.4</v>
       </c>
-      <c r="C5" s="26" t="n">
+      <c r="C5" s="25" t="n">
         <v>0.65</v>
       </c>
-      <c r="D5" s="26" t="n">
+      <c r="D5" s="25" t="n">
         <v>0.8</v>
       </c>
       <c r="E5" s="18">
@@ -5363,13 +5842,13 @@
           <t>Weight</t>
         </is>
       </c>
-      <c r="B13" s="26" t="n">
+      <c r="B13" s="25" t="n">
         <v>0.3</v>
       </c>
-      <c r="C13" s="26" t="n">
+      <c r="C13" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="D13" s="26" t="n">
+      <c r="D13" s="25" t="n">
         <v>0.2</v>
       </c>
       <c r="E13" s="18">
@@ -6078,10 +6557,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="4" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -6104,7 +6583,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>The company's own business plan (no fund fees, no carry): the funnel widens as success falls (projects_started = target ÷ flip success). Net programme profit = gross proceeds − total development cost. We value the company at exit as a repeatable platform = net profit × the platform exit multiple. All figures AUD $m.</t>
+          <t>A develop-and-flip company is a development PLATFORM, so a buyer pays for its FORWARD pipeline, not past profit. PRIMARY exit equity = forward-pipeline rNPV (projects still in flight at exit) + cash RETAINED on the balance sheet − debt. Realised programme profit feeds RETAINED cash (counted once, at face value — never at a multiple). The earnings multiple below is a CROSS-CHECK only. All figures AUD $m.</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6663,7 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Proceeds &amp; net programme profit</t>
+          <t>Proceeds &amp; realised programme profit</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6692,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Net programme profit (gross − total dev cost)</t>
+          <t>Realised net programme profit (gross − total dev cost)</t>
         </is>
       </c>
       <c r="C14" s="50">
@@ -6222,32 +6701,156 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Company exit equity value (live)</t>
-        </is>
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Forward run-rate annual dev profit (= realised ÷ term)</t>
+        </is>
+      </c>
+      <c r="C15" s="44">
+        <f>IFERROR(C14/'Inputs'!$C$11,0)</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Platform exit multiple</t>
-        </is>
-      </c>
-      <c r="C16" s="43">
-        <f>'Inputs'!$C$18</f>
-        <v/>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Company exit equity — PRIMARY (forward-pipeline rNPV + retained − debt)</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Company exit equity = MAX(0, net) × multiple</t>
-        </is>
-      </c>
-      <c r="C17" s="51">
-        <f>MAX(0,C14)*C16</f>
-        <v/>
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Avg years to sale (pipeline)</t>
+        </is>
+      </c>
+      <c r="C17" s="49">
+        <f>AVERAGE('Calc_Project_rNPV'!$D$4:$D$9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Discount factor @ base over avg years</t>
+        </is>
+      </c>
+      <c r="C18" s="45">
+        <f>1/(1+'Inputs'!$C$7)^C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Per-project rNPV (blended; live scenario)</t>
+        </is>
+      </c>
+      <c r="C19" s="44">
+        <f>('Calc_Project_rNPV'!$M$11*'Scenarios'!$E$6-C9)*C5*C18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Pipeline depth at exit (projects in flight)</t>
+        </is>
+      </c>
+      <c r="C20" s="40">
+        <f>'Inputs'!$C$48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Forward pipeline rNPV at exit (= depth × per-project)</t>
+        </is>
+      </c>
+      <c r="C21" s="50">
+        <f>C20*C19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>Net cash retained at exit (= MAX(0,realised) × (1−dist frac))</t>
+        </is>
+      </c>
+      <c r="C22" s="50">
+        <f>MAX(0,C14)*(1-'Inputs'!$C$49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Debt at exit</t>
+        </is>
+      </c>
+      <c r="C23" s="51">
+        <f>'Inputs'!$C$50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Company exit equity = forward + retained − debt</t>
+        </is>
+      </c>
+      <c r="C24" s="52">
+        <f>MAX(0,C21+C22-C23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Cross-check — earnings multiple on run-rate (NOT the primary number)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Cross-check exit eq — low (run-rate × low mult + retained − debt)</t>
+        </is>
+      </c>
+      <c r="C26" s="50">
+        <f>MAX(0,C15)*'Inputs'!$C$52+C22-C23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Cross-check exit eq — base</t>
+        </is>
+      </c>
+      <c r="C27" s="50">
+        <f>MAX(0,C15)*'Inputs'!$C$53+C22-C23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Cross-check exit eq — high</t>
+        </is>
+      </c>
+      <c r="C28" s="50">
+        <f>MAX(0,C15)*'Inputs'!$C$54+C22-C23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>Primary (pipeline) vs cross-check (base mult): anchor on the more conservative pipeline basis; if they diverge materially, the multiple is more generous than the risk-adjusted forward pipeline.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/financial_models/BESS_Valuation.xlsx
+++ b/financial_models/BESS_Valuation.xlsx
@@ -154,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -264,6 +264,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -757,7 +759,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>'Checks'!$B$23</f>
+        <f>'Checks'!$B$24</f>
         <v/>
       </c>
     </row>
@@ -2771,7 +2773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3124,19 +3126,56 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>Provenance: unverified inputs flagged, not silently independent</t>
+        </is>
+      </c>
+      <c r="B22" s="38">
+        <f>IF(OR(AND('Inputs'!$C$57=1,'Inputs'!$C$58=1),'Inputs'!$C$59=1),"OK","ERROR")</f>
+        <v/>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Contamination guard (see advisory below)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>MASTER CHECK</t>
         </is>
       </c>
-      <c r="B23" s="64">
-        <f>IF(COUNTIF(B4:B21,"ERROR")=0,"OK","ERROR")</f>
-        <v/>
+      <c r="B24" s="64">
+        <f>IF(COUNTIF(B4:B22,"ERROR")=0,"OK","ERROR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="65" t="inlineStr">
+        <is>
+          <t>PROVENANCE STATUS (advisory — not in master)</t>
+        </is>
+      </c>
+      <c r="B26" s="66">
+        <f>IF(AND('Inputs'!$C$57=1,'Inputs'!$C$58=1),"Verified","UNVERIFIED — verify RTB &amp; dev cost")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>The independent pipeline rNPV currently consumes the manager's UNVERIFIED RTB $/MW and dev-cost claims (tagged Proposed). The value is illustrative until each is verified against a primary source and re-tagged Independent (verified). Verifying them is more likely to LOWER the value than raise it — widening, not closing, the entry-price gap. Master check is unaffected (this is a disclosure).</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:B23">
+  <mergeCells count="1">
+    <mergeCell ref="A27:G27"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B4:B24">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -3202,8 +3241,8 @@
           <t>Master check</t>
         </is>
       </c>
-      <c r="E4" s="65">
-        <f>'Checks'!$B$23</f>
+      <c r="E4" s="67">
+        <f>'Checks'!$B$24</f>
         <v/>
       </c>
     </row>
@@ -3245,7 +3284,7 @@
           <t>Expected MOIC</t>
         </is>
       </c>
-      <c r="B8" s="66">
+      <c r="B8" s="68">
         <f>'Returns'!$E$36</f>
         <v/>
       </c>
@@ -3276,7 +3315,7 @@
           <t>Liquidation preference (x)</t>
         </is>
       </c>
-      <c r="E10" s="66">
+      <c r="E10" s="68">
         <f>'Inputs'!$C$17</f>
         <v/>
       </c>
@@ -3320,7 +3359,7 @@
           <t>Equity IRR</t>
         </is>
       </c>
-      <c r="D14" s="67" t="inlineStr">
+      <c r="D14" s="69" t="inlineStr">
         <is>
           <t>Programme capital $m</t>
         </is>
@@ -3344,7 +3383,7 @@
         <f>'Returns'!$B$30</f>
         <v/>
       </c>
-      <c r="D15" s="68" t="inlineStr">
+      <c r="D15" s="70" t="inlineStr">
         <is>
           <t>Projects target</t>
         </is>
@@ -3368,7 +3407,7 @@
         <f>'Returns'!$C$30</f>
         <v/>
       </c>
-      <c r="D16" s="68" t="inlineStr">
+      <c r="D16" s="70" t="inlineStr">
         <is>
           <t>Manager headline DA gate (Base)</t>
         </is>
@@ -3392,7 +3431,7 @@
         <f>'Returns'!$D$30</f>
         <v/>
       </c>
-      <c r="D17" s="68" t="inlineStr">
+      <c r="D17" s="70" t="inlineStr">
         <is>
           <t>True flip success (Base, DAxconnxsale)</t>
         </is>
@@ -4161,7 +4200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4222,7 +4261,7 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>Claude Code (v1 draft)</t>
+          <t>Analyst (v1 draft)</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4283,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Claude Code (v2 reframe)</t>
+          <t>Analyst (v2 reframe)</t>
         </is>
       </c>
     </row>
@@ -4266,12 +4305,34 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Claude Code (v3 exit-basis)</t>
+          <t>Analyst (v3 exit-basis)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="C7" s="13" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>v4.0</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Added input PROVENANCE (change5): every price/value input tagged Proposed (manager) / Independent (verified) / Placeholder, plus a contamination guard so the independent rNPV consumes only verified inputs. RTB $/MW and dev cost are the manager's UNVERIFIED claims, so the independent value is illustrative pending verification (advisory on this tab). Anonymised: no real names; all monetary figures are illustrative placeholders.</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Analyst (v4 provenance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>[Analyst review pass — record changes here]</t>
         </is>
@@ -4292,7 +4353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -5535,6 +5596,51 @@
       <c r="G54" s="17" t="inlineStr">
         <is>
           <t>TO CONFIRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Input provenance flags (change5) — 1 = Independent (verified); 0 = Proposed/Placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>RTB $/MW verified? (feeds independent rNPV)</t>
+        </is>
+      </c>
+      <c r="C57" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>Dev cost verified? (feeds independent rNPV)</t>
+        </is>
+      </c>
+      <c r="C58" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t>Provenance tagged &amp; disclosed?</t>
+        </is>
+      </c>
+      <c r="C59" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>RTB $/MW and dev cost are the manager's UNVERIFIED claims (Proposed) — verify against a primary source (comparable RTB sales; bottom-up costs) and set the flag to 1 before treating the rNPV as independent.</t>
         </is>
       </c>
     </row>

--- a/financial_models/BESS_Valuation.xlsx
+++ b/financial_models/BESS_Valuation.xlsx
@@ -1041,6 +1041,7 @@
         <v/>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
@@ -1431,6 +1432,7 @@
         <v/>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
@@ -1525,6 +1527,7 @@
         <v/>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
@@ -1603,6 +1606,7 @@
         <v/>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
@@ -1700,6 +1704,7 @@
         <v/>
       </c>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
@@ -1831,7 +1836,7 @@
         </is>
       </c>
       <c r="C6" s="50">
-        <f>'Inputs'!$C$21*'Scenarios'!$C$7*6</f>
+        <f>'Inputs'!$C$21*'Scenarios'!$C$7*COUNT('Calc_Project_rNPV'!$C$4:$C$9)</f>
         <v/>
       </c>
     </row>
@@ -1868,6 +1873,7 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -1952,6 +1958,7 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -2106,6 +2113,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -2227,6 +2235,8 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="60" t="inlineStr">
         <is>
@@ -2797,6 +2807,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
@@ -3142,6 +3153,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
@@ -3153,6 +3165,7 @@
         <v/>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="65" t="inlineStr">
         <is>
@@ -4790,7 +4803,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -5404,7 +5416,6 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
@@ -5599,7 +5610,6 @@
         </is>
       </c>
     </row>
-    <row r="55"/>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
@@ -5901,6 +5911,7 @@
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
@@ -5912,6 +5923,7 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -5962,6 +5974,7 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
@@ -6084,6 +6097,7 @@
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
@@ -6106,6 +6120,7 @@
         <v/>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
@@ -6693,6 +6708,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>

--- a/financial_models/BESS_Valuation.xlsx
+++ b/financial_models/BESS_Valuation.xlsx
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>AEMO Connections Scorecard / KCI — connection success rate &amp; duration (benchmark)</t>
+          <t>AEMO Connections Scorecard / KCI — RTB-stage connection AGREEMENT + GPS (registration / ready-for-construction; NOT energisation) [[TO CONFIRM]]</t>
         </is>
       </c>
     </row>
@@ -4950,7 +4950,7 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>Grid connection (separate gate)</t>
+          <t>Grid connection — RTB rights (agreement + GPS)</t>
         </is>
       </c>
       <c r="C27" s="16" t="n">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>AEMO Connections Scorecard / KCI — connection success rate &amp; duration (benchmark)</t>
+          <t>AEMO Connections Scorecard / KCI — RTB-stage connection AGREEMENT + GPS (registration / ready-for-construction; NOT energisation) [[TO CONFIRM]]</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr">
@@ -5997,7 +5997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6059,7 +6059,7 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Grid connection</t>
+          <t>Grid connection — RTB rights (agreement + GPS)</t>
         </is>
       </c>
       <c r="B5" s="35">
@@ -6153,6 +6153,21 @@
       <c r="A15" s="14" t="inlineStr">
         <is>
           <t>The 65% headline is the approval gate alone; after grid connection (~70%) and sale (~80%) the true flip success is ~36%. The DA gate is the master return driver — the scenarios move it 40/65/80%. The sub-5MW AEMO registration exemption MAY lift small-distribution success — verify per state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Grid connection = RTB-stage connection RIGHTS: the connection AGREEMENT + Generator Performance Standards (GPS) that make a project ready-to-build (AEMO Scorecard 'registration / executed connection agreement' stage) — NOT energisation/commissioning of a built battery (a flip sells pre-construction). 70% is a benchmark [[TO CONFIRM]].</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Gates 2 &amp; 3 are INDEPENDENT (no double-count): gate 2 = did the project SECURE connection rights/GPS; gate 3 = given a genuinely RTB project, did a BUYER pay RTB price (demand/price risk, not connection again).</t>
         </is>
       </c>
     </row>

--- a/financial_models/BESS_Valuation.xlsx
+++ b/financial_models/BESS_Valuation.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contents" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calc_Survival" sheetId="7" state="visible" r:id="rId7"/>
@@ -89,12 +89,12 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00008000"/>
       <sz val="10"/>
     </font>
@@ -154,15 +154,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -201,6 +201,9 @@
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -213,24 +216,27 @@
     <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -238,17 +244,14 @@
     <xf numFmtId="167" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -266,10 +269,10 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -992,8 +995,8 @@
           <t>Pre-money valuation</t>
         </is>
       </c>
-      <c r="B4" s="51">
-        <f>'Inputs'!$C$13</f>
+      <c r="B4" s="53">
+        <f>'Assumptions'!$C$13</f>
         <v/>
       </c>
     </row>
@@ -1003,8 +1006,8 @@
           <t>Our investment</t>
         </is>
       </c>
-      <c r="B5" s="51">
-        <f>'Inputs'!$C$14</f>
+      <c r="B5" s="53">
+        <f>'Assumptions'!$C$14</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1017,7 @@
           <t>Post-money = pre-money + investment</t>
         </is>
       </c>
-      <c r="B6" s="53">
+      <c r="B6" s="55">
         <f>B4+B5</f>
         <v/>
       </c>
@@ -1036,8 +1039,8 @@
           <t>Ownership at exit (diluted)</t>
         </is>
       </c>
-      <c r="B8" s="37">
-        <f>B7*(1-'Inputs'!$C$15)*(1-'Inputs'!$C$16)</f>
+      <c r="B8" s="39">
+        <f>B7*(1-'Assumptions'!$C$15)*(1-'Assumptions'!$C$16)</f>
         <v/>
       </c>
     </row>
@@ -1077,16 +1080,16 @@
           <t>Flip success (DA × conn × sale)</t>
         </is>
       </c>
-      <c r="B12" s="36">
-        <f>'Scenarios'!$B$5*'Inputs'!$C$27*'Inputs'!$C$28</f>
-        <v/>
-      </c>
-      <c r="C12" s="36">
-        <f>'Scenarios'!$C$5*'Inputs'!$C$27*'Inputs'!$C$28</f>
-        <v/>
-      </c>
-      <c r="D12" s="36">
-        <f>'Scenarios'!$D$5*'Inputs'!$C$27*'Inputs'!$C$28</f>
+      <c r="B12" s="38">
+        <f>'Scenarios'!$B$5*'Assumptions'!$C$27*'Assumptions'!$C$28</f>
+        <v/>
+      </c>
+      <c r="C12" s="38">
+        <f>'Scenarios'!$C$5*'Assumptions'!$C$27*'Assumptions'!$C$28</f>
+        <v/>
+      </c>
+      <c r="D12" s="38">
+        <f>'Scenarios'!$D$5*'Assumptions'!$C$27*'Assumptions'!$C$28</f>
         <v/>
       </c>
     </row>
@@ -1096,15 +1099,15 @@
           <t>RTB price multiplier</t>
         </is>
       </c>
-      <c r="B13" s="43">
+      <c r="B13" s="45">
         <f>'Scenarios'!$B$6</f>
         <v/>
       </c>
-      <c r="C13" s="43">
+      <c r="C13" s="45">
         <f>'Scenarios'!$C$6</f>
         <v/>
       </c>
-      <c r="D13" s="43">
+      <c r="D13" s="45">
         <f>'Scenarios'!$D$6</f>
         <v/>
       </c>
@@ -1115,15 +1118,15 @@
           <t>Dev cost multiplier</t>
         </is>
       </c>
-      <c r="B14" s="43">
+      <c r="B14" s="45">
         <f>'Scenarios'!$B$7</f>
         <v/>
       </c>
-      <c r="C14" s="43">
+      <c r="C14" s="45">
         <f>'Scenarios'!$C$7</f>
         <v/>
       </c>
-      <c r="D14" s="43">
+      <c r="D14" s="45">
         <f>'Scenarios'!$D$7</f>
         <v/>
       </c>
@@ -1134,16 +1137,16 @@
           <t>Dev cost per project</t>
         </is>
       </c>
-      <c r="B15" s="44">
-        <f>'Inputs'!$C$21*B14</f>
-        <v/>
-      </c>
-      <c r="C15" s="44">
-        <f>'Inputs'!$C$21*C14</f>
-        <v/>
-      </c>
-      <c r="D15" s="44">
-        <f>'Inputs'!$C$21*D14</f>
+      <c r="B15" s="46">
+        <f>'Assumptions'!$C$21*B14</f>
+        <v/>
+      </c>
+      <c r="C15" s="46">
+        <f>'Assumptions'!$C$21*C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="46">
+        <f>'Assumptions'!$C$21*D14</f>
         <v/>
       </c>
     </row>
@@ -1153,16 +1156,16 @@
           <t>Projects started</t>
         </is>
       </c>
-      <c r="B16" s="49">
-        <f>IFERROR('Inputs'!$C$10/B12,0)</f>
-        <v/>
-      </c>
-      <c r="C16" s="49">
-        <f>IFERROR('Inputs'!$C$10/C12,0)</f>
-        <v/>
-      </c>
-      <c r="D16" s="49">
-        <f>IFERROR('Inputs'!$C$10/D12,0)</f>
+      <c r="B16" s="51">
+        <f>IFERROR('Assumptions'!$C$10/B12,0)</f>
+        <v/>
+      </c>
+      <c r="C16" s="51">
+        <f>IFERROR('Assumptions'!$C$10/C12,0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="51">
+        <f>IFERROR('Assumptions'!$C$10/D12,0)</f>
         <v/>
       </c>
     </row>
@@ -1172,16 +1175,16 @@
           <t>Projects failed</t>
         </is>
       </c>
-      <c r="B17" s="49">
-        <f>B16-'Inputs'!$C$10</f>
-        <v/>
-      </c>
-      <c r="C17" s="49">
-        <f>C16-'Inputs'!$C$10</f>
-        <v/>
-      </c>
-      <c r="D17" s="49">
-        <f>D16-'Inputs'!$C$10</f>
+      <c r="B17" s="51">
+        <f>B16-'Assumptions'!$C$10</f>
+        <v/>
+      </c>
+      <c r="C17" s="51">
+        <f>C16-'Assumptions'!$C$10</f>
+        <v/>
+      </c>
+      <c r="D17" s="51">
+        <f>D16-'Assumptions'!$C$10</f>
         <v/>
       </c>
     </row>
@@ -1191,16 +1194,16 @@
           <t>Total dev cost</t>
         </is>
       </c>
-      <c r="B18" s="50">
-        <f>'Inputs'!$C$10*B15+B17*'Inputs'!$C$22*B15</f>
-        <v/>
-      </c>
-      <c r="C18" s="50">
-        <f>'Inputs'!$C$10*C15+C17*'Inputs'!$C$22*C15</f>
-        <v/>
-      </c>
-      <c r="D18" s="50">
-        <f>'Inputs'!$C$10*D15+D17*'Inputs'!$C$22*D15</f>
+      <c r="B18" s="52">
+        <f>'Assumptions'!$C$10*B15+B17*'Assumptions'!$C$22*B15</f>
+        <v/>
+      </c>
+      <c r="C18" s="52">
+        <f>'Assumptions'!$C$10*C15+C17*'Assumptions'!$C$22*C15</f>
+        <v/>
+      </c>
+      <c r="D18" s="52">
+        <f>'Assumptions'!$C$10*D15+D17*'Assumptions'!$C$22*D15</f>
         <v/>
       </c>
     </row>
@@ -1210,16 +1213,16 @@
           <t>Gross proceeds</t>
         </is>
       </c>
-      <c r="B19" s="50">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*B13</f>
-        <v/>
-      </c>
-      <c r="C19" s="50">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*C13</f>
-        <v/>
-      </c>
-      <c r="D19" s="50">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*D13</f>
+      <c r="B19" s="52">
+        <f>'Assumptions'!$C$10*'Calc_Project_rNPV'!$M$11*B13</f>
+        <v/>
+      </c>
+      <c r="C19" s="52">
+        <f>'Assumptions'!$C$10*'Calc_Project_rNPV'!$M$11*C13</f>
+        <v/>
+      </c>
+      <c r="D19" s="52">
+        <f>'Assumptions'!$C$10*'Calc_Project_rNPV'!$M$11*D13</f>
         <v/>
       </c>
     </row>
@@ -1229,15 +1232,15 @@
           <t>Realised net programme profit</t>
         </is>
       </c>
-      <c r="B20" s="50">
+      <c r="B20" s="52">
         <f>B19-B18</f>
         <v/>
       </c>
-      <c r="C20" s="50">
+      <c r="C20" s="52">
         <f>C19-C18</f>
         <v/>
       </c>
-      <c r="D20" s="50">
+      <c r="D20" s="52">
         <f>D19-D18</f>
         <v/>
       </c>
@@ -1248,16 +1251,16 @@
           <t>Forward pipeline rNPV at exit (depth × per-project)</t>
         </is>
       </c>
-      <c r="B21" s="44">
-        <f>'Inputs'!$C$48*('Calc_Project_rNPV'!$M$11*B13-B15)*B12*'Calc_Company'!$C$18</f>
-        <v/>
-      </c>
-      <c r="C21" s="44">
-        <f>'Inputs'!$C$48*('Calc_Project_rNPV'!$M$11*C13-C15)*C12*'Calc_Company'!$C$18</f>
-        <v/>
-      </c>
-      <c r="D21" s="44">
-        <f>'Inputs'!$C$48*('Calc_Project_rNPV'!$M$11*D13-D15)*D12*'Calc_Company'!$C$18</f>
+      <c r="B21" s="46">
+        <f>'Assumptions'!$C$48*('Calc_Project_rNPV'!$M$11*B13-B15)*B12*'Calc_Company'!$C$18</f>
+        <v/>
+      </c>
+      <c r="C21" s="46">
+        <f>'Assumptions'!$C$48*('Calc_Project_rNPV'!$M$11*C13-C15)*C12*'Calc_Company'!$C$18</f>
+        <v/>
+      </c>
+      <c r="D21" s="46">
+        <f>'Assumptions'!$C$48*('Calc_Project_rNPV'!$M$11*D13-D15)*D12*'Calc_Company'!$C$18</f>
         <v/>
       </c>
     </row>
@@ -1267,16 +1270,16 @@
           <t>Net cash retained = MAX(0,realised)×(1−dist)</t>
         </is>
       </c>
-      <c r="B22" s="44">
-        <f>MAX(0,B20)*(1-'Inputs'!$C$49)</f>
-        <v/>
-      </c>
-      <c r="C22" s="44">
-        <f>MAX(0,C20)*(1-'Inputs'!$C$49)</f>
-        <v/>
-      </c>
-      <c r="D22" s="44">
-        <f>MAX(0,D20)*(1-'Inputs'!$C$49)</f>
+      <c r="B22" s="46">
+        <f>MAX(0,B20)*(1-'Assumptions'!$C$49)</f>
+        <v/>
+      </c>
+      <c r="C22" s="46">
+        <f>MAX(0,C20)*(1-'Assumptions'!$C$49)</f>
+        <v/>
+      </c>
+      <c r="D22" s="46">
+        <f>MAX(0,D20)*(1-'Assumptions'!$C$49)</f>
         <v/>
       </c>
     </row>
@@ -1286,16 +1289,16 @@
           <t>Company exit equity = fwd + retained − debt</t>
         </is>
       </c>
-      <c r="B23" s="53">
-        <f>MAX(0,B21+B22-'Inputs'!$C$50)</f>
-        <v/>
-      </c>
-      <c r="C23" s="53">
-        <f>MAX(0,C21+C22-'Inputs'!$C$50)</f>
-        <v/>
-      </c>
-      <c r="D23" s="53">
-        <f>MAX(0,D21+D22-'Inputs'!$C$50)</f>
+      <c r="B23" s="55">
+        <f>MAX(0,B21+B22-'Assumptions'!$C$50)</f>
+        <v/>
+      </c>
+      <c r="C23" s="55">
+        <f>MAX(0,C21+C22-'Assumptions'!$C$50)</f>
+        <v/>
+      </c>
+      <c r="D23" s="55">
+        <f>MAX(0,D21+D22-'Assumptions'!$C$50)</f>
         <v/>
       </c>
     </row>
@@ -1305,15 +1308,15 @@
           <t>As-converted (diluted × exit equity)</t>
         </is>
       </c>
-      <c r="B24" s="44">
+      <c r="B24" s="46">
         <f>'Returns'!$B$8*B23</f>
         <v/>
       </c>
-      <c r="C24" s="44">
+      <c r="C24" s="46">
         <f>'Returns'!$B$8*C23</f>
         <v/>
       </c>
-      <c r="D24" s="44">
+      <c r="D24" s="46">
         <f>'Returns'!$B$8*D23</f>
         <v/>
       </c>
@@ -1324,16 +1327,16 @@
           <t>Preference claim = MIN(liq×inv, exit eq)</t>
         </is>
       </c>
-      <c r="B25" s="44">
-        <f>MIN('Inputs'!$C$17*'Inputs'!$C$14,B23)</f>
-        <v/>
-      </c>
-      <c r="C25" s="44">
-        <f>MIN('Inputs'!$C$17*'Inputs'!$C$14,C23)</f>
-        <v/>
-      </c>
-      <c r="D25" s="44">
-        <f>MIN('Inputs'!$C$17*'Inputs'!$C$14,D23)</f>
+      <c r="B25" s="46">
+        <f>MIN('Assumptions'!$C$17*'Assumptions'!$C$14,B23)</f>
+        <v/>
+      </c>
+      <c r="C25" s="46">
+        <f>MIN('Assumptions'!$C$17*'Assumptions'!$C$14,C23)</f>
+        <v/>
+      </c>
+      <c r="D25" s="46">
+        <f>MIN('Assumptions'!$C$17*'Assumptions'!$C$14,D23)</f>
         <v/>
       </c>
     </row>
@@ -1343,15 +1346,15 @@
           <t>Terminal proceeds = MAX(pref, as-converted)</t>
         </is>
       </c>
-      <c r="B26" s="47">
+      <c r="B26" s="49">
         <f>MAX(B25,B24)</f>
         <v/>
       </c>
-      <c r="C26" s="47">
+      <c r="C26" s="49">
         <f>MAX(C25,C24)</f>
         <v/>
       </c>
-      <c r="D26" s="47">
+      <c r="D26" s="49">
         <f>MAX(D25,D24)</f>
         <v/>
       </c>
@@ -1362,16 +1365,16 @@
           <t>Interim distributions (diluted×dist×realised)</t>
         </is>
       </c>
-      <c r="B27" s="44">
-        <f>'Returns'!$B$8*'Inputs'!$C$49*MAX(0,B20)</f>
-        <v/>
-      </c>
-      <c r="C27" s="44">
-        <f>'Returns'!$B$8*'Inputs'!$C$49*MAX(0,C20)</f>
-        <v/>
-      </c>
-      <c r="D27" s="44">
-        <f>'Returns'!$B$8*'Inputs'!$C$49*MAX(0,D20)</f>
+      <c r="B27" s="46">
+        <f>'Returns'!$B$8*'Assumptions'!$C$49*MAX(0,B20)</f>
+        <v/>
+      </c>
+      <c r="C27" s="46">
+        <f>'Returns'!$B$8*'Assumptions'!$C$49*MAX(0,C20)</f>
+        <v/>
+      </c>
+      <c r="D27" s="46">
+        <f>'Returns'!$B$8*'Assumptions'!$C$49*MAX(0,D20)</f>
         <v/>
       </c>
     </row>
@@ -1381,15 +1384,15 @@
           <t>Our total proceeds = terminal + interim</t>
         </is>
       </c>
-      <c r="B28" s="47">
+      <c r="B28" s="49">
         <f>B26+B27</f>
         <v/>
       </c>
-      <c r="C28" s="47">
+      <c r="C28" s="49">
         <f>C26+C27</f>
         <v/>
       </c>
-      <c r="D28" s="47">
+      <c r="D28" s="49">
         <f>D26+D27</f>
         <v/>
       </c>
@@ -1400,16 +1403,16 @@
           <t>MOIC = our proceeds ÷ our investment</t>
         </is>
       </c>
-      <c r="B29" s="54">
-        <f>IFERROR(B28/'Inputs'!$C$14,0)</f>
-        <v/>
-      </c>
-      <c r="C29" s="54">
-        <f>IFERROR(C28/'Inputs'!$C$14,0)</f>
-        <v/>
-      </c>
-      <c r="D29" s="54">
-        <f>IFERROR(D28/'Inputs'!$C$14,0)</f>
+      <c r="B29" s="56">
+        <f>IFERROR(B28/'Assumptions'!$C$14,0)</f>
+        <v/>
+      </c>
+      <c r="C29" s="56">
+        <f>IFERROR(C28/'Assumptions'!$C$14,0)</f>
+        <v/>
+      </c>
+      <c r="D29" s="56">
+        <f>IFERROR(D28/'Assumptions'!$C$14,0)</f>
         <v/>
       </c>
     </row>
@@ -1420,15 +1423,15 @@
         </is>
       </c>
       <c r="B30" s="18">
-        <f>IFERROR(B29^(1/'Inputs'!$C$18)-1,-1)</f>
+        <f>IFERROR(B29^(1/'Assumptions'!$C$18)-1,-1)</f>
         <v/>
       </c>
       <c r="C30" s="18">
-        <f>IFERROR(C29^(1/'Inputs'!$C$18)-1,-1)</f>
+        <f>IFERROR(C29^(1/'Assumptions'!$C$18)-1,-1)</f>
         <v/>
       </c>
       <c r="D30" s="18">
-        <f>IFERROR(D29^(1/'Inputs'!$C$18)-1,-1)</f>
+        <f>IFERROR(D29^(1/'Assumptions'!$C$18)-1,-1)</f>
         <v/>
       </c>
     </row>
@@ -1469,15 +1472,15 @@
           <t>Weight</t>
         </is>
       </c>
-      <c r="B34" s="55">
+      <c r="B34" s="33">
         <f>'Scenarios'!$B$13</f>
         <v/>
       </c>
-      <c r="C34" s="55">
+      <c r="C34" s="33">
         <f>'Scenarios'!$C$13</f>
         <v/>
       </c>
-      <c r="D34" s="55">
+      <c r="D34" s="33">
         <f>'Scenarios'!$D$13</f>
         <v/>
       </c>
@@ -1488,19 +1491,19 @@
           <t>Our proceeds</t>
         </is>
       </c>
-      <c r="B35" s="56">
+      <c r="B35" s="57">
         <f>'Returns'!$B$28</f>
         <v/>
       </c>
-      <c r="C35" s="56">
+      <c r="C35" s="57">
         <f>'Returns'!$C$28</f>
         <v/>
       </c>
-      <c r="D35" s="56">
+      <c r="D35" s="57">
         <f>'Returns'!$D$28</f>
         <v/>
       </c>
-      <c r="E35" s="47">
+      <c r="E35" s="49">
         <f>SUMPRODUCT('Scenarios'!$B$13:$D$13,B35:D35)</f>
         <v/>
       </c>
@@ -1511,8 +1514,8 @@
           <t>Expected MOIC = exp proceeds ÷ investment</t>
         </is>
       </c>
-      <c r="E36" s="54">
-        <f>IFERROR(E35/'Inputs'!$C$14,0)</f>
+      <c r="E36" s="56">
+        <f>IFERROR(E35/'Assumptions'!$C$14,0)</f>
         <v/>
       </c>
     </row>
@@ -1522,8 +1525,8 @@
           <t>Expected equity IRR = exp MOIC^(1/exit yr) − 1</t>
         </is>
       </c>
-      <c r="E37" s="37">
-        <f>IFERROR(E36^(1/'Inputs'!$C$18)-1,-1)</f>
+      <c r="E37" s="39">
+        <f>IFERROR(E36^(1/'Assumptions'!$C$18)-1,-1)</f>
         <v/>
       </c>
     </row>
@@ -1546,7 +1549,7 @@
           <t>rNPV pipeline (Base)</t>
         </is>
       </c>
-      <c r="C40" s="56">
+      <c r="C40" s="57">
         <f>'Calc_Project_rNPV'!$M$10</f>
         <v/>
       </c>
@@ -1557,7 +1560,7 @@
           <t>$/MW benchmark (dev value)</t>
         </is>
       </c>
-      <c r="C41" s="56">
+      <c r="C41" s="57">
         <f>'Calc_CrossChecks'!$C$9</f>
         <v/>
       </c>
@@ -1568,7 +1571,7 @@
           <t>VC method (today value)</t>
         </is>
       </c>
-      <c r="C42" s="56">
+      <c r="C42" s="57">
         <f>'Calc_CrossChecks'!$C$18</f>
         <v/>
       </c>
@@ -1579,7 +1582,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="C43" s="47">
+      <c r="C43" s="49">
         <f>MIN(C40:C42)</f>
         <v/>
       </c>
@@ -1590,7 +1593,7 @@
           <t>Midpoint</t>
         </is>
       </c>
-      <c r="C44" s="48">
+      <c r="C44" s="50">
         <f>AVERAGE(C40:C42)</f>
         <v/>
       </c>
@@ -1601,7 +1604,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="C45" s="47">
+      <c r="C45" s="49">
         <f>MAX(C40:C42)</f>
         <v/>
       </c>
@@ -1637,12 +1640,12 @@
           <t>Founders / existing holders</t>
         </is>
       </c>
-      <c r="B49" s="36">
+      <c r="B49" s="38">
         <f>1-'Returns'!$B$7</f>
         <v/>
       </c>
-      <c r="C49" s="36">
-        <f>(1-'Returns'!$B$7)*(1-'Inputs'!$C$15)*(1-'Inputs'!$C$16)</f>
+      <c r="C49" s="38">
+        <f>(1-'Returns'!$B$7)*(1-'Assumptions'!$C$15)*(1-'Assumptions'!$C$16)</f>
         <v/>
       </c>
     </row>
@@ -1652,11 +1655,11 @@
           <t>Us (new investor)</t>
         </is>
       </c>
-      <c r="B50" s="35">
+      <c r="B50" s="37">
         <f>'Returns'!$B$7</f>
         <v/>
       </c>
-      <c r="C50" s="57">
+      <c r="C50" s="58">
         <f>'Returns'!$B$8</f>
         <v/>
       </c>
@@ -1667,11 +1670,11 @@
           <t>Option pool (staff)</t>
         </is>
       </c>
-      <c r="B51" s="36" t="n">
+      <c r="B51" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="C51" s="36">
-        <f>'Inputs'!$C$15*(1-'Inputs'!$C$16)</f>
+      <c r="C51" s="38">
+        <f>'Assumptions'!$C$15*(1-'Assumptions'!$C$16)</f>
         <v/>
       </c>
     </row>
@@ -1681,11 +1684,11 @@
           <t>Future-round investors</t>
         </is>
       </c>
-      <c r="B52" s="36" t="n">
+      <c r="B52" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="C52" s="35">
-        <f>'Inputs'!$C$16</f>
+      <c r="C52" s="37">
+        <f>'Assumptions'!$C$16</f>
         <v/>
       </c>
     </row>
@@ -1718,7 +1721,7 @@
           <t>Company exit equity (Base)</t>
         </is>
       </c>
-      <c r="C56" s="56">
+      <c r="C56" s="57">
         <f>'Returns'!$C$23</f>
         <v/>
       </c>
@@ -1729,7 +1732,7 @@
           <t>Our terminal proceeds (1x pref / as-converted)</t>
         </is>
       </c>
-      <c r="C57" s="56">
+      <c r="C57" s="57">
         <f>'Returns'!$C$26</f>
         <v/>
       </c>
@@ -1740,7 +1743,7 @@
           <t>Other holders' proceeds (residual)</t>
         </is>
       </c>
-      <c r="C58" s="44">
+      <c r="C58" s="46">
         <f>C56-C57</f>
         <v/>
       </c>
@@ -1751,7 +1754,7 @@
           <t>Distributed (ours + others = exit equity)</t>
         </is>
       </c>
-      <c r="C59" s="47">
+      <c r="C59" s="49">
         <f>C57+C58</f>
         <v/>
       </c>
@@ -1824,7 +1827,7 @@
           <t>Gross RTB asset value $m</t>
         </is>
       </c>
-      <c r="C5" s="50">
+      <c r="C5" s="52">
         <f>SUMPRODUCT('Calc_Project_rNPV'!$C$4:$C$9,'Calc_Project_rNPV'!$E$4:$E$9)*'Scenarios'!$C$6</f>
         <v/>
       </c>
@@ -1835,8 +1838,8 @@
           <t>Total dev cost $m</t>
         </is>
       </c>
-      <c r="C6" s="50">
-        <f>'Inputs'!$C$21*'Scenarios'!$C$7*COUNT('Calc_Project_rNPV'!$C$4:$C$9)</f>
+      <c r="C6" s="52">
+        <f>'Assumptions'!$C$21*'Scenarios'!$C$7*COUNT('Calc_Project_rNPV'!$C$4:$C$9)</f>
         <v/>
       </c>
     </row>
@@ -1846,7 +1849,7 @@
           <t>Average years to sale</t>
         </is>
       </c>
-      <c r="C7" s="49">
+      <c r="C7" s="51">
         <f>AVERAGE('Calc_Project_rNPV'!$D$4:$D$9)</f>
         <v/>
       </c>
@@ -1857,8 +1860,8 @@
           <t>Flip success (Base, DA x conn x sale)</t>
         </is>
       </c>
-      <c r="C8" s="36">
-        <f>'Scenarios'!$C$5*'Inputs'!$C$27*'Inputs'!$C$28</f>
+      <c r="C8" s="38">
+        <f>'Scenarios'!$C$5*'Assumptions'!$C$27*'Assumptions'!$C$28</f>
         <v/>
       </c>
     </row>
@@ -1868,8 +1871,8 @@
           <t>$/MW implied dev value $m</t>
         </is>
       </c>
-      <c r="C9" s="47">
-        <f>IFERROR((C5-C6)*C8/(1+'Inputs'!$C$7)^C7,0)</f>
+      <c r="C9" s="49">
+        <f>IFERROR((C5-C6)*C8/(1+'Assumptions'!$C$7)^C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1887,7 +1890,7 @@
           <t>Total RTB sale value $m</t>
         </is>
       </c>
-      <c r="C12" s="50">
+      <c r="C12" s="52">
         <f>SUMPRODUCT('Calc_Project_rNPV'!$C$4:$C$9,'Calc_Project_rNPV'!$E$4:$E$9)*'Scenarios'!$C$6</f>
         <v/>
       </c>
@@ -1898,7 +1901,7 @@
           <t>Total dev cost $m</t>
         </is>
       </c>
-      <c r="C13" s="50">
+      <c r="C13" s="52">
         <f>C6</f>
         <v/>
       </c>
@@ -1909,7 +1912,7 @@
           <t>Flip success (Base)</t>
         </is>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="37">
         <f>C8</f>
         <v/>
       </c>
@@ -1920,7 +1923,7 @@
           <t>Exit equity value (expected) $m</t>
         </is>
       </c>
-      <c r="C15" s="44">
+      <c r="C15" s="46">
         <f>C14*(C12-C13)</f>
         <v/>
       </c>
@@ -1931,8 +1934,8 @@
           <t>VC target return</t>
         </is>
       </c>
-      <c r="C16" s="35">
-        <f>'Inputs'!$C$34</f>
+      <c r="C16" s="37">
+        <f>'Assumptions'!$C$34</f>
         <v/>
       </c>
     </row>
@@ -1942,8 +1945,8 @@
           <t>Hold horizon (yrs)</t>
         </is>
       </c>
-      <c r="C17" s="40">
-        <f>'Inputs'!$C$11</f>
+      <c r="C17" s="42">
+        <f>'Assumptions'!$C$11</f>
         <v/>
       </c>
     </row>
@@ -1953,7 +1956,7 @@
           <t>VC today value $m</t>
         </is>
       </c>
-      <c r="C18" s="47">
+      <c r="C18" s="49">
         <f>IFERROR(C15/(1+C16)^C17,0)</f>
         <v/>
       </c>
@@ -1994,15 +1997,15 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="B22" s="58">
-        <f>'Inputs'!$C$30</f>
-        <v/>
-      </c>
-      <c r="C22" s="58">
-        <f>'Inputs'!$C$24</f>
-        <v/>
-      </c>
-      <c r="D22" s="36">
+      <c r="B22" s="59">
+        <f>'Assumptions'!$C$30</f>
+        <v/>
+      </c>
+      <c r="C22" s="59">
+        <f>'Assumptions'!$C$24</f>
+        <v/>
+      </c>
+      <c r="D22" s="38">
         <f>IFERROR(B22/C22,0)</f>
         <v/>
       </c>
@@ -2013,15 +2016,15 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="B23" s="58">
-        <f>'Inputs'!$C$31</f>
-        <v/>
-      </c>
-      <c r="C23" s="58">
-        <f>'Inputs'!$C$24</f>
-        <v/>
-      </c>
-      <c r="D23" s="36">
+      <c r="B23" s="59">
+        <f>'Assumptions'!$C$31</f>
+        <v/>
+      </c>
+      <c r="C23" s="59">
+        <f>'Assumptions'!$C$24</f>
+        <v/>
+      </c>
+      <c r="D23" s="38">
         <f>IFERROR(B23/C23,0)</f>
         <v/>
       </c>
@@ -2032,15 +2035,15 @@
           <t>SA</t>
         </is>
       </c>
-      <c r="B24" s="58">
-        <f>'Inputs'!$C$32</f>
-        <v/>
-      </c>
-      <c r="C24" s="58">
-        <f>'Inputs'!$C$24</f>
-        <v/>
-      </c>
-      <c r="D24" s="36">
+      <c r="B24" s="59">
+        <f>'Assumptions'!$C$32</f>
+        <v/>
+      </c>
+      <c r="C24" s="59">
+        <f>'Assumptions'!$C$24</f>
+        <v/>
+      </c>
+      <c r="D24" s="38">
         <f>IFERROR(B24/C24,0)</f>
         <v/>
       </c>
@@ -2120,8 +2123,8 @@
           <t>Conn × sale (flip adj)</t>
         </is>
       </c>
-      <c r="B4" s="36">
-        <f>'Inputs'!$C$27*'Inputs'!$C$28</f>
+      <c r="B4" s="38">
+        <f>'Assumptions'!$C$27*'Assumptions'!$C$28</f>
         <v/>
       </c>
     </row>
@@ -2131,7 +2134,7 @@
           <t>Diluted ownership</t>
         </is>
       </c>
-      <c r="B5" s="35">
+      <c r="B5" s="37">
         <f>'Returns'!$B$8</f>
         <v/>
       </c>
@@ -2142,8 +2145,8 @@
           <t>Pipeline depth at exit</t>
         </is>
       </c>
-      <c r="B6" s="40">
-        <f>'Inputs'!$C$48</f>
+      <c r="B6" s="42">
+        <f>'Assumptions'!$C$48</f>
         <v/>
       </c>
     </row>
@@ -2153,8 +2156,8 @@
           <t>Preference cap (liq × investment) $m</t>
         </is>
       </c>
-      <c r="B7" s="44">
-        <f>'Inputs'!$C$17*'Inputs'!$C$14</f>
+      <c r="B7" s="46">
+        <f>'Assumptions'!$C$17*'Assumptions'!$C$14</f>
         <v/>
       </c>
     </row>
@@ -2164,8 +2167,8 @@
           <t>Our investment $m</t>
         </is>
       </c>
-      <c r="B8" s="56">
-        <f>'Inputs'!$C$14</f>
+      <c r="B8" s="57">
+        <f>'Assumptions'!$C$14</f>
         <v/>
       </c>
     </row>
@@ -2175,8 +2178,8 @@
           <t>Exit year</t>
         </is>
       </c>
-      <c r="B9" s="40">
-        <f>'Inputs'!$C$18</f>
+      <c r="B9" s="42">
+        <f>'Assumptions'!$C$18</f>
         <v/>
       </c>
     </row>
@@ -2186,7 +2189,7 @@
           <t>Base blended sale/project $m</t>
         </is>
       </c>
-      <c r="B10" s="56">
+      <c r="B10" s="57">
         <f>'Calc_Project_rNPV'!$M$11</f>
         <v/>
       </c>
@@ -2197,8 +2200,8 @@
           <t>Dev cost/project $m</t>
         </is>
       </c>
-      <c r="B11" s="56">
-        <f>'Inputs'!$C$21</f>
+      <c r="B11" s="57">
+        <f>'Assumptions'!$C$21</f>
         <v/>
       </c>
     </row>
@@ -2208,7 +2211,7 @@
           <t>Disc factor @ base over avg years</t>
         </is>
       </c>
-      <c r="B12" s="59">
+      <c r="B12" s="60">
         <f>'Calc_Company'!$C$18</f>
         <v/>
       </c>
@@ -2219,8 +2222,8 @@
           <t>Retain fraction (1 − dist)</t>
         </is>
       </c>
-      <c r="B13" s="36">
-        <f>1-'Inputs'!$C$49</f>
+      <c r="B13" s="38">
+        <f>1-'Assumptions'!$C$49</f>
         <v/>
       </c>
     </row>
@@ -2230,89 +2233,89 @@
           <t>Debt at exit $m</t>
         </is>
       </c>
-      <c r="B14" s="56">
-        <f>'Inputs'!$C$50</f>
+      <c r="B14" s="57">
+        <f>'Assumptions'!$C$50</f>
         <v/>
       </c>
     </row>
     <row r="15"/>
     <row r="16"/>
     <row r="17">
-      <c r="B17" s="60" t="inlineStr">
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t>Price mult →</t>
         </is>
       </c>
-      <c r="C17" s="32" t="n">
+      <c r="C17" s="28" t="n">
         <v>0.7</v>
       </c>
-      <c r="D17" s="32" t="n">
+      <c r="D17" s="28" t="n">
         <v>0.85</v>
       </c>
-      <c r="E17" s="32" t="n">
+      <c r="E17" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="32" t="n">
+      <c r="F17" s="28" t="n">
         <v>1.15</v>
       </c>
-      <c r="G17" s="32" t="n">
+      <c r="G17" s="28" t="n">
         <v>1.3</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="60" t="inlineStr">
+      <c r="B18" s="61" t="inlineStr">
         <is>
           <t>Gross $m →</t>
         </is>
       </c>
-      <c r="C18" s="61">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*C17</f>
-        <v/>
-      </c>
-      <c r="D18" s="61">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*D17</f>
-        <v/>
-      </c>
-      <c r="E18" s="61">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*E17</f>
-        <v/>
-      </c>
-      <c r="F18" s="61">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*F17</f>
-        <v/>
-      </c>
-      <c r="G18" s="61">
-        <f>'Inputs'!$C$10*'Calc_Project_rNPV'!$M$11*G17</f>
+      <c r="C18" s="62">
+        <f>'Assumptions'!$C$10*'Calc_Project_rNPV'!$M$11*C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="62">
+        <f>'Assumptions'!$C$10*'Calc_Project_rNPV'!$M$11*D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="62">
+        <f>'Assumptions'!$C$10*'Calc_Project_rNPV'!$M$11*E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="62">
+        <f>'Assumptions'!$C$10*'Calc_Project_rNPV'!$M$11*F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="62">
+        <f>'Assumptions'!$C$10*'Calc_Project_rNPV'!$M$11*G17</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="62" t="inlineStr">
+      <c r="B19" s="63" t="inlineStr">
         <is>
           <t>DA gate ↓</t>
         </is>
       </c>
-      <c r="C19" s="62" t="inlineStr">
+      <c r="C19" s="63" t="inlineStr">
         <is>
           <t>IRR</t>
         </is>
       </c>
-      <c r="D19" s="62" t="inlineStr">
+      <c r="D19" s="63" t="inlineStr">
         <is>
           <t>IRR</t>
         </is>
       </c>
-      <c r="E19" s="62" t="inlineStr">
+      <c r="E19" s="63" t="inlineStr">
         <is>
           <t>IRR</t>
         </is>
       </c>
-      <c r="F19" s="62" t="inlineStr">
+      <c r="F19" s="63" t="inlineStr">
         <is>
           <t>IRR</t>
         </is>
       </c>
-      <c r="G19" s="62" t="inlineStr">
+      <c r="G19" s="63" t="inlineStr">
         <is>
           <t>IRR</t>
         </is>
@@ -2387,75 +2390,75 @@
       <c r="B20" s="25" t="n">
         <v>0.4</v>
       </c>
-      <c r="C20" s="36">
+      <c r="C20" s="38">
         <f>IFERROR((R20/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="38">
         <f>IFERROR((S20/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="E20" s="36">
+      <c r="E20" s="38">
         <f>IFERROR((T20/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="38">
         <f>IFERROR((U20/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="G20" s="36">
+      <c r="G20" s="38">
         <f>IFERROR((V20/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="H20" s="36">
+      <c r="H20" s="38">
         <f>$B20*$B$4</f>
         <v/>
       </c>
-      <c r="I20" s="49">
-        <f>IFERROR('Inputs'!$C$10/H20,0)</f>
-        <v/>
-      </c>
-      <c r="J20" s="50">
-        <f>'Inputs'!$C$10*'Inputs'!$C$21+(I20-'Inputs'!$C$10)*'Inputs'!$C$22*'Inputs'!$C$21</f>
-        <v/>
-      </c>
-      <c r="L20" s="44">
+      <c r="I20" s="51">
+        <f>IFERROR('Assumptions'!$C$10/H20,0)</f>
+        <v/>
+      </c>
+      <c r="J20" s="52">
+        <f>'Assumptions'!$C$21*('Assumptions'!$C$10+(I20-'Assumptions'!$C$10)*'Assumptions'!$C$22)</f>
+        <v/>
+      </c>
+      <c r="L20" s="46">
         <f>MAX(0,$B$6*($B$10*C$17-$B$11)*$H20*$B$12+MAX(0,C$18-$J20)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="M20" s="44">
+      <c r="M20" s="46">
         <f>MAX(0,$B$6*($B$10*D$17-$B$11)*$H20*$B$12+MAX(0,D$18-$J20)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="N20" s="44">
+      <c r="N20" s="46">
         <f>MAX(0,$B$6*($B$10*E$17-$B$11)*$H20*$B$12+MAX(0,E$18-$J20)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="O20" s="44">
+      <c r="O20" s="46">
         <f>MAX(0,$B$6*($B$10*F$17-$B$11)*$H20*$B$12+MAX(0,F$18-$J20)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="P20" s="44">
+      <c r="P20" s="46">
         <f>MAX(0,$B$6*($B$10*G$17-$B$11)*$H20*$B$12+MAX(0,G$18-$J20)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="R20" s="44">
+      <c r="R20" s="46">
         <f>MAX(MIN($B$7,L20),$B$5*L20)</f>
         <v/>
       </c>
-      <c r="S20" s="44">
+      <c r="S20" s="46">
         <f>MAX(MIN($B$7,M20),$B$5*M20)</f>
         <v/>
       </c>
-      <c r="T20" s="44">
+      <c r="T20" s="46">
         <f>MAX(MIN($B$7,N20),$B$5*N20)</f>
         <v/>
       </c>
-      <c r="U20" s="44">
+      <c r="U20" s="46">
         <f>MAX(MIN($B$7,O20),$B$5*O20)</f>
         <v/>
       </c>
-      <c r="V20" s="44">
+      <c r="V20" s="46">
         <f>MAX(MIN($B$7,P20),$B$5*P20)</f>
         <v/>
       </c>
@@ -2464,75 +2467,75 @@
       <c r="B21" s="25" t="n">
         <v>0.55</v>
       </c>
-      <c r="C21" s="36">
+      <c r="C21" s="38">
         <f>IFERROR((R21/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="D21" s="36">
+      <c r="D21" s="38">
         <f>IFERROR((S21/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="E21" s="36">
+      <c r="E21" s="38">
         <f>IFERROR((T21/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="38">
         <f>IFERROR((U21/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="G21" s="36">
+      <c r="G21" s="38">
         <f>IFERROR((V21/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="H21" s="36">
+      <c r="H21" s="38">
         <f>$B21*$B$4</f>
         <v/>
       </c>
-      <c r="I21" s="49">
-        <f>IFERROR('Inputs'!$C$10/H21,0)</f>
-        <v/>
-      </c>
-      <c r="J21" s="50">
-        <f>'Inputs'!$C$10*'Inputs'!$C$21+(I21-'Inputs'!$C$10)*'Inputs'!$C$22*'Inputs'!$C$21</f>
-        <v/>
-      </c>
-      <c r="L21" s="44">
+      <c r="I21" s="51">
+        <f>IFERROR('Assumptions'!$C$10/H21,0)</f>
+        <v/>
+      </c>
+      <c r="J21" s="52">
+        <f>'Assumptions'!$C$21*('Assumptions'!$C$10+(I21-'Assumptions'!$C$10)*'Assumptions'!$C$22)</f>
+        <v/>
+      </c>
+      <c r="L21" s="46">
         <f>MAX(0,$B$6*($B$10*C$17-$B$11)*$H21*$B$12+MAX(0,C$18-$J21)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="M21" s="44">
+      <c r="M21" s="46">
         <f>MAX(0,$B$6*($B$10*D$17-$B$11)*$H21*$B$12+MAX(0,D$18-$J21)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="N21" s="44">
+      <c r="N21" s="46">
         <f>MAX(0,$B$6*($B$10*E$17-$B$11)*$H21*$B$12+MAX(0,E$18-$J21)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="O21" s="44">
+      <c r="O21" s="46">
         <f>MAX(0,$B$6*($B$10*F$17-$B$11)*$H21*$B$12+MAX(0,F$18-$J21)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="P21" s="44">
+      <c r="P21" s="46">
         <f>MAX(0,$B$6*($B$10*G$17-$B$11)*$H21*$B$12+MAX(0,G$18-$J21)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="R21" s="44">
+      <c r="R21" s="46">
         <f>MAX(MIN($B$7,L21),$B$5*L21)</f>
         <v/>
       </c>
-      <c r="S21" s="44">
+      <c r="S21" s="46">
         <f>MAX(MIN($B$7,M21),$B$5*M21)</f>
         <v/>
       </c>
-      <c r="T21" s="44">
+      <c r="T21" s="46">
         <f>MAX(MIN($B$7,N21),$B$5*N21)</f>
         <v/>
       </c>
-      <c r="U21" s="44">
+      <c r="U21" s="46">
         <f>MAX(MIN($B$7,O21),$B$5*O21)</f>
         <v/>
       </c>
-      <c r="V21" s="44">
+      <c r="V21" s="46">
         <f>MAX(MIN($B$7,P21),$B$5*P21)</f>
         <v/>
       </c>
@@ -2541,75 +2544,75 @@
       <c r="B22" s="25" t="n">
         <v>0.65</v>
       </c>
-      <c r="C22" s="36">
+      <c r="C22" s="38">
         <f>IFERROR((R22/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="D22" s="36">
+      <c r="D22" s="38">
         <f>IFERROR((S22/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="E22" s="36">
+      <c r="E22" s="38">
         <f>IFERROR((T22/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="F22" s="36">
+      <c r="F22" s="38">
         <f>IFERROR((U22/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="G22" s="36">
+      <c r="G22" s="38">
         <f>IFERROR((V22/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="H22" s="36">
+      <c r="H22" s="38">
         <f>$B22*$B$4</f>
         <v/>
       </c>
-      <c r="I22" s="49">
-        <f>IFERROR('Inputs'!$C$10/H22,0)</f>
-        <v/>
-      </c>
-      <c r="J22" s="50">
-        <f>'Inputs'!$C$10*'Inputs'!$C$21+(I22-'Inputs'!$C$10)*'Inputs'!$C$22*'Inputs'!$C$21</f>
-        <v/>
-      </c>
-      <c r="L22" s="44">
+      <c r="I22" s="51">
+        <f>IFERROR('Assumptions'!$C$10/H22,0)</f>
+        <v/>
+      </c>
+      <c r="J22" s="52">
+        <f>'Assumptions'!$C$21*('Assumptions'!$C$10+(I22-'Assumptions'!$C$10)*'Assumptions'!$C$22)</f>
+        <v/>
+      </c>
+      <c r="L22" s="46">
         <f>MAX(0,$B$6*($B$10*C$17-$B$11)*$H22*$B$12+MAX(0,C$18-$J22)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="M22" s="44">
+      <c r="M22" s="46">
         <f>MAX(0,$B$6*($B$10*D$17-$B$11)*$H22*$B$12+MAX(0,D$18-$J22)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="N22" s="44">
+      <c r="N22" s="46">
         <f>MAX(0,$B$6*($B$10*E$17-$B$11)*$H22*$B$12+MAX(0,E$18-$J22)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="O22" s="44">
+      <c r="O22" s="46">
         <f>MAX(0,$B$6*($B$10*F$17-$B$11)*$H22*$B$12+MAX(0,F$18-$J22)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="P22" s="44">
+      <c r="P22" s="46">
         <f>MAX(0,$B$6*($B$10*G$17-$B$11)*$H22*$B$12+MAX(0,G$18-$J22)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="R22" s="44">
+      <c r="R22" s="46">
         <f>MAX(MIN($B$7,L22),$B$5*L22)</f>
         <v/>
       </c>
-      <c r="S22" s="44">
+      <c r="S22" s="46">
         <f>MAX(MIN($B$7,M22),$B$5*M22)</f>
         <v/>
       </c>
-      <c r="T22" s="44">
+      <c r="T22" s="46">
         <f>MAX(MIN($B$7,N22),$B$5*N22)</f>
         <v/>
       </c>
-      <c r="U22" s="44">
+      <c r="U22" s="46">
         <f>MAX(MIN($B$7,O22),$B$5*O22)</f>
         <v/>
       </c>
-      <c r="V22" s="44">
+      <c r="V22" s="46">
         <f>MAX(MIN($B$7,P22),$B$5*P22)</f>
         <v/>
       </c>
@@ -2618,75 +2621,75 @@
       <c r="B23" s="25" t="n">
         <v>0.8</v>
       </c>
-      <c r="C23" s="36">
+      <c r="C23" s="38">
         <f>IFERROR((R23/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="D23" s="36">
+      <c r="D23" s="38">
         <f>IFERROR((S23/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="E23" s="36">
+      <c r="E23" s="38">
         <f>IFERROR((T23/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="F23" s="36">
+      <c r="F23" s="38">
         <f>IFERROR((U23/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="G23" s="36">
+      <c r="G23" s="38">
         <f>IFERROR((V23/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="H23" s="36">
+      <c r="H23" s="38">
         <f>$B23*$B$4</f>
         <v/>
       </c>
-      <c r="I23" s="49">
-        <f>IFERROR('Inputs'!$C$10/H23,0)</f>
-        <v/>
-      </c>
-      <c r="J23" s="50">
-        <f>'Inputs'!$C$10*'Inputs'!$C$21+(I23-'Inputs'!$C$10)*'Inputs'!$C$22*'Inputs'!$C$21</f>
-        <v/>
-      </c>
-      <c r="L23" s="44">
+      <c r="I23" s="51">
+        <f>IFERROR('Assumptions'!$C$10/H23,0)</f>
+        <v/>
+      </c>
+      <c r="J23" s="52">
+        <f>'Assumptions'!$C$21*('Assumptions'!$C$10+(I23-'Assumptions'!$C$10)*'Assumptions'!$C$22)</f>
+        <v/>
+      </c>
+      <c r="L23" s="46">
         <f>MAX(0,$B$6*($B$10*C$17-$B$11)*$H23*$B$12+MAX(0,C$18-$J23)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="M23" s="44">
+      <c r="M23" s="46">
         <f>MAX(0,$B$6*($B$10*D$17-$B$11)*$H23*$B$12+MAX(0,D$18-$J23)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="N23" s="44">
+      <c r="N23" s="46">
         <f>MAX(0,$B$6*($B$10*E$17-$B$11)*$H23*$B$12+MAX(0,E$18-$J23)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="O23" s="44">
+      <c r="O23" s="46">
         <f>MAX(0,$B$6*($B$10*F$17-$B$11)*$H23*$B$12+MAX(0,F$18-$J23)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="P23" s="44">
+      <c r="P23" s="46">
         <f>MAX(0,$B$6*($B$10*G$17-$B$11)*$H23*$B$12+MAX(0,G$18-$J23)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="R23" s="44">
+      <c r="R23" s="46">
         <f>MAX(MIN($B$7,L23),$B$5*L23)</f>
         <v/>
       </c>
-      <c r="S23" s="44">
+      <c r="S23" s="46">
         <f>MAX(MIN($B$7,M23),$B$5*M23)</f>
         <v/>
       </c>
-      <c r="T23" s="44">
+      <c r="T23" s="46">
         <f>MAX(MIN($B$7,N23),$B$5*N23)</f>
         <v/>
       </c>
-      <c r="U23" s="44">
+      <c r="U23" s="46">
         <f>MAX(MIN($B$7,O23),$B$5*O23)</f>
         <v/>
       </c>
-      <c r="V23" s="44">
+      <c r="V23" s="46">
         <f>MAX(MIN($B$7,P23),$B$5*P23)</f>
         <v/>
       </c>
@@ -2695,75 +2698,75 @@
       <c r="B24" s="25" t="n">
         <v>0.95</v>
       </c>
-      <c r="C24" s="36">
+      <c r="C24" s="38">
         <f>IFERROR((R24/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="D24" s="36">
+      <c r="D24" s="38">
         <f>IFERROR((S24/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="E24" s="36">
+      <c r="E24" s="38">
         <f>IFERROR((T24/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="F24" s="36">
+      <c r="F24" s="38">
         <f>IFERROR((U24/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="G24" s="36">
+      <c r="G24" s="38">
         <f>IFERROR((V24/$B$8)^(1/$B$9)-1,-1)</f>
         <v/>
       </c>
-      <c r="H24" s="36">
+      <c r="H24" s="38">
         <f>$B24*$B$4</f>
         <v/>
       </c>
-      <c r="I24" s="49">
-        <f>IFERROR('Inputs'!$C$10/H24,0)</f>
-        <v/>
-      </c>
-      <c r="J24" s="50">
-        <f>'Inputs'!$C$10*'Inputs'!$C$21+(I24-'Inputs'!$C$10)*'Inputs'!$C$22*'Inputs'!$C$21</f>
-        <v/>
-      </c>
-      <c r="L24" s="44">
+      <c r="I24" s="51">
+        <f>IFERROR('Assumptions'!$C$10/H24,0)</f>
+        <v/>
+      </c>
+      <c r="J24" s="52">
+        <f>'Assumptions'!$C$21*('Assumptions'!$C$10+(I24-'Assumptions'!$C$10)*'Assumptions'!$C$22)</f>
+        <v/>
+      </c>
+      <c r="L24" s="46">
         <f>MAX(0,$B$6*($B$10*C$17-$B$11)*$H24*$B$12+MAX(0,C$18-$J24)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="M24" s="44">
+      <c r="M24" s="46">
         <f>MAX(0,$B$6*($B$10*D$17-$B$11)*$H24*$B$12+MAX(0,D$18-$J24)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="N24" s="44">
+      <c r="N24" s="46">
         <f>MAX(0,$B$6*($B$10*E$17-$B$11)*$H24*$B$12+MAX(0,E$18-$J24)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="O24" s="44">
+      <c r="O24" s="46">
         <f>MAX(0,$B$6*($B$10*F$17-$B$11)*$H24*$B$12+MAX(0,F$18-$J24)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="P24" s="44">
+      <c r="P24" s="46">
         <f>MAX(0,$B$6*($B$10*G$17-$B$11)*$H24*$B$12+MAX(0,G$18-$J24)*$B$13-$B$14)</f>
         <v/>
       </c>
-      <c r="R24" s="44">
+      <c r="R24" s="46">
         <f>MAX(MIN($B$7,L24),$B$5*L24)</f>
         <v/>
       </c>
-      <c r="S24" s="44">
+      <c r="S24" s="46">
         <f>MAX(MIN($B$7,M24),$B$5*M24)</f>
         <v/>
       </c>
-      <c r="T24" s="44">
+      <c r="T24" s="46">
         <f>MAX(MIN($B$7,N24),$B$5*N24)</f>
         <v/>
       </c>
-      <c r="U24" s="44">
+      <c r="U24" s="46">
         <f>MAX(MIN($B$7,O24),$B$5*O24)</f>
         <v/>
       </c>
-      <c r="V24" s="44">
+      <c r="V24" s="46">
         <f>MAX(MIN($B$7,P24),$B$5*P24)</f>
         <v/>
       </c>
@@ -2831,8 +2834,8 @@
           <t>Every gate probability ∈ [0,1]</t>
         </is>
       </c>
-      <c r="B4" s="38">
-        <f>IF(AND(MIN('Inputs'!$C$26:$C$28)&gt;=0,MAX('Inputs'!$C$26:$C$28)&lt;=1),"OK","ERROR")</f>
+      <c r="B4" s="40">
+        <f>IF(AND(MIN('Assumptions'!$C$26:$C$28)&gt;=0,MAX('Assumptions'!$C$26:$C$28)&lt;=1),"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -2847,7 +2850,7 @@
           <t>Flip success ≤ each gate</t>
         </is>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="40">
         <f>IF('Calc_Survival'!$C$7&lt;=MIN('Calc_Survival'!$B$4:$B$6)+0.000001,"OK","ERROR")</f>
         <v/>
       </c>
@@ -2863,8 +2866,8 @@
           <t>All MW positive</t>
         </is>
       </c>
-      <c r="B6" s="38">
-        <f>IF(MIN('Inputs'!$D$40:$D$45)&gt;0,"OK","ERROR")</f>
+      <c r="B6" s="40">
+        <f>IF(MIN('Assumptions'!$D$40:$D$45)&gt;0,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -2879,7 +2882,7 @@
           <t>All RTB sale values positive</t>
         </is>
       </c>
-      <c r="B7" s="38">
+      <c r="B7" s="40">
         <f>IF(MIN('Calc_Project_rNPV'!$G$4:$G$9)&gt;0,"OK","ERROR")</f>
         <v/>
       </c>
@@ -2895,8 +2898,8 @@
           <t>Dev cost positive</t>
         </is>
       </c>
-      <c r="B8" s="38">
-        <f>IF('Inputs'!$C$21&gt;0,"OK","ERROR")</f>
+      <c r="B8" s="40">
+        <f>IF('Assumptions'!$C$21&gt;0,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -2911,7 +2914,7 @@
           <t>Scenario switch ∈ {1,2,3}</t>
         </is>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="40">
         <f>IF(AND('Scenarios'!$B$2&gt;=1,'Scenarios'!$B$2&lt;=3),"OK","ERROR")</f>
         <v/>
       </c>
@@ -2927,7 +2930,7 @@
           <t>Scenario DA-gate monotonic</t>
         </is>
       </c>
-      <c r="B10" s="38">
+      <c r="B10" s="40">
         <f>IF(AND('Scenarios'!$B$5&lt;='Scenarios'!$C$5,'Scenarios'!$C$5&lt;='Scenarios'!$D$5),"OK","ERROR")</f>
         <v/>
       </c>
@@ -2943,8 +2946,8 @@
           <t>Post-money = pre-money + investment</t>
         </is>
       </c>
-      <c r="B11" s="38">
-        <f>IF(ABS('Returns'!$B$6-('Inputs'!$C$13+'Inputs'!$C$14))&lt;0.0001,"OK","ERROR")</f>
+      <c r="B11" s="40">
+        <f>IF(ABS('Returns'!$B$6-('Assumptions'!$C$13+'Assumptions'!$C$14))&lt;0.0001,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -2959,8 +2962,8 @@
           <t>Ownership = investment ÷ post-money</t>
         </is>
       </c>
-      <c r="B12" s="38">
-        <f>IF(ABS('Returns'!$B$7-'Inputs'!$C$14/'Returns'!$B$6)&lt;0.0001,"OK","ERROR")</f>
+      <c r="B12" s="40">
+        <f>IF(ABS('Returns'!$B$7-'Assumptions'!$C$14/'Returns'!$B$6)&lt;0.0001,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -2975,7 +2978,7 @@
           <t>Diluted ownership ≤ entry ownership</t>
         </is>
       </c>
-      <c r="B13" s="38">
+      <c r="B13" s="40">
         <f>IF('Returns'!$B$8&lt;='Returns'!$B$7+0.0001,"OK","ERROR")</f>
         <v/>
       </c>
@@ -2991,7 +2994,7 @@
           <t>Investor MOIC monotonic</t>
         </is>
       </c>
-      <c r="B14" s="38">
+      <c r="B14" s="40">
         <f>IF(AND('Returns'!$B$29&lt;='Returns'!$C$29,'Returns'!$C$29&lt;='Returns'!$D$29),"OK","ERROR")</f>
         <v/>
       </c>
@@ -3007,7 +3010,7 @@
           <t>Scenario weights sum to 100%</t>
         </is>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="40">
         <f>IF(ABS('Scenarios'!$E$13-1)&lt;0.001,"OK","ERROR")</f>
         <v/>
       </c>
@@ -3023,7 +3026,7 @@
           <t>First-Chicago IRR within scenario range</t>
         </is>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="40">
         <f>IF(AND(G16&gt;=E16-0.0001,G16&lt;=F16+0.0001),"OK","ERROR")</f>
         <v/>
       </c>
@@ -3032,15 +3035,15 @@
           <t>Weighting sanity (helpers E:G)</t>
         </is>
       </c>
-      <c r="E16" s="63">
+      <c r="E16" s="64">
         <f>MIN('Returns'!$B$30:$D$30)</f>
         <v/>
       </c>
-      <c r="F16" s="63">
+      <c r="F16" s="64">
         <f>MAX('Returns'!$B$30:$D$30)</f>
         <v/>
       </c>
-      <c r="G16" s="55">
+      <c r="G16" s="33">
         <f>'Returns'!$E$37</f>
         <v/>
       </c>
@@ -3051,7 +3054,7 @@
           <t>Our proceeds non-negative (all scenarios)</t>
         </is>
       </c>
-      <c r="B17" s="38">
+      <c r="B17" s="40">
         <f>IF(MIN('Returns'!$B$28:$D$28)&gt;=0,"OK","ERROR")</f>
         <v/>
       </c>
@@ -3067,7 +3070,7 @@
           <t>No error cells in key outputs</t>
         </is>
       </c>
-      <c r="B18" s="38">
+      <c r="B18" s="40">
         <f>IF(SUM(E18:G18)=0,"OK","ERROR")</f>
         <v/>
       </c>
@@ -3076,15 +3079,15 @@
           <t>#REF!/#DIV0! scan</t>
         </is>
       </c>
-      <c r="E18" s="38">
+      <c r="E18" s="40">
         <f>SUMPRODUCT(--ISERROR('Calc_Project_rNPV'!$M$4:$M$10))</f>
         <v/>
       </c>
-      <c r="F18" s="38">
+      <c r="F18" s="40">
         <f>SUMPRODUCT(--ISERROR('Returns'!$B$30:$D$30))</f>
         <v/>
       </c>
-      <c r="G18" s="38">
+      <c r="G18" s="40">
         <f>SUMPRODUCT(--ISERROR('Sensitivity'!$C$20:$G$24))</f>
         <v/>
       </c>
@@ -3095,7 +3098,7 @@
           <t>Cap table ties (ownership sums to 100%)</t>
         </is>
       </c>
-      <c r="B19" s="38">
+      <c r="B19" s="40">
         <f>IF(AND(ABS('Returns'!$B$53-1)&lt;0.001,ABS('Returns'!$C$53-1)&lt;0.001),"OK","ERROR")</f>
         <v/>
       </c>
@@ -3111,7 +3114,7 @@
           <t>Exit equity fully distributed (ours + others)</t>
         </is>
       </c>
-      <c r="B20" s="38">
+      <c r="B20" s="40">
         <f>IF(ABS('Returns'!$C$59-'Returns'!$C$56)&lt;0.001,"OK","ERROR")</f>
         <v/>
       </c>
@@ -3127,7 +3130,7 @@
           <t>No double-count (exit value ≤ realised + forward pipeline)</t>
         </is>
       </c>
-      <c r="B21" s="38">
+      <c r="B21" s="40">
         <f>IF('Returns'!$C$23&lt;='Returns'!$C$21+'Returns'!$C$22+0.000001,"OK","ERROR")</f>
         <v/>
       </c>
@@ -3143,8 +3146,8 @@
           <t>Provenance: unverified inputs flagged, not silently independent</t>
         </is>
       </c>
-      <c r="B22" s="38">
-        <f>IF(OR(AND('Inputs'!$C$57=1,'Inputs'!$C$58=1),'Inputs'!$C$59=1),"OK","ERROR")</f>
+      <c r="B22" s="40">
+        <f>IF(OR(AND('Assumptions'!$C$57=1,'Assumptions'!$C$58=1),'Assumptions'!$C$59=1),"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -3160,20 +3163,20 @@
           <t>MASTER CHECK</t>
         </is>
       </c>
-      <c r="B24" s="64">
+      <c r="B24" s="65">
         <f>IF(COUNTIF(B4:B22,"ERROR")=0,"OK","ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="25"/>
     <row r="26">
-      <c r="A26" s="65" t="inlineStr">
+      <c r="A26" s="66" t="inlineStr">
         <is>
           <t>PROVENANCE STATUS (advisory — not in master)</t>
         </is>
       </c>
-      <c r="B26" s="66">
-        <f>IF(AND('Inputs'!$C$57=1,'Inputs'!$C$58=1),"Verified","UNVERIFIED — verify RTB &amp; dev cost")</f>
+      <c r="B26" s="67">
+        <f>IF(AND('Assumptions'!$C$57=1,'Assumptions'!$C$58=1),"Verified","UNVERIFIED — verify inputs")</f>
         <v/>
       </c>
     </row>
@@ -3254,7 +3257,7 @@
           <t>Master check</t>
         </is>
       </c>
-      <c r="E4" s="67">
+      <c r="E4" s="68">
         <f>'Checks'!$B$24</f>
         <v/>
       </c>
@@ -3277,7 +3280,7 @@
           <t>Expected equity IRR</t>
         </is>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="36">
         <f>'Returns'!$E$37</f>
         <v/>
       </c>
@@ -3286,7 +3289,7 @@
           <t>Post-money valuation $m</t>
         </is>
       </c>
-      <c r="E7" s="51">
+      <c r="E7" s="53">
         <f>'Returns'!$B$6</f>
         <v/>
       </c>
@@ -3297,7 +3300,7 @@
           <t>Expected MOIC</t>
         </is>
       </c>
-      <c r="B8" s="68">
+      <c r="B8" s="69">
         <f>'Returns'!$E$36</f>
         <v/>
       </c>
@@ -3306,7 +3309,7 @@
           <t>Ownership at entry</t>
         </is>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="37">
         <f>'Returns'!$B$7</f>
         <v/>
       </c>
@@ -3317,7 +3320,7 @@
           <t>Ownership at exit (diluted)</t>
         </is>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="37">
         <f>'Returns'!$B$8</f>
         <v/>
       </c>
@@ -3328,8 +3331,8 @@
           <t>Liquidation preference (x)</t>
         </is>
       </c>
-      <c r="E10" s="68">
-        <f>'Inputs'!$C$17</f>
+      <c r="E10" s="69">
+        <f>'Assumptions'!$C$17</f>
         <v/>
       </c>
     </row>
@@ -3339,8 +3342,8 @@
           <t>Exit year</t>
         </is>
       </c>
-      <c r="E11" s="40">
-        <f>'Inputs'!$C$18</f>
+      <c r="E11" s="42">
+        <f>'Assumptions'!$C$18</f>
         <v/>
       </c>
     </row>
@@ -3372,13 +3375,13 @@
           <t>Equity IRR</t>
         </is>
       </c>
-      <c r="D14" s="69" t="inlineStr">
+      <c r="D14" s="70" t="inlineStr">
         <is>
           <t>Programme capital $m</t>
         </is>
       </c>
-      <c r="E14" s="51">
-        <f>'Inputs'!$C$9</f>
+      <c r="E14" s="53">
+        <f>'Assumptions'!$C$9</f>
         <v/>
       </c>
     </row>
@@ -3388,21 +3391,21 @@
           <t>Conservative</t>
         </is>
       </c>
-      <c r="B15" s="36">
-        <f>'Scenarios'!$B$5*'Inputs'!$C$27*'Inputs'!$C$28</f>
-        <v/>
-      </c>
-      <c r="C15" s="35">
+      <c r="B15" s="38">
+        <f>'Scenarios'!$B$5*'Assumptions'!$C$27*'Assumptions'!$C$28</f>
+        <v/>
+      </c>
+      <c r="C15" s="37">
         <f>'Returns'!$B$30</f>
         <v/>
       </c>
-      <c r="D15" s="70" t="inlineStr">
+      <c r="D15" s="71" t="inlineStr">
         <is>
           <t>Projects target</t>
         </is>
       </c>
-      <c r="E15" s="40">
-        <f>'Inputs'!$C$10</f>
+      <c r="E15" s="42">
+        <f>'Assumptions'!$C$10</f>
         <v/>
       </c>
     </row>
@@ -3412,20 +3415,20 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="B16" s="36">
-        <f>'Scenarios'!$C$5*'Inputs'!$C$27*'Inputs'!$C$28</f>
-        <v/>
-      </c>
-      <c r="C16" s="35">
+      <c r="B16" s="38">
+        <f>'Scenarios'!$C$5*'Assumptions'!$C$27*'Assumptions'!$C$28</f>
+        <v/>
+      </c>
+      <c r="C16" s="37">
         <f>'Returns'!$C$30</f>
         <v/>
       </c>
-      <c r="D16" s="70" t="inlineStr">
+      <c r="D16" s="71" t="inlineStr">
         <is>
           <t>Manager headline DA gate (Base)</t>
         </is>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="37">
         <f>'Scenarios'!$C$5</f>
         <v/>
       </c>
@@ -3436,20 +3439,20 @@
           <t>Ideal</t>
         </is>
       </c>
-      <c r="B17" s="36">
-        <f>'Scenarios'!$D$5*'Inputs'!$C$27*'Inputs'!$C$28</f>
-        <v/>
-      </c>
-      <c r="C17" s="35">
+      <c r="B17" s="38">
+        <f>'Scenarios'!$D$5*'Assumptions'!$C$27*'Assumptions'!$C$28</f>
+        <v/>
+      </c>
+      <c r="C17" s="37">
         <f>'Returns'!$D$30</f>
         <v/>
       </c>
-      <c r="D17" s="70" t="inlineStr">
+      <c r="D17" s="71" t="inlineStr">
         <is>
           <t>True flip success (Base, DAxconnxsale)</t>
         </is>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="37">
         <f>'Calc_Survival'!$C$13</f>
         <v/>
       </c>
@@ -3460,7 +3463,7 @@
           <t>Independent flip success (benchmark)</t>
         </is>
       </c>
-      <c r="E18" s="35">
+      <c r="E18" s="37">
         <f>'Calc_Survival'!$C$10</f>
         <v/>
       </c>
@@ -4010,7 +4013,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Inputs</t>
+          <t>Assumptions</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -4366,7 +4369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4382,7 +4385,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>INPUTS — all model assumptions (blue = input cell)</t>
+          <t>ASSUMPTIONS — the single junction; every driver flows from here (blue = input cell)</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
@@ -4510,7 +4513,7 @@
         </is>
       </c>
       <c r="C7" s="18">
-        <f>'Inputs'!$C$5+'Inputs'!$C$6</f>
+        <f>'Assumptions'!$C$5+'Assumptions'!$C$6</f>
         <v/>
       </c>
       <c r="D7" s="15" t="inlineStr">
@@ -5652,6 +5655,99 @@
         <is>
           <t>RTB $/MW and dev cost are the manager's UNVERIFIED claims (Proposed) — verify against a primary source (comparable RTB sales; bottom-up costs) and set the flag to 1 before treating the rNPV as independent.</t>
         </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Scenario driver values (by case) — single source; the Scenarios tab links here</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="inlineStr">
+        <is>
+          <t>Development-approval rate (DA gate — 40/65/80%)</t>
+        </is>
+      </c>
+      <c r="B64" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C64" s="25" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D64" s="25" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="inlineStr">
+        <is>
+          <t>RTB price multiplier</t>
+        </is>
+      </c>
+      <c r="B65" s="28" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C65" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="28" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="15" t="inlineStr">
+        <is>
+          <t>Dev cost multiplier</t>
+        </is>
+      </c>
+      <c r="B66" s="28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C66" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="28" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="inlineStr">
+        <is>
+          <t>First-Chicago weight (by case)</t>
+        </is>
+      </c>
+      <c r="B67" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D67" s="25" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -5707,16 +5803,16 @@
           <t>Period number</t>
         </is>
       </c>
-      <c r="B3" s="28" t="n">
+      <c r="B3" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="28" t="n">
+      <c r="C3" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="28" t="n">
+      <c r="D3" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="28" t="n">
+      <c r="E3" s="29" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5726,19 +5822,19 @@
           <t>Year</t>
         </is>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="30">
         <f>$B$2+B3</f>
         <v/>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="30">
         <f>$B$2+C3</f>
         <v/>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <f>$B$2+D3</f>
         <v/>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <f>$B$2+E3</f>
         <v/>
       </c>
@@ -5749,19 +5845,19 @@
           <t>Discount factor @ live discount</t>
         </is>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^B3,0)</f>
         <v/>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^C3,0)</f>
         <v/>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^D3,0)</f>
         <v/>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^E3,0)</f>
         <v/>
       </c>
@@ -5809,7 +5905,7 @@
           <t>Scenario switch  (1=Conservative 2=Base 3=Ideal)</t>
         </is>
       </c>
-      <c r="B2" s="31" t="n">
+      <c r="B2" s="32" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5857,14 +5953,17 @@
           <t>Development-approval rate (DA gate — the 40/65/80%)</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C5" s="25" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="D5" s="25" t="n">
-        <v>0.8</v>
+      <c r="B5" s="33">
+        <f>'Assumptions'!$B$64</f>
+        <v/>
+      </c>
+      <c r="C5" s="33">
+        <f>'Assumptions'!$C$64</f>
+        <v/>
+      </c>
+      <c r="D5" s="33">
+        <f>'Assumptions'!$D$64</f>
+        <v/>
       </c>
       <c r="E5" s="18">
         <f>CHOOSE('Scenarios'!$B$2,B5,C5,D5)</f>
@@ -5877,16 +5976,19 @@
           <t>RTB price multiplier</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="C6" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="32" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E6" s="33">
+      <c r="B6" s="34">
+        <f>'Assumptions'!$B$65</f>
+        <v/>
+      </c>
+      <c r="C6" s="34">
+        <f>'Assumptions'!$C$65</f>
+        <v/>
+      </c>
+      <c r="D6" s="34">
+        <f>'Assumptions'!$D$65</f>
+        <v/>
+      </c>
+      <c r="E6" s="35">
         <f>CHOOSE('Scenarios'!$B$2,B6,C6,D6)</f>
         <v/>
       </c>
@@ -5897,16 +5999,19 @@
           <t>Dev cost multiplier</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="C7" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="32" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E7" s="33">
+      <c r="B7" s="34">
+        <f>'Assumptions'!$B$66</f>
+        <v/>
+      </c>
+      <c r="C7" s="34">
+        <f>'Assumptions'!$C$66</f>
+        <v/>
+      </c>
+      <c r="D7" s="34">
+        <f>'Assumptions'!$D$66</f>
+        <v/>
+      </c>
+      <c r="E7" s="35">
         <f>CHOOSE('Scenarios'!$B$2,B7,C7,D7)</f>
         <v/>
       </c>
@@ -5918,8 +6023,8 @@
           <t>Live discount rate (= base; scenarios don't move it)</t>
         </is>
       </c>
-      <c r="E9" s="34">
-        <f>'Inputs'!$C$7</f>
+      <c r="E9" s="36">
+        <f>'Assumptions'!$C$7</f>
         <v/>
       </c>
     </row>
@@ -5960,14 +6065,17 @@
           <t>Weight</t>
         </is>
       </c>
-      <c r="B13" s="25" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C13" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D13" s="25" t="n">
-        <v>0.2</v>
+      <c r="B13" s="33">
+        <f>'Assumptions'!$B$67</f>
+        <v/>
+      </c>
+      <c r="C13" s="33">
+        <f>'Assumptions'!$C$67</f>
+        <v/>
+      </c>
+      <c r="D13" s="33">
+        <f>'Assumptions'!$D$67</f>
+        <v/>
       </c>
       <c r="E13" s="18">
         <f>SUM(B13:D13)</f>
@@ -5978,7 +6086,7 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>The 40/65/80% are the DEVELOPMENT-APPROVAL gate ONLY (the manager's deck). True flip success = development approval x grid connection x sale — far below 65% (see Calc_Survival). The switch moves ONLY the DA gate; connection and sale are fixed public benchmarks. Scenarios are the analyst's to OWN.</t>
+          <t>The 40/65/80% are the DEVELOPMENT-APPROVAL gate ONLY (the manager's deck). True flip success = development approval x grid connection x sale — far below 65% (see Calc_Survival). The switch moves ONLY the DA gate; connection and sale are fixed public benchmarks. Scenarios are the analyst's to OWN. The driver VALUES live on the Assumptions tab (the single source); this tab links to them and holds only the switch + live case.</t>
         </is>
       </c>
     </row>
@@ -6047,11 +6155,11 @@
           <t>Development approval (live scenario DA gate)</t>
         </is>
       </c>
-      <c r="B4" s="35">
+      <c r="B4" s="37">
         <f>'Scenarios'!$E$5</f>
         <v/>
       </c>
-      <c r="C4" s="36">
+      <c r="C4" s="38">
         <f>B4</f>
         <v/>
       </c>
@@ -6062,11 +6170,11 @@
           <t>Grid connection — RTB rights (agreement + GPS)</t>
         </is>
       </c>
-      <c r="B5" s="35">
-        <f>'Inputs'!$C$27</f>
-        <v/>
-      </c>
-      <c r="C5" s="36">
+      <c r="B5" s="37">
+        <f>'Assumptions'!$C$27</f>
+        <v/>
+      </c>
+      <c r="C5" s="38">
         <f>C4*B5</f>
         <v/>
       </c>
@@ -6077,11 +6185,11 @@
           <t>Reach sale (flip exit)</t>
         </is>
       </c>
-      <c r="B6" s="35">
-        <f>'Inputs'!$C$28</f>
-        <v/>
-      </c>
-      <c r="C6" s="36">
+      <c r="B6" s="37">
+        <f>'Assumptions'!$C$28</f>
+        <v/>
+      </c>
+      <c r="C6" s="38">
         <f>C5*B6</f>
         <v/>
       </c>
@@ -6092,7 +6200,7 @@
           <t>LIVE flip success (DA x connection x sale)</t>
         </is>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="39">
         <f>C6</f>
         <v/>
       </c>
@@ -6104,8 +6212,8 @@
           <t>Public-benchmark development approval</t>
         </is>
       </c>
-      <c r="C9" s="35">
-        <f>'Inputs'!$C$26</f>
+      <c r="C9" s="37">
+        <f>'Assumptions'!$C$26</f>
         <v/>
       </c>
     </row>
@@ -6116,7 +6224,7 @@
         </is>
       </c>
       <c r="C10" s="18">
-        <f>C9*'Inputs'!$C$27*'Inputs'!$C$28</f>
+        <f>C9*'Assumptions'!$C$27*'Assumptions'!$C$28</f>
         <v/>
       </c>
     </row>
@@ -6127,7 +6235,7 @@
           <t>Manager's headline DA rate (Base — the '65%')</t>
         </is>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="37">
         <f>'Scenarios'!$C$5</f>
         <v/>
       </c>
@@ -6139,12 +6247,12 @@
         </is>
       </c>
       <c r="C13" s="18">
-        <f>'Scenarios'!$C$5*'Inputs'!$C$27*'Inputs'!$C$28</f>
+        <f>'Scenarios'!$C$5*'Assumptions'!$C$27*'Assumptions'!$C$28</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="C14" s="38">
+      <c r="C14" s="40">
         <f>IF(C13&lt;C12,"FLAG: 65% is the DA gate only","ok")</f>
         <v/>
       </c>
@@ -6298,348 +6406,348 @@
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <f>'Inputs'!$A$40</f>
-        <v/>
-      </c>
-      <c r="B4" s="39">
-        <f>'Inputs'!$B$40</f>
-        <v/>
-      </c>
-      <c r="C4" s="40">
-        <f>'Inputs'!$D$40</f>
-        <v/>
-      </c>
-      <c r="D4" s="41">
-        <f>'Inputs'!$G$40</f>
-        <v/>
-      </c>
-      <c r="E4" s="42">
-        <f>IFERROR(INDEX('Inputs'!$C$30:$C$32,MATCH(B4,'Inputs'!$A$30:$A$32,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F4" s="43">
+        <f>'Assumptions'!$A$40</f>
+        <v/>
+      </c>
+      <c r="B4" s="41">
+        <f>'Assumptions'!$B$40</f>
+        <v/>
+      </c>
+      <c r="C4" s="42">
+        <f>'Assumptions'!$D$40</f>
+        <v/>
+      </c>
+      <c r="D4" s="43">
+        <f>'Assumptions'!$G$40</f>
+        <v/>
+      </c>
+      <c r="E4" s="44">
+        <f>IFERROR(INDEX('Assumptions'!$C$30:$C$32,MATCH(B4,'Assumptions'!$A$30:$A$32,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F4" s="45">
         <f>'Scenarios'!$E$6</f>
         <v/>
       </c>
-      <c r="G4" s="44">
+      <c r="G4" s="46">
         <f>C4*E4*F4</f>
         <v/>
       </c>
-      <c r="H4" s="44">
-        <f>'Inputs'!$C$21*'Scenarios'!$E$7</f>
-        <v/>
-      </c>
-      <c r="I4" s="44">
+      <c r="H4" s="46">
+        <f>'Assumptions'!$C$21*'Scenarios'!$E$7</f>
+        <v/>
+      </c>
+      <c r="I4" s="46">
         <f>G4-H4</f>
         <v/>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="37">
         <f>'Calc_Survival'!$C$7</f>
         <v/>
       </c>
-      <c r="K4" s="44">
+      <c r="K4" s="46">
         <f>I4*J4</f>
         <v/>
       </c>
-      <c r="L4" s="45">
+      <c r="L4" s="47">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^D4,0)</f>
         <v/>
       </c>
-      <c r="M4" s="44">
+      <c r="M4" s="46">
         <f>K4*L4</f>
         <v/>
       </c>
-      <c r="N4" s="44">
+      <c r="N4" s="46">
         <f>C4*E4</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <f>'Inputs'!$A$41</f>
-        <v/>
-      </c>
-      <c r="B5" s="39">
-        <f>'Inputs'!$B$41</f>
-        <v/>
-      </c>
-      <c r="C5" s="40">
-        <f>'Inputs'!$D$41</f>
-        <v/>
-      </c>
-      <c r="D5" s="41">
-        <f>'Inputs'!$G$41</f>
-        <v/>
-      </c>
-      <c r="E5" s="42">
-        <f>IFERROR(INDEX('Inputs'!$C$30:$C$32,MATCH(B5,'Inputs'!$A$30:$A$32,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F5" s="43">
+        <f>'Assumptions'!$A$41</f>
+        <v/>
+      </c>
+      <c r="B5" s="41">
+        <f>'Assumptions'!$B$41</f>
+        <v/>
+      </c>
+      <c r="C5" s="42">
+        <f>'Assumptions'!$D$41</f>
+        <v/>
+      </c>
+      <c r="D5" s="43">
+        <f>'Assumptions'!$G$41</f>
+        <v/>
+      </c>
+      <c r="E5" s="44">
+        <f>IFERROR(INDEX('Assumptions'!$C$30:$C$32,MATCH(B5,'Assumptions'!$A$30:$A$32,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F5" s="45">
         <f>'Scenarios'!$E$6</f>
         <v/>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="46">
         <f>C5*E5*F5</f>
         <v/>
       </c>
-      <c r="H5" s="44">
-        <f>'Inputs'!$C$21*'Scenarios'!$E$7</f>
-        <v/>
-      </c>
-      <c r="I5" s="44">
+      <c r="H5" s="46">
+        <f>'Assumptions'!$C$21*'Scenarios'!$E$7</f>
+        <v/>
+      </c>
+      <c r="I5" s="46">
         <f>G5-H5</f>
         <v/>
       </c>
-      <c r="J5" s="35">
+      <c r="J5" s="37">
         <f>'Calc_Survival'!$C$7</f>
         <v/>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="46">
         <f>I5*J5</f>
         <v/>
       </c>
-      <c r="L5" s="45">
+      <c r="L5" s="47">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^D5,0)</f>
         <v/>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="46">
         <f>K5*L5</f>
         <v/>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="46">
         <f>C5*E5</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <f>'Inputs'!$A$42</f>
-        <v/>
-      </c>
-      <c r="B6" s="39">
-        <f>'Inputs'!$B$42</f>
-        <v/>
-      </c>
-      <c r="C6" s="40">
-        <f>'Inputs'!$D$42</f>
-        <v/>
-      </c>
-      <c r="D6" s="41">
-        <f>'Inputs'!$G$42</f>
-        <v/>
-      </c>
-      <c r="E6" s="42">
-        <f>IFERROR(INDEX('Inputs'!$C$30:$C$32,MATCH(B6,'Inputs'!$A$30:$A$32,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F6" s="43">
+        <f>'Assumptions'!$A$42</f>
+        <v/>
+      </c>
+      <c r="B6" s="41">
+        <f>'Assumptions'!$B$42</f>
+        <v/>
+      </c>
+      <c r="C6" s="42">
+        <f>'Assumptions'!$D$42</f>
+        <v/>
+      </c>
+      <c r="D6" s="43">
+        <f>'Assumptions'!$G$42</f>
+        <v/>
+      </c>
+      <c r="E6" s="44">
+        <f>IFERROR(INDEX('Assumptions'!$C$30:$C$32,MATCH(B6,'Assumptions'!$A$30:$A$32,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F6" s="45">
         <f>'Scenarios'!$E$6</f>
         <v/>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="46">
         <f>C6*E6*F6</f>
         <v/>
       </c>
-      <c r="H6" s="44">
-        <f>'Inputs'!$C$21*'Scenarios'!$E$7</f>
-        <v/>
-      </c>
-      <c r="I6" s="44">
+      <c r="H6" s="46">
+        <f>'Assumptions'!$C$21*'Scenarios'!$E$7</f>
+        <v/>
+      </c>
+      <c r="I6" s="46">
         <f>G6-H6</f>
         <v/>
       </c>
-      <c r="J6" s="35">
+      <c r="J6" s="37">
         <f>'Calc_Survival'!$C$7</f>
         <v/>
       </c>
-      <c r="K6" s="44">
+      <c r="K6" s="46">
         <f>I6*J6</f>
         <v/>
       </c>
-      <c r="L6" s="45">
+      <c r="L6" s="47">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^D6,0)</f>
         <v/>
       </c>
-      <c r="M6" s="44">
+      <c r="M6" s="46">
         <f>K6*L6</f>
         <v/>
       </c>
-      <c r="N6" s="44">
+      <c r="N6" s="46">
         <f>C6*E6</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <f>'Inputs'!$A$43</f>
-        <v/>
-      </c>
-      <c r="B7" s="39">
-        <f>'Inputs'!$B$43</f>
-        <v/>
-      </c>
-      <c r="C7" s="40">
-        <f>'Inputs'!$D$43</f>
-        <v/>
-      </c>
-      <c r="D7" s="41">
-        <f>'Inputs'!$G$43</f>
-        <v/>
-      </c>
-      <c r="E7" s="42">
-        <f>IFERROR(INDEX('Inputs'!$C$30:$C$32,MATCH(B7,'Inputs'!$A$30:$A$32,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F7" s="43">
+        <f>'Assumptions'!$A$43</f>
+        <v/>
+      </c>
+      <c r="B7" s="41">
+        <f>'Assumptions'!$B$43</f>
+        <v/>
+      </c>
+      <c r="C7" s="42">
+        <f>'Assumptions'!$D$43</f>
+        <v/>
+      </c>
+      <c r="D7" s="43">
+        <f>'Assumptions'!$G$43</f>
+        <v/>
+      </c>
+      <c r="E7" s="44">
+        <f>IFERROR(INDEX('Assumptions'!$C$30:$C$32,MATCH(B7,'Assumptions'!$A$30:$A$32,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F7" s="45">
         <f>'Scenarios'!$E$6</f>
         <v/>
       </c>
-      <c r="G7" s="44">
+      <c r="G7" s="46">
         <f>C7*E7*F7</f>
         <v/>
       </c>
-      <c r="H7" s="44">
-        <f>'Inputs'!$C$21*'Scenarios'!$E$7</f>
-        <v/>
-      </c>
-      <c r="I7" s="44">
+      <c r="H7" s="46">
+        <f>'Assumptions'!$C$21*'Scenarios'!$E$7</f>
+        <v/>
+      </c>
+      <c r="I7" s="46">
         <f>G7-H7</f>
         <v/>
       </c>
-      <c r="J7" s="35">
+      <c r="J7" s="37">
         <f>'Calc_Survival'!$C$7</f>
         <v/>
       </c>
-      <c r="K7" s="44">
+      <c r="K7" s="46">
         <f>I7*J7</f>
         <v/>
       </c>
-      <c r="L7" s="45">
+      <c r="L7" s="47">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^D7,0)</f>
         <v/>
       </c>
-      <c r="M7" s="44">
+      <c r="M7" s="46">
         <f>K7*L7</f>
         <v/>
       </c>
-      <c r="N7" s="44">
+      <c r="N7" s="46">
         <f>C7*E7</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <f>'Inputs'!$A$44</f>
-        <v/>
-      </c>
-      <c r="B8" s="39">
-        <f>'Inputs'!$B$44</f>
-        <v/>
-      </c>
-      <c r="C8" s="40">
-        <f>'Inputs'!$D$44</f>
-        <v/>
-      </c>
-      <c r="D8" s="41">
-        <f>'Inputs'!$G$44</f>
-        <v/>
-      </c>
-      <c r="E8" s="42">
-        <f>IFERROR(INDEX('Inputs'!$C$30:$C$32,MATCH(B8,'Inputs'!$A$30:$A$32,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F8" s="43">
+        <f>'Assumptions'!$A$44</f>
+        <v/>
+      </c>
+      <c r="B8" s="41">
+        <f>'Assumptions'!$B$44</f>
+        <v/>
+      </c>
+      <c r="C8" s="42">
+        <f>'Assumptions'!$D$44</f>
+        <v/>
+      </c>
+      <c r="D8" s="43">
+        <f>'Assumptions'!$G$44</f>
+        <v/>
+      </c>
+      <c r="E8" s="44">
+        <f>IFERROR(INDEX('Assumptions'!$C$30:$C$32,MATCH(B8,'Assumptions'!$A$30:$A$32,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="45">
         <f>'Scenarios'!$E$6</f>
         <v/>
       </c>
-      <c r="G8" s="44">
+      <c r="G8" s="46">
         <f>C8*E8*F8</f>
         <v/>
       </c>
-      <c r="H8" s="44">
-        <f>'Inputs'!$C$21*'Scenarios'!$E$7</f>
-        <v/>
-      </c>
-      <c r="I8" s="44">
+      <c r="H8" s="46">
+        <f>'Assumptions'!$C$21*'Scenarios'!$E$7</f>
+        <v/>
+      </c>
+      <c r="I8" s="46">
         <f>G8-H8</f>
         <v/>
       </c>
-      <c r="J8" s="35">
+      <c r="J8" s="37">
         <f>'Calc_Survival'!$C$7</f>
         <v/>
       </c>
-      <c r="K8" s="44">
+      <c r="K8" s="46">
         <f>I8*J8</f>
         <v/>
       </c>
-      <c r="L8" s="45">
+      <c r="L8" s="47">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^D8,0)</f>
         <v/>
       </c>
-      <c r="M8" s="44">
+      <c r="M8" s="46">
         <f>K8*L8</f>
         <v/>
       </c>
-      <c r="N8" s="44">
+      <c r="N8" s="46">
         <f>C8*E8</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <f>'Inputs'!$A$45</f>
-        <v/>
-      </c>
-      <c r="B9" s="39">
-        <f>'Inputs'!$B$45</f>
-        <v/>
-      </c>
-      <c r="C9" s="40">
-        <f>'Inputs'!$D$45</f>
-        <v/>
-      </c>
-      <c r="D9" s="41">
-        <f>'Inputs'!$G$45</f>
-        <v/>
-      </c>
-      <c r="E9" s="42">
-        <f>IFERROR(INDEX('Inputs'!$C$30:$C$32,MATCH(B9,'Inputs'!$A$30:$A$32,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F9" s="43">
+        <f>'Assumptions'!$A$45</f>
+        <v/>
+      </c>
+      <c r="B9" s="41">
+        <f>'Assumptions'!$B$45</f>
+        <v/>
+      </c>
+      <c r="C9" s="42">
+        <f>'Assumptions'!$D$45</f>
+        <v/>
+      </c>
+      <c r="D9" s="43">
+        <f>'Assumptions'!$G$45</f>
+        <v/>
+      </c>
+      <c r="E9" s="44">
+        <f>IFERROR(INDEX('Assumptions'!$C$30:$C$32,MATCH(B9,'Assumptions'!$A$30:$A$32,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F9" s="45">
         <f>'Scenarios'!$E$6</f>
         <v/>
       </c>
-      <c r="G9" s="44">
+      <c r="G9" s="46">
         <f>C9*E9*F9</f>
         <v/>
       </c>
-      <c r="H9" s="44">
-        <f>'Inputs'!$C$21*'Scenarios'!$E$7</f>
-        <v/>
-      </c>
-      <c r="I9" s="44">
+      <c r="H9" s="46">
+        <f>'Assumptions'!$C$21*'Scenarios'!$E$7</f>
+        <v/>
+      </c>
+      <c r="I9" s="46">
         <f>G9-H9</f>
         <v/>
       </c>
-      <c r="J9" s="35">
+      <c r="J9" s="37">
         <f>'Calc_Survival'!$C$7</f>
         <v/>
       </c>
-      <c r="K9" s="44">
+      <c r="K9" s="46">
         <f>I9*J9</f>
         <v/>
       </c>
-      <c r="L9" s="45">
+      <c r="L9" s="47">
         <f>IFERROR(1/(1+'Scenarios'!$E$9)^D9,0)</f>
         <v/>
       </c>
-      <c r="M9" s="44">
+      <c r="M9" s="46">
         <f>K9*L9</f>
         <v/>
       </c>
-      <c r="N9" s="44">
+      <c r="N9" s="46">
         <f>C9*E9</f>
         <v/>
       </c>
@@ -6650,19 +6758,19 @@
           <t>Pipeline total (representative)</t>
         </is>
       </c>
-      <c r="C10" s="46">
+      <c r="C10" s="48">
         <f>SUM(C4:C9)</f>
         <v/>
       </c>
-      <c r="G10" s="47">
+      <c r="G10" s="49">
         <f>SUM(G4:G9)</f>
         <v/>
       </c>
-      <c r="H10" s="47">
+      <c r="H10" s="49">
         <f>SUM(H4:H9)</f>
         <v/>
       </c>
-      <c r="M10" s="47">
+      <c r="M10" s="49">
         <f>SUM(M4:M9)</f>
         <v/>
       </c>
@@ -6673,7 +6781,7 @@
           <t>Blended RTB sale per project (@1x)</t>
         </is>
       </c>
-      <c r="M11" s="48">
+      <c r="M11" s="50">
         <f>AVERAGE('Calc_Project_rNPV'!$N$4:$N$9)</f>
         <v/>
       </c>
@@ -6737,7 +6845,7 @@
           <t>Live flip success (DA × conn × sale)</t>
         </is>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="37">
         <f>'Calc_Survival'!$C$7</f>
         <v/>
       </c>
@@ -6748,8 +6856,8 @@
           <t>Projects target (delivered &amp; sold)</t>
         </is>
       </c>
-      <c r="C6" s="40">
-        <f>'Inputs'!$C$10</f>
+      <c r="C6" s="42">
+        <f>'Assumptions'!$C$10</f>
         <v/>
       </c>
     </row>
@@ -6759,7 +6867,7 @@
           <t>Projects started (funnel)</t>
         </is>
       </c>
-      <c r="C7" s="49">
+      <c r="C7" s="51">
         <f>IFERROR(C6/C5,0)</f>
         <v/>
       </c>
@@ -6770,7 +6878,7 @@
           <t>Projects failed (dropouts)</t>
         </is>
       </c>
-      <c r="C8" s="49">
+      <c r="C8" s="51">
         <f>C7-C6</f>
         <v/>
       </c>
@@ -6781,8 +6889,8 @@
           <t>Dev cost per project (live)</t>
         </is>
       </c>
-      <c r="C9" s="44">
-        <f>'Inputs'!$C$21*'Scenarios'!$E$7</f>
+      <c r="C9" s="46">
+        <f>'Assumptions'!$C$21*'Scenarios'!$E$7</f>
         <v/>
       </c>
     </row>
@@ -6792,8 +6900,8 @@
           <t>Total development cost</t>
         </is>
       </c>
-      <c r="C10" s="50">
-        <f>C6*C9+C8*'Inputs'!$C$22*C9</f>
+      <c r="C10" s="52">
+        <f>C6*C9+C8*'Assumptions'!$C$22*C9</f>
         <v/>
       </c>
     </row>
@@ -6810,7 +6918,7 @@
           <t>Blended RTB sale per project (live)</t>
         </is>
       </c>
-      <c r="C12" s="44">
+      <c r="C12" s="46">
         <f>'Calc_Project_rNPV'!$M$11*'Scenarios'!$E$6</f>
         <v/>
       </c>
@@ -6821,7 +6929,7 @@
           <t>Gross proceeds</t>
         </is>
       </c>
-      <c r="C13" s="50">
+      <c r="C13" s="52">
         <f>C6*C12</f>
         <v/>
       </c>
@@ -6832,7 +6940,7 @@
           <t>Realised net programme profit (gross − total dev cost)</t>
         </is>
       </c>
-      <c r="C14" s="50">
+      <c r="C14" s="52">
         <f>C13-C10</f>
         <v/>
       </c>
@@ -6843,8 +6951,8 @@
           <t>Forward run-rate annual dev profit (= realised ÷ term)</t>
         </is>
       </c>
-      <c r="C15" s="44">
-        <f>IFERROR(C14/'Inputs'!$C$11,0)</f>
+      <c r="C15" s="46">
+        <f>IFERROR(C14/'Assumptions'!$C$11,0)</f>
         <v/>
       </c>
     </row>
@@ -6861,7 +6969,7 @@
           <t>Avg years to sale (pipeline)</t>
         </is>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="51">
         <f>AVERAGE('Calc_Project_rNPV'!$D$4:$D$9)</f>
         <v/>
       </c>
@@ -6872,8 +6980,8 @@
           <t>Discount factor @ base over avg years</t>
         </is>
       </c>
-      <c r="C18" s="45">
-        <f>1/(1+'Inputs'!$C$7)^C17</f>
+      <c r="C18" s="47">
+        <f>1/(1+'Assumptions'!$C$7)^C17</f>
         <v/>
       </c>
     </row>
@@ -6883,7 +6991,7 @@
           <t>Per-project rNPV (blended; live scenario)</t>
         </is>
       </c>
-      <c r="C19" s="44">
+      <c r="C19" s="46">
         <f>('Calc_Project_rNPV'!$M$11*'Scenarios'!$E$6-C9)*C5*C18</f>
         <v/>
       </c>
@@ -6894,8 +7002,8 @@
           <t>Pipeline depth at exit (projects in flight)</t>
         </is>
       </c>
-      <c r="C20" s="40">
-        <f>'Inputs'!$C$48</f>
+      <c r="C20" s="42">
+        <f>'Assumptions'!$C$48</f>
         <v/>
       </c>
     </row>
@@ -6905,7 +7013,7 @@
           <t>Forward pipeline rNPV at exit (= depth × per-project)</t>
         </is>
       </c>
-      <c r="C21" s="50">
+      <c r="C21" s="52">
         <f>C20*C19</f>
         <v/>
       </c>
@@ -6916,8 +7024,8 @@
           <t>Net cash retained at exit (= MAX(0,realised) × (1−dist frac))</t>
         </is>
       </c>
-      <c r="C22" s="50">
-        <f>MAX(0,C14)*(1-'Inputs'!$C$49)</f>
+      <c r="C22" s="52">
+        <f>MAX(0,C14)*(1-'Assumptions'!$C$49)</f>
         <v/>
       </c>
     </row>
@@ -6927,8 +7035,8 @@
           <t>Debt at exit</t>
         </is>
       </c>
-      <c r="C23" s="51">
-        <f>'Inputs'!$C$50</f>
+      <c r="C23" s="53">
+        <f>'Assumptions'!$C$50</f>
         <v/>
       </c>
     </row>
@@ -6938,7 +7046,7 @@
           <t>Company exit equity = forward + retained − debt</t>
         </is>
       </c>
-      <c r="C24" s="52">
+      <c r="C24" s="54">
         <f>MAX(0,C21+C22-C23)</f>
         <v/>
       </c>
@@ -6956,8 +7064,8 @@
           <t>Cross-check exit eq — low (run-rate × low mult + retained − debt)</t>
         </is>
       </c>
-      <c r="C26" s="50">
-        <f>MAX(0,C15)*'Inputs'!$C$52+C22-C23</f>
+      <c r="C26" s="52">
+        <f>MAX(0,C15)*'Assumptions'!$C$52+C22-C23</f>
         <v/>
       </c>
     </row>
@@ -6967,8 +7075,8 @@
           <t>Cross-check exit eq — base</t>
         </is>
       </c>
-      <c r="C27" s="50">
-        <f>MAX(0,C15)*'Inputs'!$C$53+C22-C23</f>
+      <c r="C27" s="52">
+        <f>MAX(0,C15)*'Assumptions'!$C$53+C22-C23</f>
         <v/>
       </c>
     </row>
@@ -6978,8 +7086,8 @@
           <t>Cross-check exit eq — high</t>
         </is>
       </c>
-      <c r="C28" s="50">
-        <f>MAX(0,C15)*'Inputs'!$C$54+C22-C23</f>
+      <c r="C28" s="52">
+        <f>MAX(0,C15)*'Assumptions'!$C$54+C22-C23</f>
         <v/>
       </c>
     </row>

--- a/financial_models/BESS_Valuation.xlsx
+++ b/financial_models/BESS_Valuation.xlsx
@@ -22,6 +22,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; Glossary" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Inputs" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Assumptions" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3923,6 +3925,1713 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00BFBFBF"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Raw_Inputs — Power Query feed from INPUTS_AND_ASSUMPTIONS.xlsx ('Inputs' sheet)</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>GENERATED stub — do NOT hand-edit. Wire the live, refreshable Power Query below, then Data -&gt; Refresh. The source workbook sits in the SAME folder as this model (relative path).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Step 1 — Formulas &gt; Define Name 'WorkbookPath'  = LEFT(CELL("filename",$A$1),FIND("[",CELL("filename",$A$1))-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Step 2 — Data &gt; Get Data &gt; Blank Query &gt; Advanced Editor, paste:</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>let
+    Path = Excel.CurrentWorkbook(){[Name="WorkbookPath"]}[Content]{0}[Column1],
+    Source = Excel.Workbook(File.Contents(Path &amp; "INPUTS_AND_ASSUMPTIONS.xlsx"), null, true),
+    Data = Source{[Item="Inputs",Kind="Sheet"]}[Data]
+in
+    Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Static snapshot (replaced when the live query refreshes):</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Inputs — SOURCED data (from data/raw/). GENERATED — do not hand-edit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Source name</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>source_key</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>Raw file (data/raw/…)</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>Page/Table or URL</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>Provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>RBA — Capital Market Yields (F2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>10-year CGS yield</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n">
+        <v>4.776</v>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>RBA — Cash Rate Target &amp; Capital Market Yields</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>rba</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>data/raw/rba-cgs-10yr-2026-06.csv</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>col 'Australian Government 10 year bond', row 17-Jun-2026</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>Independent (verified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>CSIRO — GenCost 2025-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>2-hour battery build cost (cell)</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="n">
+        <v>525</v>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>$/kWh</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>CSIRO — GenCost (annual, with AEMO)</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>csiro_gencost</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>data/raw/csiro-gencost-2025-26.pdf</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>current capital-cost tables, 2-hr battery [[TO CONFIRM: page]]</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>Independent (verified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>AEMO — 2026 Integrated System Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>Small-scale storage power (2030)</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>GW</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>AEMO — Integrated System Plan 2026 (storage trajectory)</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>aemo_isp</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>data/raw/aemo-2026-isp.pdf</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>Storage capacity, Step Change [[TO CONFIRM: page]]</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>Independent (verified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>Small-scale storage energy (2030)</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>AEMO — Integrated System Plan 2026 (storage trajectory)</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>aemo_isp</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>data/raw/aemo-2026-isp.pdf</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>Storage capacity, Step Change [[TO CONFIRM: page]]</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>Independent (verified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Grid-scale storage need (2050)</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>GW</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>AEMO — Integrated System Plan 2026 (storage trajectory)</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>aemo_isp</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>data/raw/aemo-2026-isp.pdf</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>Storage capacity, Step Change (35 + 5) [[TO CONFIRM: page]]</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>Independent (verified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Grid-scale storage in connections</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>GW</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>AEMO — Integrated System Plan 2026 (storage trajectory)</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>aemo_isp</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>data/raw/aemo-2026-isp.pdf</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>Connections / transition outlook (~45 of ~67 GW) [[TO CONFIRM: page]]</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>Independent (verified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>AEMO — gate benchmarks (Connections / Generation Information)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Grid-connection rate (RTB rights: agreement + GPS)</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>AEMO — Connections Scorecard / Key Connection Information (KCI)</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>aemo_connections</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>data/raw/ (Scorecard not pinned)</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>registration / executed connection agreement stage; NOT energisation</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>[[TO CONFIRM]] benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Reach-sale rate (proposed-&gt;committed attrition)</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n">
+        <v>80</v>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>AEMO — NEM Generation Information</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>aemo_generation_info</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>data/raw/aemo_generation_information_&lt;date&gt;.xlsx</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>proposed -&gt; committed status</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>[[TO CONFIRM]] benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>NSW Planning Portal — approval benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>Development-approval rate (independent benchmark)</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
+        <v>80</v>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>NSW Planning Portal — Major Projects / Application Tracker</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>nsw_planning</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>data/raw/nsw_planning_&lt;date&gt;.json</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>approved vs refused/withdrawn BESS major projects</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>[[TO CONFIRM]] benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Trade press — RTB $/MW comps (manager claim to verify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>RTB sale price — NSW</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>$m/MW</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>Energy trade press — RTB / development-rights deal comps</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>trade_press_comps</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>data/raw/trade_press_candidates_20260624.csv</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>trade-press deal comps (independent comps needed)</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>Proposed (manager)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>RTB sale price — VIC</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>$m/MW</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>Energy trade press — RTB / development-rights deal comps</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>trade_press_comps</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>data/raw/trade_press_candidates_20260624.csv</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>trade-press deal comps (independent comps needed)</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
+        <is>
+          <t>Proposed (manager)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>RTB sale price — SA</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>$m/MW</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>Energy trade press — RTB / development-rights deal comps</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>trade_press_comps</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>data/raw/trade_press_candidates_20260624.csv</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>trade-press deal comps (independent comps needed)</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>Proposed (manager)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>All-in built-asset value (context; above GenCost cell cost)</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>$m/MW</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>CSIRO — GenCost (annual, with AEMO)</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>csiro_gencost</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>data/raw/csiro-gencost-2025-26.pdf</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>all-in value ABOVE the ~$1.1m/MW cell cost — no primary</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>Placeholder [[TO CONFIRM]]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:I10"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00BFBFBF"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Raw_Assumptions — Power Query feed from INPUTS_AND_ASSUMPTIONS.xlsx ('Assumptions' sheet)</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>GENERATED stub — do NOT hand-edit. Wire the live, refreshable Power Query below, then Data -&gt; Refresh. The source workbook sits in the SAME folder as this model (relative path).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Step 1 — Formulas &gt; Define Name 'WorkbookPath'  = LEFT(CELL("filename",$A$1),FIND("[",CELL("filename",$A$1))-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Step 2 — Data &gt; Get Data &gt; Blank Query &gt; Advanced Editor, paste:</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>let
+    Path = Excel.CurrentWorkbook(){[Name="WorkbookPath"]}[Content]{0}[Column1],
+    Source = Excel.Workbook(File.Contents(Path &amp; "INPUTS_AND_ASSUMPTIONS.xlsx"), null, true),
+    Data = Source{[Item="Assumptions",Kind="Sheet"]}[Data]
+in
+    Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Static snapshot (replaced when the live query refreshes):</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Assumptions — JUDGEMENT (from config/assumptions.yaml). GENERATED — do not hand-edit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>How it's derived / rationale</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>source_key</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>[[TO CONFIRM]]</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>as_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Discount / required return</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>discount_rate.risk_premium</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Analyst judgement — development-stage equity risk premium (illustrative); all-in base ~18%</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>returns.vc_target_return</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>VC-method target return for development-stage equity (25%+); analyst judgement</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Company programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>company.programme_capital_m</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Illustrative scale of the company's equity-funded development programme; verify</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>company.projects_target</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Company plan — deliver &amp; sell ~35 ready-to-build projects; verify</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>company.term_years</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Company plan — ~2+1 year develop-and-flip programme cycle; verify</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>company.capital_call_profile</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>0.5, 0.5, 0.0, 0.0</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Illustrative — development spend in yrs 0-1</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>company.distribution_profile</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>0.0, 0.0, 0.5, 0.5</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Illustrative — programme proceeds in yrs 2-3</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>Equity deal terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>equity_deal.pre_money_m</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>[[TO CONFIRM]] PLACEHOLDER — the company's pre-money valuation (value before our money goes in)</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>equity_deal.investment_amount_m</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>[[TO CONFIRM]] PLACEHOLDER — our equity cheque</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>equity_deal.option_pool_pct</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>[[TO CONFIRM]] PLACEHOLDER — staff option pool created at our round (dilutes us)</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>equity_deal.future_round_dilution_pct</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>[[TO CONFIRM]] PLACEHOLDER — expected dilution from future capital raises before exit</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>equity_deal.liquidation_preference_x</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — 1x non-participating preferred (the greater of our money back or our as-converted share); confirm in the term sheet</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>equity_deal.exit_year</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>[[TO CONFIRM]] PLACEHOLDER — years to our exit (we sell our shares)</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>Exit drivers</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>exit_value.pipeline_depth_at_exit</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>[[TO CONFIRM]] PLACEHOLDER — number of projects still IN FLIGHT (not yet sold) when we exit; the MAIN sensitivity of the pipeline basis (see Exhibit D). The company targets ~35 delivered over its programme.</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>exit_value.interim_distribution_fraction</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>[[TO CONFIRM]] PLACEHOLDER — fraction of realised net programme profit DISTRIBUTED to shareholders during the hold (convention (b), IC_MEMO §7). 0% (conservative) retains all realised profit and counts it ONCE, at face value, in the exit value — never at a multiple. Raise once the distribution policy is confirmed.</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>exit_value.debt_at_exit_m</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>[[TO CONFIRM]] PLACEHOLDER — company debt outstanding at exit; the company is equity-funded, so 0 by default.</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>exit_value_crosscheck.earnings_multiple.low</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>low EV/earnings multiple for a development platform</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>exit_value_crosscheck.earnings_multiple.base</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>base EV/earnings multiple for a development platform</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>exit_value_crosscheck.earnings_multiple.high</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>high EV/earnings multiple for a development platform</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>Development cost &amp; attrition</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>dev_cost.per_project_m</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>Manager claim ~$500k/project — verify bottom-up</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="G40" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>dev_cost.abandonment_fraction</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>Illustrative (conservative) — partial spend before a failed project is abandoned</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="G41" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>Gates / scenarios (manager DA claim)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>scenarios</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>Illustrative representative pipeline; sizes/locations synthetic (not a real portfolio).</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>Value ladder</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>value_ladder.years_to_r1</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>[[TO CONFIRM]] years to RTB sale</t>
+        </is>
+      </c>
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G47" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>value_ladder.operating_ramp_years</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>[[TO CONFIRM]] operating ramp before R3 sale</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>value_ladder.stabilised_premium</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>[[TO CONFIRM]] stabilised-asset premium</t>
+        </is>
+      </c>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G49" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>value_ladder.equity_dilution_r2</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>[[TO CONFIRM]] equity raised to build dilutes us</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="F50" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G50" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>value_ladder.equity_dilution_r3</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>[[TO CONFIRM]] equity raised to operate dilutes us further</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="inlineStr">
+        <is>
+          <t>none / judgement</t>
+        </is>
+      </c>
+      <c r="F51" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G51" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:I10"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3930,7 +5639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4186,6 +5895,28 @@
           <t>Sources + glossary</t>
         </is>
       </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Raw_Inputs</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Raw_Assumptions</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4204,6 +5935,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
